--- a/价格数据模版.xlsx
+++ b/价格数据模版.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="13">
   <si>
     <t>日期</t>
   </si>
@@ -241,12 +241,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -580,7 +586,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -604,16 +610,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -622,89 +628,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -712,6 +718,8 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1051,7 +1059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1323"/>
+  <dimension ref="A1:F1400"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="25.75" customWidth="1"/>
@@ -27515,6 +27523,881 @@
       </c>
       <c r="F1323">
         <v>59.3</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:6">
+      <c r="A1324" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1324">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:6">
+      <c r="A1325" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1325">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:6">
+      <c r="A1326" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1326">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:6">
+      <c r="A1327" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1327">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:6">
+      <c r="A1328" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1328">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:6">
+      <c r="A1329" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1329">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:6">
+      <c r="A1330" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1330">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:6">
+      <c r="A1331" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1331">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:6">
+      <c r="A1332" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1332">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:6">
+      <c r="A1333" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1333">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:6">
+      <c r="A1334" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1334">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:6">
+      <c r="A1335" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1335">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:6">
+      <c r="A1336" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1336">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:6">
+      <c r="A1337" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1337">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:6">
+      <c r="A1338" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1338">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:6">
+      <c r="A1339" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1339">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:6">
+      <c r="A1340" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1340">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:6">
+      <c r="A1341" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1341">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:6">
+      <c r="A1342" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1342">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:6">
+      <c r="A1343" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1343">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:6">
+      <c r="A1344" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1344">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:6">
+      <c r="A1345" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1345">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:6">
+      <c r="A1346" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1346">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:6">
+      <c r="A1347" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1347">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:6">
+      <c r="A1348" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1348">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:6">
+      <c r="A1349" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1349">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:6">
+      <c r="A1350" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1350">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:6">
+      <c r="A1351" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1351">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:6">
+      <c r="A1352" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1352">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:6">
+      <c r="A1353" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1353">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:6">
+      <c r="A1354" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1354">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:6">
+      <c r="A1355" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1355">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:6">
+      <c r="A1356" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1356">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:6">
+      <c r="A1357" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1357">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:6">
+      <c r="A1358" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1358">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:6">
+      <c r="A1359" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1359">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:6">
+      <c r="A1360" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1360">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:6">
+      <c r="A1361" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1361">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:6">
+      <c r="A1362" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1362">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:6">
+      <c r="A1363" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1363">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:6">
+      <c r="A1364" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1364">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:6">
+      <c r="A1365" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1365">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:6">
+      <c r="A1366" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1366">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:6">
+      <c r="A1367" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1367">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:6">
+      <c r="A1368" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1368">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:6">
+      <c r="A1369" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1369">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:6">
+      <c r="A1370" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1370">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:6">
+      <c r="A1371" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1371">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:6">
+      <c r="A1372" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1372">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:6">
+      <c r="A1373" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1373">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:6">
+      <c r="A1374" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1374">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:6">
+      <c r="A1375" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1375">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:6">
+      <c r="A1376" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1376">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:6">
+      <c r="A1377" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1377">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:6">
+      <c r="A1378" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1378">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:6">
+      <c r="A1379" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1379">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:6">
+      <c r="A1380" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1380">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:6">
+      <c r="A1381" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1381">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:6">
+      <c r="A1382" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1382">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:6">
+      <c r="A1383" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1383">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:6">
+      <c r="A1384" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1384">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:6">
+      <c r="A1385" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1385">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:6">
+      <c r="A1386" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1386">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:6">
+      <c r="A1387" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1387"/>
+      <c r="F1387">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:6">
+      <c r="A1388" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1388"/>
+      <c r="F1388">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:6">
+      <c r="A1389" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1389"/>
+      <c r="F1389">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:6">
+      <c r="A1390" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1390"/>
+      <c r="F1390">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:6">
+      <c r="A1391" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1391"/>
+      <c r="F1391">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:6">
+      <c r="A1392" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1392"/>
+      <c r="F1392">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:6">
+      <c r="A1393" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1393"/>
+      <c r="F1393">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:6">
+      <c r="A1394" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1394" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1394" s="6"/>
+      <c r="D1394" s="6"/>
+      <c r="E1394" s="6"/>
+      <c r="F1394" s="6">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:6">
+      <c r="A1395" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1395" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1395" s="6"/>
+      <c r="D1395" s="6"/>
+      <c r="E1395" s="6"/>
+      <c r="F1395" s="6">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:6">
+      <c r="A1396" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1396" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1396" s="6"/>
+      <c r="D1396" s="6"/>
+      <c r="E1396" s="6"/>
+      <c r="F1396" s="6">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:6">
+      <c r="A1397" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1397" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1397" s="6"/>
+      <c r="D1397" s="6"/>
+      <c r="E1397" s="6"/>
+      <c r="F1397" s="6">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:6">
+      <c r="A1398" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1398" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1398" s="6"/>
+      <c r="D1398" s="6"/>
+      <c r="E1398" s="6"/>
+      <c r="F1398" s="6">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:6">
+      <c r="A1399" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1399" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1399" s="6"/>
+      <c r="D1399" s="6"/>
+      <c r="E1399" s="6"/>
+      <c r="F1399" s="6">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:6">
+      <c r="A1400" s="5">
+        <v>45868</v>
+      </c>
+      <c r="B1400" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1400" s="6"/>
+      <c r="D1400" s="6"/>
+      <c r="E1400" s="6"/>
+      <c r="F1400" s="6">
+        <v>58.8</v>
       </c>
     </row>
   </sheetData>

--- a/价格数据模版.xlsx
+++ b/价格数据模版.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="13">
   <si>
     <t>日期</t>
   </si>
@@ -1065,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1932"/>
+  <dimension ref="A1:F2177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="25.75" customWidth="1"/>
@@ -35788,7 +35788,7 @@
         <v>57.01</v>
       </c>
       <c r="F1736" s="3">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1737" spans="1:6">
@@ -35928,7 +35928,7 @@
         <v>56.78</v>
       </c>
       <c r="F1743" s="3">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1744" spans="1:6">
@@ -36068,7 +36068,7 @@
         <v>57.05</v>
       </c>
       <c r="F1750" s="3">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1751" spans="1:6">
@@ -36208,7 +36208,7 @@
         <v>56.89</v>
       </c>
       <c r="F1757" s="3">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1758" spans="1:6">
@@ -36348,7 +36348,7 @@
         <v>57.26</v>
       </c>
       <c r="F1764" s="3">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="1765" spans="1:6">
@@ -36488,7 +36488,7 @@
         <v>56.83</v>
       </c>
       <c r="F1771" s="3">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="1772" spans="1:6">
@@ -36628,7 +36628,7 @@
         <v>57.3</v>
       </c>
       <c r="F1778" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1779" spans="1:6">
@@ -36768,7 +36768,7 @@
         <v>57.25</v>
       </c>
       <c r="F1785" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1786" spans="1:6">
@@ -36908,7 +36908,7 @@
         <v>56.96</v>
       </c>
       <c r="F1792" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1793" spans="1:6">
@@ -37048,7 +37048,7 @@
         <v>57.09</v>
       </c>
       <c r="F1799" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1800" spans="1:6">
@@ -37188,7 +37188,7 @@
         <v>57.16</v>
       </c>
       <c r="F1806" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1807" spans="1:6">
@@ -37328,7 +37328,7 @@
         <v>57.29</v>
       </c>
       <c r="F1813" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1814" spans="1:6">
@@ -37468,7 +37468,7 @@
         <v>57.07</v>
       </c>
       <c r="F1820" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1821" spans="1:6">
@@ -37608,7 +37608,7 @@
         <v>56.9</v>
       </c>
       <c r="F1827" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1828" spans="1:6">
@@ -37748,7 +37748,7 @@
         <v>57.11</v>
       </c>
       <c r="F1834" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1835" spans="1:6">
@@ -37888,7 +37888,7 @@
         <v>57.08</v>
       </c>
       <c r="F1841" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1842" spans="1:6">
@@ -38028,147 +38028,147 @@
         <v>57.14</v>
       </c>
       <c r="F1848" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1849" spans="1:6">
-      <c r="A1849" s="4">
+      <c r="A1849" s="2">
         <v>45961</v>
       </c>
-      <c r="B1849" s="5" t="s">
+      <c r="B1849" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1849" s="5">
+      <c r="C1849" s="3">
         <v>59.23</v>
       </c>
-      <c r="D1849" s="5">
+      <c r="D1849" s="3">
         <v>59.51</v>
       </c>
-      <c r="E1849" s="5">
+      <c r="E1849" s="3">
         <v>58.34</v>
       </c>
-      <c r="F1849" s="5">
+      <c r="F1849" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="1850" spans="1:6">
-      <c r="A1850" s="4">
+      <c r="A1850" s="2">
         <v>45961</v>
       </c>
-      <c r="B1850" s="5" t="s">
+      <c r="B1850" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1850" s="5">
+      <c r="C1850" s="3">
         <v>57.76</v>
       </c>
-      <c r="D1850" s="5">
+      <c r="D1850" s="3">
         <v>57.98</v>
       </c>
-      <c r="E1850" s="5">
+      <c r="E1850" s="3">
         <v>57.11</v>
       </c>
-      <c r="F1850" s="5">
+      <c r="F1850" s="3">
         <v>57.2</v>
       </c>
     </row>
     <row r="1851" spans="1:6">
-      <c r="A1851" s="4">
+      <c r="A1851" s="2">
         <v>45961</v>
       </c>
-      <c r="B1851" s="5" t="s">
+      <c r="B1851" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1851" s="5">
+      <c r="C1851" s="3">
         <v>49.01</v>
       </c>
-      <c r="D1851" s="5">
+      <c r="D1851" s="3">
         <v>49.11</v>
       </c>
-      <c r="E1851" s="5">
+      <c r="E1851" s="3">
         <v>48.72</v>
       </c>
-      <c r="F1851" s="5">
+      <c r="F1851" s="3">
         <v>49</v>
       </c>
     </row>
     <row r="1852" spans="1:6">
-      <c r="A1852" s="4">
+      <c r="A1852" s="2">
         <v>45961</v>
       </c>
-      <c r="B1852" s="5" t="s">
+      <c r="B1852" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1852" s="5">
+      <c r="C1852" s="3">
         <v>41.71</v>
       </c>
-      <c r="D1852" s="5">
+      <c r="D1852" s="3">
         <v>41.81</v>
       </c>
-      <c r="E1852" s="5">
+      <c r="E1852" s="3">
         <v>41.61</v>
       </c>
-      <c r="F1852" s="5">
+      <c r="F1852" s="3">
         <v>41.7</v>
       </c>
     </row>
     <row r="1853" spans="1:6">
-      <c r="A1853" s="4">
+      <c r="A1853" s="2">
         <v>45961</v>
       </c>
-      <c r="B1853" s="5" t="s">
+      <c r="B1853" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1853" s="5">
+      <c r="C1853" s="3">
         <v>41.41</v>
       </c>
-      <c r="D1853" s="5">
+      <c r="D1853" s="3">
         <v>41.79</v>
       </c>
-      <c r="E1853" s="5">
+      <c r="E1853" s="3">
         <v>41.38</v>
       </c>
-      <c r="F1853" s="5">
+      <c r="F1853" s="3">
         <v>41.5</v>
       </c>
     </row>
     <row r="1854" spans="1:6">
-      <c r="A1854" s="4">
+      <c r="A1854" s="2">
         <v>45961</v>
       </c>
-      <c r="B1854" s="5" t="s">
+      <c r="B1854" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1854" s="5">
+      <c r="C1854" s="3">
         <v>54.8</v>
       </c>
-      <c r="D1854" s="5">
+      <c r="D1854" s="3">
         <v>55.39</v>
       </c>
-      <c r="E1854" s="5">
+      <c r="E1854" s="3">
         <v>54.73</v>
       </c>
-      <c r="F1854" s="5">
+      <c r="F1854" s="3">
         <v>55.1</v>
       </c>
     </row>
     <row r="1855" spans="1:6">
-      <c r="A1855" s="4">
+      <c r="A1855" s="2">
         <v>45961</v>
       </c>
-      <c r="B1855" s="5" t="s">
+      <c r="B1855" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1855" s="5">
+      <c r="C1855" s="3">
         <v>57.91</v>
       </c>
-      <c r="D1855" s="5">
+      <c r="D1855" s="3">
         <v>57.99</v>
       </c>
-      <c r="E1855" s="5">
+      <c r="E1855" s="3">
         <v>57.33</v>
       </c>
-      <c r="F1855" s="5">
-        <v>57.5</v>
+      <c r="F1855" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1856" spans="1:6">
@@ -38178,10 +38178,16 @@
       <c r="B1856" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1856" s="3"/>
-      <c r="D1856" s="3"/>
-      <c r="E1856" s="3"/>
-      <c r="F1856" s="5">
+      <c r="C1856" s="3">
+        <v>58.55</v>
+      </c>
+      <c r="D1856" s="3">
+        <v>59.12</v>
+      </c>
+      <c r="E1856" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="F1856" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38192,10 +38198,16 @@
       <c r="B1857" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1857" s="3"/>
-      <c r="D1857" s="3"/>
-      <c r="E1857" s="3"/>
-      <c r="F1857" s="5">
+      <c r="C1857" s="3">
+        <v>57.71</v>
+      </c>
+      <c r="D1857" s="3">
+        <v>57.99</v>
+      </c>
+      <c r="E1857" s="3">
+        <v>56.85</v>
+      </c>
+      <c r="F1857" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38206,10 +38218,16 @@
       <c r="B1858" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1858" s="3"/>
-      <c r="D1858" s="3"/>
-      <c r="E1858" s="3"/>
-      <c r="F1858" s="5">
+      <c r="C1858" s="3">
+        <v>48.81</v>
+      </c>
+      <c r="D1858" s="3">
+        <v>49.01</v>
+      </c>
+      <c r="E1858" s="3">
+        <v>48.77</v>
+      </c>
+      <c r="F1858" s="3">
         <v>48.8</v>
       </c>
     </row>
@@ -38220,10 +38238,16 @@
       <c r="B1859" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1859" s="3"/>
-      <c r="D1859" s="3"/>
-      <c r="E1859" s="3"/>
-      <c r="F1859" s="5">
+      <c r="C1859" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="D1859" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="E1859" s="3">
+        <v>41.24</v>
+      </c>
+      <c r="F1859" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38234,10 +38258,16 @@
       <c r="B1860" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1860" s="3"/>
-      <c r="D1860" s="3"/>
-      <c r="E1860" s="3"/>
-      <c r="F1860" s="5">
+      <c r="C1860" s="3">
+        <v>41.18</v>
+      </c>
+      <c r="D1860" s="3">
+        <v>41.61</v>
+      </c>
+      <c r="E1860" s="3">
+        <v>40.99</v>
+      </c>
+      <c r="F1860" s="3">
         <v>41.5</v>
       </c>
     </row>
@@ -38248,10 +38278,16 @@
       <c r="B1861" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1861" s="3"/>
-      <c r="D1861" s="3"/>
-      <c r="E1861" s="3"/>
-      <c r="F1861" s="5">
+      <c r="C1861" s="3">
+        <v>55.47</v>
+      </c>
+      <c r="D1861" s="3">
+        <v>55.56</v>
+      </c>
+      <c r="E1861" s="3">
+        <v>55.02</v>
+      </c>
+      <c r="F1861" s="3">
         <v>55.1</v>
       </c>
     </row>
@@ -38262,11 +38298,17 @@
       <c r="B1862" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1862" s="3"/>
-      <c r="D1862" s="3"/>
-      <c r="E1862" s="3"/>
-      <c r="F1862" s="5">
-        <v>57.5</v>
+      <c r="C1862" s="3">
+        <v>57.95</v>
+      </c>
+      <c r="D1862" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="E1862" s="3">
+        <v>57.22</v>
+      </c>
+      <c r="F1862" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1863" spans="1:6">
@@ -38276,10 +38318,16 @@
       <c r="B1863" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1863" s="3"/>
-      <c r="D1863" s="3"/>
-      <c r="E1863" s="3"/>
-      <c r="F1863" s="5">
+      <c r="C1863" s="3">
+        <v>58.82</v>
+      </c>
+      <c r="D1863" s="3">
+        <v>58.86</v>
+      </c>
+      <c r="E1863" s="3">
+        <v>58.63</v>
+      </c>
+      <c r="F1863" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38290,10 +38338,16 @@
       <c r="B1864" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1864" s="3"/>
-      <c r="D1864" s="3"/>
-      <c r="E1864" s="3"/>
-      <c r="F1864" s="5">
+      <c r="C1864" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="D1864" s="3">
+        <v>57.24</v>
+      </c>
+      <c r="E1864" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F1864" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38304,10 +38358,16 @@
       <c r="B1865" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1865" s="3"/>
-      <c r="D1865" s="3"/>
-      <c r="E1865" s="3"/>
-      <c r="F1865" s="5">
+      <c r="C1865" s="3">
+        <v>48.68</v>
+      </c>
+      <c r="D1865" s="3">
+        <v>48.87</v>
+      </c>
+      <c r="E1865" s="3">
+        <v>48.53</v>
+      </c>
+      <c r="F1865" s="3">
         <v>48.6</v>
       </c>
     </row>
@@ -38318,10 +38378,16 @@
       <c r="B1866" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1866" s="3"/>
-      <c r="D1866" s="3"/>
-      <c r="E1866" s="3"/>
-      <c r="F1866" s="5">
+      <c r="C1866" s="3">
+        <v>41.55</v>
+      </c>
+      <c r="D1866" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="E1866" s="3">
+        <v>41.36</v>
+      </c>
+      <c r="F1866" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38332,10 +38398,16 @@
       <c r="B1867" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1867" s="3"/>
-      <c r="D1867" s="3"/>
-      <c r="E1867" s="3"/>
-      <c r="F1867" s="5">
+      <c r="C1867" s="3">
+        <v>41.35</v>
+      </c>
+      <c r="D1867" s="3">
+        <v>41.66</v>
+      </c>
+      <c r="E1867" s="3">
+        <v>41.21</v>
+      </c>
+      <c r="F1867" s="3">
         <v>41.5</v>
       </c>
     </row>
@@ -38346,10 +38418,16 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="3"/>
-      <c r="D1868" s="3"/>
-      <c r="E1868" s="3"/>
-      <c r="F1868" s="5">
+      <c r="C1868" s="3">
+        <v>54.59</v>
+      </c>
+      <c r="D1868" s="3">
+        <v>55.34</v>
+      </c>
+      <c r="E1868" s="3">
+        <v>54.41</v>
+      </c>
+      <c r="F1868" s="3">
         <v>55.1</v>
       </c>
     </row>
@@ -38360,11 +38438,17 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="3"/>
-      <c r="D1869" s="3"/>
-      <c r="E1869" s="3"/>
-      <c r="F1869" s="5">
-        <v>57.5</v>
+      <c r="C1869" s="3">
+        <v>57.02</v>
+      </c>
+      <c r="D1869" s="3">
+        <v>57.57</v>
+      </c>
+      <c r="E1869" s="3">
+        <v>56.77</v>
+      </c>
+      <c r="F1869" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1870" spans="1:6">
@@ -38374,10 +38458,16 @@
       <c r="B1870" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1870" s="3"/>
-      <c r="D1870" s="3"/>
-      <c r="E1870" s="3"/>
-      <c r="F1870" s="5">
+      <c r="C1870" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="D1870" s="3">
+        <v>59.08</v>
+      </c>
+      <c r="E1870" s="3">
+        <v>58.01</v>
+      </c>
+      <c r="F1870" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38388,10 +38478,16 @@
       <c r="B1871" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1871" s="3"/>
-      <c r="D1871" s="3"/>
-      <c r="E1871" s="3"/>
-      <c r="F1871" s="5">
+      <c r="C1871" s="3">
+        <v>57.13</v>
+      </c>
+      <c r="D1871" s="3">
+        <v>57.25</v>
+      </c>
+      <c r="E1871" s="3">
+        <v>56.99</v>
+      </c>
+      <c r="F1871" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38402,10 +38498,16 @@
       <c r="B1872" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1872" s="3"/>
-      <c r="D1872" s="3"/>
-      <c r="E1872" s="3"/>
-      <c r="F1872" s="5">
+      <c r="C1872" s="3">
+        <v>48.5</v>
+      </c>
+      <c r="D1872" s="3">
+        <v>48.7</v>
+      </c>
+      <c r="E1872" s="3">
+        <v>48.24</v>
+      </c>
+      <c r="F1872" s="3">
         <v>48.5</v>
       </c>
     </row>
@@ -38416,10 +38518,16 @@
       <c r="B1873" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1873" s="3"/>
-      <c r="D1873" s="3"/>
-      <c r="E1873" s="3"/>
-      <c r="F1873" s="5">
+      <c r="C1873" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="D1873" s="3">
+        <v>41.83</v>
+      </c>
+      <c r="E1873" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="F1873" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38430,10 +38538,16 @@
       <c r="B1874" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1874" s="3"/>
-      <c r="D1874" s="3"/>
-      <c r="E1874" s="3"/>
-      <c r="F1874" s="5">
+      <c r="C1874" s="3">
+        <v>41.39</v>
+      </c>
+      <c r="D1874" s="3">
+        <v>41.8</v>
+      </c>
+      <c r="E1874" s="3">
+        <v>41.19</v>
+      </c>
+      <c r="F1874" s="3">
         <v>41.5</v>
       </c>
     </row>
@@ -38444,10 +38558,16 @@
       <c r="B1875" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1875" s="3"/>
-      <c r="D1875" s="3"/>
-      <c r="E1875" s="3"/>
-      <c r="F1875" s="5">
+      <c r="C1875" s="3">
+        <v>54.57</v>
+      </c>
+      <c r="D1875" s="3">
+        <v>55.31</v>
+      </c>
+      <c r="E1875" s="3">
+        <v>54.51</v>
+      </c>
+      <c r="F1875" s="3">
         <v>55.1</v>
       </c>
     </row>
@@ -38458,11 +38578,17 @@
       <c r="B1876" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1876" s="3"/>
-      <c r="D1876" s="3"/>
-      <c r="E1876" s="3"/>
-      <c r="F1876" s="5">
-        <v>57.5</v>
+      <c r="C1876" s="3">
+        <v>57.62</v>
+      </c>
+      <c r="D1876" s="3">
+        <v>57.63</v>
+      </c>
+      <c r="E1876" s="3">
+        <v>57.46</v>
+      </c>
+      <c r="F1876" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1877" spans="1:6">
@@ -38472,10 +38598,16 @@
       <c r="B1877" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1877" s="3"/>
-      <c r="D1877" s="3"/>
-      <c r="E1877" s="3"/>
-      <c r="F1877" s="5">
+      <c r="C1877" s="3">
+        <v>58.94</v>
+      </c>
+      <c r="D1877" s="3">
+        <v>58.95</v>
+      </c>
+      <c r="E1877" s="3">
+        <v>58.27</v>
+      </c>
+      <c r="F1877" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38486,10 +38618,16 @@
       <c r="B1878" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1878" s="3"/>
-      <c r="D1878" s="3"/>
-      <c r="E1878" s="3"/>
-      <c r="F1878" s="5">
+      <c r="C1878" s="3">
+        <v>56.67</v>
+      </c>
+      <c r="D1878" s="3">
+        <v>57.59</v>
+      </c>
+      <c r="E1878" s="3">
+        <v>56.59</v>
+      </c>
+      <c r="F1878" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38500,10 +38638,16 @@
       <c r="B1879" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1879" s="3"/>
-      <c r="D1879" s="3"/>
-      <c r="E1879" s="3"/>
-      <c r="F1879" s="5">
+      <c r="C1879" s="3">
+        <v>48.72</v>
+      </c>
+      <c r="D1879" s="3">
+        <v>48.91</v>
+      </c>
+      <c r="E1879" s="3">
+        <v>48.47</v>
+      </c>
+      <c r="F1879" s="3">
         <v>48.5</v>
       </c>
     </row>
@@ -38514,10 +38658,16 @@
       <c r="B1880" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1880" s="3"/>
-      <c r="D1880" s="3"/>
-      <c r="E1880" s="3"/>
-      <c r="F1880" s="5">
+      <c r="C1880" s="3">
+        <v>41.47</v>
+      </c>
+      <c r="D1880" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="E1880" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="F1880" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38528,10 +38678,16 @@
       <c r="B1881" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1881" s="3"/>
-      <c r="D1881" s="3"/>
-      <c r="E1881" s="3"/>
-      <c r="F1881" s="5">
+      <c r="C1881" s="3">
+        <v>41.29</v>
+      </c>
+      <c r="D1881" s="3">
+        <v>41.65</v>
+      </c>
+      <c r="E1881" s="3">
+        <v>41.23</v>
+      </c>
+      <c r="F1881" s="3">
         <v>41.5</v>
       </c>
     </row>
@@ -38542,10 +38698,16 @@
       <c r="B1882" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1882" s="3"/>
-      <c r="D1882" s="3"/>
-      <c r="E1882" s="3"/>
-      <c r="F1882" s="5">
+      <c r="C1882" s="3">
+        <v>55.26</v>
+      </c>
+      <c r="D1882" s="3">
+        <v>55.31</v>
+      </c>
+      <c r="E1882" s="3">
+        <v>54.81</v>
+      </c>
+      <c r="F1882" s="3">
         <v>55.1</v>
       </c>
     </row>
@@ -38556,11 +38718,17 @@
       <c r="B1883" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1883" s="3"/>
-      <c r="D1883" s="3"/>
-      <c r="E1883" s="3"/>
-      <c r="F1883" s="5">
-        <v>57.5</v>
+      <c r="C1883" s="3">
+        <v>57.69</v>
+      </c>
+      <c r="D1883" s="3">
+        <v>57.69</v>
+      </c>
+      <c r="E1883" s="3">
+        <v>57.43</v>
+      </c>
+      <c r="F1883" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1884" spans="1:6">
@@ -38570,10 +38738,16 @@
       <c r="B1884" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1884" s="3"/>
-      <c r="D1884" s="3"/>
-      <c r="E1884" s="3"/>
-      <c r="F1884" s="5">
+      <c r="C1884" s="3">
+        <v>59.09</v>
+      </c>
+      <c r="D1884" s="3">
+        <v>59.15</v>
+      </c>
+      <c r="E1884" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="F1884" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38584,10 +38758,16 @@
       <c r="B1885" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1885" s="3"/>
-      <c r="D1885" s="3"/>
-      <c r="E1885" s="3"/>
-      <c r="F1885" s="5">
+      <c r="C1885" s="3">
+        <v>57.39</v>
+      </c>
+      <c r="D1885" s="3">
+        <v>57.48</v>
+      </c>
+      <c r="E1885" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="F1885" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38598,10 +38778,16 @@
       <c r="B1886" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1886" s="3"/>
-      <c r="D1886" s="3"/>
-      <c r="E1886" s="3"/>
-      <c r="F1886" s="5">
+      <c r="C1886" s="3">
+        <v>48.24</v>
+      </c>
+      <c r="D1886" s="3">
+        <v>48.27</v>
+      </c>
+      <c r="E1886" s="3">
+        <v>47.89</v>
+      </c>
+      <c r="F1886" s="3">
         <v>48.2</v>
       </c>
     </row>
@@ -38612,10 +38798,16 @@
       <c r="B1887" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1887" s="3"/>
-      <c r="D1887" s="3"/>
-      <c r="E1887" s="3"/>
-      <c r="F1887" s="5">
+      <c r="C1887" s="3">
+        <v>41.42</v>
+      </c>
+      <c r="D1887" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E1887" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="F1887" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38626,10 +38818,16 @@
       <c r="B1888" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1888" s="3"/>
-      <c r="D1888" s="3"/>
-      <c r="E1888" s="3"/>
-      <c r="F1888" s="5">
+      <c r="C1888" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="D1888" s="3">
+        <v>41.42</v>
+      </c>
+      <c r="E1888" s="3">
+        <v>41.21</v>
+      </c>
+      <c r="F1888" s="3">
         <v>41.4</v>
       </c>
     </row>
@@ -38640,10 +38838,16 @@
       <c r="B1889" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1889" s="3"/>
-      <c r="D1889" s="3"/>
-      <c r="E1889" s="3"/>
-      <c r="F1889" s="5">
+      <c r="C1889" s="3">
+        <v>55.02</v>
+      </c>
+      <c r="D1889" s="3">
+        <v>55.27</v>
+      </c>
+      <c r="E1889" s="3">
+        <v>54.94</v>
+      </c>
+      <c r="F1889" s="3">
         <v>55</v>
       </c>
     </row>
@@ -38654,11 +38858,17 @@
       <c r="B1890" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1890" s="3"/>
-      <c r="D1890" s="3"/>
-      <c r="E1890" s="3"/>
-      <c r="F1890" s="5">
-        <v>57.5</v>
+      <c r="C1890" s="3">
+        <v>57.56</v>
+      </c>
+      <c r="D1890" s="3">
+        <v>57.76</v>
+      </c>
+      <c r="E1890" s="3">
+        <v>57.22</v>
+      </c>
+      <c r="F1890" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1891" spans="1:6">
@@ -38668,10 +38878,16 @@
       <c r="B1891" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1891" s="3"/>
-      <c r="D1891" s="3"/>
-      <c r="E1891" s="3"/>
-      <c r="F1891" s="5">
+      <c r="C1891" s="3">
+        <v>58.33</v>
+      </c>
+      <c r="D1891" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1891" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="F1891" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38682,10 +38898,16 @@
       <c r="B1892" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1892" s="3"/>
-      <c r="D1892" s="3"/>
-      <c r="E1892" s="3"/>
-      <c r="F1892" s="5">
+      <c r="C1892" s="3">
+        <v>57.25</v>
+      </c>
+      <c r="D1892" s="3">
+        <v>57.31</v>
+      </c>
+      <c r="E1892" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F1892" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38696,10 +38918,16 @@
       <c r="B1893" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1893" s="3"/>
-      <c r="D1893" s="3"/>
-      <c r="E1893" s="3"/>
-      <c r="F1893" s="5">
+      <c r="C1893" s="3">
+        <v>47.97</v>
+      </c>
+      <c r="D1893" s="3">
+        <v>48.05</v>
+      </c>
+      <c r="E1893" s="3">
+        <v>47.88</v>
+      </c>
+      <c r="F1893" s="3">
         <v>47.9</v>
       </c>
     </row>
@@ -38710,10 +38938,16 @@
       <c r="B1894" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1894" s="3"/>
-      <c r="D1894" s="3"/>
-      <c r="E1894" s="3"/>
-      <c r="F1894" s="5">
+      <c r="C1894" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="D1894" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E1894" s="3">
+        <v>41.45</v>
+      </c>
+      <c r="F1894" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -38724,10 +38958,16 @@
       <c r="B1895" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1895" s="3"/>
-      <c r="D1895" s="3"/>
-      <c r="E1895" s="3"/>
-      <c r="F1895" s="5">
+      <c r="C1895" s="3">
+        <v>41.32</v>
+      </c>
+      <c r="D1895" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="E1895" s="3">
+        <v>41.21</v>
+      </c>
+      <c r="F1895" s="3">
         <v>41.3</v>
       </c>
     </row>
@@ -38738,10 +38978,16 @@
       <c r="B1896" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1896" s="3"/>
-      <c r="D1896" s="3"/>
-      <c r="E1896" s="3"/>
-      <c r="F1896" s="5">
+      <c r="C1896" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="D1896" s="3">
+        <v>55.05</v>
+      </c>
+      <c r="E1896" s="3">
+        <v>54.57</v>
+      </c>
+      <c r="F1896" s="3">
         <v>55</v>
       </c>
     </row>
@@ -38752,11 +38998,17 @@
       <c r="B1897" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1897" s="3"/>
-      <c r="D1897" s="3"/>
-      <c r="E1897" s="3"/>
-      <c r="F1897" s="5">
-        <v>57.5</v>
+      <c r="C1897" s="3">
+        <v>57.18</v>
+      </c>
+      <c r="D1897" s="3">
+        <v>57.81</v>
+      </c>
+      <c r="E1897" s="3">
+        <v>57.12</v>
+      </c>
+      <c r="F1897" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1898" spans="1:6">
@@ -38766,10 +39018,16 @@
       <c r="B1898" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1898" s="3"/>
-      <c r="D1898" s="3"/>
-      <c r="E1898" s="3"/>
-      <c r="F1898" s="5">
+      <c r="C1898" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="D1898" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1898" s="3">
+        <v>58.44</v>
+      </c>
+      <c r="F1898" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38780,10 +39038,16 @@
       <c r="B1899" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1899" s="3"/>
-      <c r="D1899" s="3"/>
-      <c r="E1899" s="3"/>
-      <c r="F1899" s="5">
+      <c r="C1899" s="3">
+        <v>57.51</v>
+      </c>
+      <c r="D1899" s="3">
+        <v>57.78</v>
+      </c>
+      <c r="E1899" s="3">
+        <v>56.82</v>
+      </c>
+      <c r="F1899" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38794,10 +39058,16 @@
       <c r="B1900" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1900" s="3"/>
-      <c r="D1900" s="3"/>
-      <c r="E1900" s="3"/>
-      <c r="F1900" s="5">
+      <c r="C1900" s="3">
+        <v>47.72</v>
+      </c>
+      <c r="D1900" s="3">
+        <v>48.02</v>
+      </c>
+      <c r="E1900" s="3">
+        <v>47.54</v>
+      </c>
+      <c r="F1900" s="3">
         <v>47.9</v>
       </c>
     </row>
@@ -38808,10 +39078,16 @@
       <c r="B1901" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1901" s="3"/>
-      <c r="D1901" s="3"/>
-      <c r="E1901" s="3"/>
-      <c r="F1901" s="5">
+      <c r="C1901" s="3">
+        <v>41.61</v>
+      </c>
+      <c r="D1901" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="E1901" s="3">
+        <v>41.43</v>
+      </c>
+      <c r="F1901" s="3">
         <v>41.6</v>
       </c>
     </row>
@@ -38822,10 +39098,16 @@
       <c r="B1902" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1902" s="3"/>
-      <c r="D1902" s="3"/>
-      <c r="E1902" s="3"/>
-      <c r="F1902" s="5">
+      <c r="C1902" s="3">
+        <v>41.64</v>
+      </c>
+      <c r="D1902" s="3">
+        <v>41.69</v>
+      </c>
+      <c r="E1902" s="3">
+        <v>41.26</v>
+      </c>
+      <c r="F1902" s="3">
         <v>41.3</v>
       </c>
     </row>
@@ -38836,10 +39118,16 @@
       <c r="B1903" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1903" s="3"/>
-      <c r="D1903" s="3"/>
-      <c r="E1903" s="3"/>
-      <c r="F1903" s="5">
+      <c r="C1903" s="3">
+        <v>54.94</v>
+      </c>
+      <c r="D1903" s="3">
+        <v>55.01</v>
+      </c>
+      <c r="E1903" s="3">
+        <v>54.63</v>
+      </c>
+      <c r="F1903" s="3">
         <v>54.9</v>
       </c>
     </row>
@@ -38850,11 +39138,17 @@
       <c r="B1904" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1904" s="3"/>
-      <c r="D1904" s="3"/>
-      <c r="E1904" s="3"/>
-      <c r="F1904" s="5">
-        <v>57.5</v>
+      <c r="C1904" s="3">
+        <v>57.3</v>
+      </c>
+      <c r="D1904" s="3">
+        <v>57.82</v>
+      </c>
+      <c r="E1904" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="F1904" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1905" spans="1:6">
@@ -38864,10 +39158,16 @@
       <c r="B1905" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1905" s="3"/>
-      <c r="D1905" s="3"/>
-      <c r="E1905" s="3"/>
-      <c r="F1905" s="5">
+      <c r="C1905" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="D1905" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1905" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="F1905" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38878,10 +39178,16 @@
       <c r="B1906" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1906" s="3"/>
-      <c r="D1906" s="3"/>
-      <c r="E1906" s="3"/>
-      <c r="F1906" s="5">
+      <c r="C1906" s="3">
+        <v>57.31</v>
+      </c>
+      <c r="D1906" s="3">
+        <v>57.58</v>
+      </c>
+      <c r="E1906" s="3">
+        <v>57.16</v>
+      </c>
+      <c r="F1906" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38892,10 +39198,16 @@
       <c r="B1907" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1907" s="3"/>
-      <c r="D1907" s="3"/>
-      <c r="E1907" s="3"/>
-      <c r="F1907" s="5">
+      <c r="C1907" s="3">
+        <v>48.03</v>
+      </c>
+      <c r="D1907" s="3">
+        <v>48.24</v>
+      </c>
+      <c r="E1907" s="3">
+        <v>47.73</v>
+      </c>
+      <c r="F1907" s="3">
         <v>47.9</v>
       </c>
     </row>
@@ -38906,10 +39218,16 @@
       <c r="B1908" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1908" s="3"/>
-      <c r="D1908" s="3"/>
-      <c r="E1908" s="3"/>
-      <c r="F1908" s="5">
+      <c r="C1908" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="D1908" s="3">
+        <v>42.04</v>
+      </c>
+      <c r="E1908" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="F1908" s="3">
         <v>41.6</v>
       </c>
     </row>
@@ -38920,10 +39238,16 @@
       <c r="B1909" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1909" s="3"/>
-      <c r="D1909" s="3"/>
-      <c r="E1909" s="3"/>
-      <c r="F1909" s="5">
+      <c r="C1909" s="3">
+        <v>41.22</v>
+      </c>
+      <c r="D1909" s="3">
+        <v>41.42</v>
+      </c>
+      <c r="E1909" s="3">
+        <v>41.13</v>
+      </c>
+      <c r="F1909" s="3">
         <v>41.2</v>
       </c>
     </row>
@@ -38934,10 +39258,16 @@
       <c r="B1910" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1910" s="3"/>
-      <c r="D1910" s="3"/>
-      <c r="E1910" s="3"/>
-      <c r="F1910" s="5">
+      <c r="C1910" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="D1910" s="3">
+        <v>54.98</v>
+      </c>
+      <c r="E1910" s="3">
+        <v>54.58</v>
+      </c>
+      <c r="F1910" s="3">
         <v>54.8</v>
       </c>
     </row>
@@ -38948,11 +39278,17 @@
       <c r="B1911" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1911" s="3"/>
-      <c r="D1911" s="3"/>
-      <c r="E1911" s="3"/>
-      <c r="F1911" s="5">
-        <v>57.5</v>
+      <c r="C1911" s="3">
+        <v>57.9</v>
+      </c>
+      <c r="D1911" s="3">
+        <v>58.09</v>
+      </c>
+      <c r="E1911" s="3">
+        <v>57.25</v>
+      </c>
+      <c r="F1911" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1912" spans="1:6">
@@ -38962,10 +39298,16 @@
       <c r="B1912" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1912" s="3"/>
-      <c r="D1912" s="2"/>
-      <c r="E1912" s="3"/>
-      <c r="F1912" s="5">
+      <c r="C1912" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D1912" s="3">
+        <v>59.05</v>
+      </c>
+      <c r="E1912" s="3">
+        <v>58.59</v>
+      </c>
+      <c r="F1912" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -38976,10 +39318,16 @@
       <c r="B1913" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1913" s="3"/>
-      <c r="D1913" s="2"/>
-      <c r="E1913" s="3"/>
-      <c r="F1913" s="5">
+      <c r="C1913" s="3">
+        <v>56.85</v>
+      </c>
+      <c r="D1913" s="3">
+        <v>57.22</v>
+      </c>
+      <c r="E1913" s="3">
+        <v>56.76</v>
+      </c>
+      <c r="F1913" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -38990,10 +39338,16 @@
       <c r="B1914" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1914" s="3"/>
-      <c r="D1914" s="2"/>
-      <c r="E1914" s="3"/>
-      <c r="F1914" s="5">
+      <c r="C1914" s="3">
+        <v>48.09</v>
+      </c>
+      <c r="D1914" s="3">
+        <v>48.36</v>
+      </c>
+      <c r="E1914" s="3">
+        <v>47.91</v>
+      </c>
+      <c r="F1914" s="3">
         <v>48.1</v>
       </c>
     </row>
@@ -39004,10 +39358,16 @@
       <c r="B1915" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1915" s="3"/>
-      <c r="D1915" s="2"/>
-      <c r="E1915" s="3"/>
-      <c r="F1915" s="5">
+      <c r="C1915" s="3">
+        <v>41.28</v>
+      </c>
+      <c r="D1915" s="3">
+        <v>41.67</v>
+      </c>
+      <c r="E1915" s="3">
+        <v>41.19</v>
+      </c>
+      <c r="F1915" s="3">
         <v>41.6</v>
       </c>
     </row>
@@ -39018,10 +39378,16 @@
       <c r="B1916" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1916" s="3"/>
-      <c r="D1916" s="2"/>
-      <c r="E1916" s="3"/>
-      <c r="F1916" s="5">
+      <c r="C1916" s="3">
+        <v>41.34</v>
+      </c>
+      <c r="D1916" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="E1916" s="3">
+        <v>41.13</v>
+      </c>
+      <c r="F1916" s="3">
         <v>41.2</v>
       </c>
     </row>
@@ -39032,10 +39398,16 @@
       <c r="B1917" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1917" s="3"/>
-      <c r="D1917" s="2"/>
-      <c r="E1917" s="3"/>
-      <c r="F1917" s="5">
+      <c r="C1917" s="3">
+        <v>54.89</v>
+      </c>
+      <c r="D1917" s="3">
+        <v>54.94</v>
+      </c>
+      <c r="E1917" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="F1917" s="3">
         <v>54.9</v>
       </c>
     </row>
@@ -39046,11 +39418,17 @@
       <c r="B1918" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1918" s="3"/>
-      <c r="D1918" s="2"/>
-      <c r="E1918" s="3"/>
-      <c r="F1918" s="5">
-        <v>57.5</v>
+      <c r="C1918" s="3">
+        <v>57.03</v>
+      </c>
+      <c r="D1918" s="3">
+        <v>57.66</v>
+      </c>
+      <c r="E1918" s="3">
+        <v>56.96</v>
+      </c>
+      <c r="F1918" s="3">
+        <v>57.7</v>
       </c>
     </row>
     <row r="1919" spans="1:6">
@@ -39060,9 +39438,15 @@
       <c r="B1919" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1919" s="3"/>
-      <c r="D1919" s="2"/>
-      <c r="E1919" s="3"/>
+      <c r="C1919" s="3">
+        <v>58.72</v>
+      </c>
+      <c r="D1919" s="3">
+        <v>58.89</v>
+      </c>
+      <c r="E1919" s="3">
+        <v>58.68</v>
+      </c>
       <c r="F1919" s="3">
         <v>58.7</v>
       </c>
@@ -39074,9 +39458,15 @@
       <c r="B1920" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1920" s="3"/>
-      <c r="D1920" s="2"/>
-      <c r="E1920" s="3"/>
+      <c r="C1920" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="D1920" s="3">
+        <v>57.32</v>
+      </c>
+      <c r="E1920" s="3">
+        <v>56.84</v>
+      </c>
       <c r="F1920" s="3">
         <v>57.2</v>
       </c>
@@ -39088,9 +39478,15 @@
       <c r="B1921" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1921" s="3"/>
-      <c r="D1921" s="2"/>
-      <c r="E1921" s="3"/>
+      <c r="C1921" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="D1921" s="3">
+        <v>48.58</v>
+      </c>
+      <c r="E1921" s="3">
+        <v>48.14</v>
+      </c>
       <c r="F1921" s="3">
         <v>48.3</v>
       </c>
@@ -39102,9 +39498,15 @@
       <c r="B1922" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1922" s="3"/>
-      <c r="D1922" s="2"/>
-      <c r="E1922" s="3"/>
+      <c r="C1922" s="3">
+        <v>41.67</v>
+      </c>
+      <c r="D1922" s="3">
+        <v>41.97</v>
+      </c>
+      <c r="E1922" s="3">
+        <v>41.67</v>
+      </c>
       <c r="F1922" s="3">
         <v>41.7</v>
       </c>
@@ -39116,9 +39518,15 @@
       <c r="B1923" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1923" s="3"/>
-      <c r="D1923" s="2"/>
-      <c r="E1923" s="3"/>
+      <c r="C1923" s="3">
+        <v>41.27</v>
+      </c>
+      <c r="D1923" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="E1923" s="3">
+        <v>41.14</v>
+      </c>
       <c r="F1923" s="3">
         <v>41.3</v>
       </c>
@@ -39130,9 +39538,15 @@
       <c r="B1924" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1924" s="3"/>
-      <c r="D1924" s="2"/>
-      <c r="E1924" s="3"/>
+      <c r="C1924" s="3">
+        <v>54.96</v>
+      </c>
+      <c r="D1924" s="3">
+        <v>55.26</v>
+      </c>
+      <c r="E1924" s="3">
+        <v>54.87</v>
+      </c>
       <c r="F1924" s="3">
         <v>55</v>
       </c>
@@ -39144,11 +39558,17 @@
       <c r="B1925" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1925" s="3"/>
-      <c r="D1925" s="2"/>
-      <c r="E1925" s="3"/>
+      <c r="C1925" s="3">
+        <v>57.21</v>
+      </c>
+      <c r="D1925" s="3">
+        <v>57.92</v>
+      </c>
+      <c r="E1925" s="3">
+        <v>57.09</v>
+      </c>
       <c r="F1925" s="3">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="1926" spans="1:6">
@@ -39158,10 +39578,16 @@
       <c r="B1926" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1926" s="3"/>
-      <c r="D1926" s="2"/>
-      <c r="E1926" s="3"/>
-      <c r="F1926" s="5">
+      <c r="C1926" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="D1926" s="3">
+        <v>58.88</v>
+      </c>
+      <c r="E1926" s="3">
+        <v>58.67</v>
+      </c>
+      <c r="F1926" s="3">
         <v>58.7</v>
       </c>
     </row>
@@ -39172,10 +39598,16 @@
       <c r="B1927" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1927" s="3"/>
-      <c r="D1927" s="2"/>
-      <c r="E1927" s="3"/>
-      <c r="F1927" s="5">
+      <c r="C1927" s="3">
+        <v>57.04</v>
+      </c>
+      <c r="D1927" s="3">
+        <v>57.32</v>
+      </c>
+      <c r="E1927" s="3">
+        <v>56.88</v>
+      </c>
+      <c r="F1927" s="3">
         <v>57.2</v>
       </c>
     </row>
@@ -39186,10 +39618,16 @@
       <c r="B1928" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1928" s="3"/>
-      <c r="D1928" s="2"/>
-      <c r="E1928" s="3"/>
-      <c r="F1928" s="5">
+      <c r="C1928" s="3">
+        <v>48.69</v>
+      </c>
+      <c r="D1928" s="3">
+        <v>48.96</v>
+      </c>
+      <c r="E1928" s="3">
+        <v>48.69</v>
+      </c>
+      <c r="F1928" s="3">
         <v>48.8</v>
       </c>
     </row>
@@ -39200,10 +39638,16 @@
       <c r="B1929" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1929" s="3"/>
-      <c r="D1929" s="2"/>
-      <c r="E1929" s="3"/>
-      <c r="F1929" s="5">
+      <c r="C1929" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="D1929" s="3">
+        <v>41.8</v>
+      </c>
+      <c r="E1929" s="3">
+        <v>41.63</v>
+      </c>
+      <c r="F1929" s="3">
         <v>41.7</v>
       </c>
     </row>
@@ -39214,10 +39658,16 @@
       <c r="B1930" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1930" s="3"/>
-      <c r="D1930" s="2"/>
-      <c r="E1930" s="3"/>
-      <c r="F1930" s="5">
+      <c r="C1930" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="D1930" s="3">
+        <v>41.57</v>
+      </c>
+      <c r="E1930" s="3">
+        <v>41.36</v>
+      </c>
+      <c r="F1930" s="3">
         <v>41.4</v>
       </c>
     </row>
@@ -39228,10 +39678,16 @@
       <c r="B1931" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1931" s="3"/>
-      <c r="D1931" s="2"/>
-      <c r="E1931" s="3"/>
-      <c r="F1931" s="5">
+      <c r="C1931" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="D1931" s="3">
+        <v>55.3</v>
+      </c>
+      <c r="E1931" s="3">
+        <v>54.59</v>
+      </c>
+      <c r="F1931" s="3">
         <v>55</v>
       </c>
     </row>
@@ -39242,11 +39698,4413 @@
       <c r="B1932" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1932" s="3"/>
-      <c r="D1932" s="2"/>
-      <c r="E1932" s="3"/>
-      <c r="F1932" s="5">
+      <c r="C1932" s="3">
+        <v>57.95</v>
+      </c>
+      <c r="D1932" s="3">
+        <v>58.13</v>
+      </c>
+      <c r="E1932" s="3">
+        <v>57.16</v>
+      </c>
+      <c r="F1932" s="3">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:6">
+      <c r="A1933" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1933" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1933" s="3">
+        <v>58.55</v>
+      </c>
+      <c r="D1933" s="3">
+        <v>59.12</v>
+      </c>
+      <c r="E1933" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="F1933" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:6">
+      <c r="A1934" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1934" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1934" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="D1934" s="3">
+        <v>57.24</v>
+      </c>
+      <c r="E1934" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F1934" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:6">
+      <c r="A1935" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1935" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1935" s="3">
+        <v>49.4</v>
+      </c>
+      <c r="D1935" s="3">
+        <v>49.7</v>
+      </c>
+      <c r="E1935" s="3">
+        <v>49.22</v>
+      </c>
+      <c r="F1935" s="3">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:6">
+      <c r="A1936" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1936" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1936" s="3">
+        <v>41.47</v>
+      </c>
+      <c r="D1936" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="E1936" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="F1936" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:6">
+      <c r="A1937" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1937" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1937" s="3">
+        <v>41.22</v>
+      </c>
+      <c r="D1937" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="E1937" s="3">
+        <v>41.1</v>
+      </c>
+      <c r="F1937" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:6">
+      <c r="A1938" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1938" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1938" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="D1938" s="3">
+        <v>55.05</v>
+      </c>
+      <c r="E1938" s="3">
+        <v>54.57</v>
+      </c>
+      <c r="F1938" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:6">
+      <c r="A1939" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B1939" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1939" s="3">
+        <v>57.3</v>
+      </c>
+      <c r="D1939" s="3">
+        <v>57.82</v>
+      </c>
+      <c r="E1939" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="F1939" s="3">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:6">
+      <c r="A1940" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1940" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1940" s="3">
+        <v>58.82</v>
+      </c>
+      <c r="D1940" s="3">
+        <v>58.86</v>
+      </c>
+      <c r="E1940" s="3">
+        <v>58.63</v>
+      </c>
+      <c r="F1940" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:6">
+      <c r="A1941" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1941" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1941" s="3">
+        <v>57.13</v>
+      </c>
+      <c r="D1941" s="3">
+        <v>57.25</v>
+      </c>
+      <c r="E1941" s="3">
+        <v>56.99</v>
+      </c>
+      <c r="F1941" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:6">
+      <c r="A1942" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1942" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1942" s="3">
+        <v>49.63</v>
+      </c>
+      <c r="D1942" s="3">
+        <v>49.82</v>
+      </c>
+      <c r="E1942" s="3">
+        <v>49.37</v>
+      </c>
+      <c r="F1942" s="3">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:6">
+      <c r="A1943" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1943" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1943" s="3">
+        <v>41.42</v>
+      </c>
+      <c r="D1943" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E1943" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="F1943" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:6">
+      <c r="A1944" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1944" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1944" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="D1944" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="E1944" s="3">
+        <v>41.31</v>
+      </c>
+      <c r="F1944" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:6">
+      <c r="A1945" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1945" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1945" s="3">
+        <v>55.42</v>
+      </c>
+      <c r="D1945" s="3">
+        <v>55.49</v>
+      </c>
+      <c r="E1945" s="3">
+        <v>54.73</v>
+      </c>
+      <c r="F1945" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:6">
+      <c r="A1946" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B1946" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1946" s="3">
+        <v>57.57</v>
+      </c>
+      <c r="D1946" s="3">
+        <v>57.88</v>
+      </c>
+      <c r="E1946" s="3">
+        <v>57.4</v>
+      </c>
+      <c r="F1946" s="3">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:6">
+      <c r="A1947" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1947" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1947" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="D1947" s="3">
+        <v>59.08</v>
+      </c>
+      <c r="E1947" s="3">
+        <v>58.01</v>
+      </c>
+      <c r="F1947" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:6">
+      <c r="A1948" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1948" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1948" s="3">
+        <v>56.67</v>
+      </c>
+      <c r="D1948" s="3">
+        <v>57.59</v>
+      </c>
+      <c r="E1948" s="3">
+        <v>56.59</v>
+      </c>
+      <c r="F1948" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:6">
+      <c r="A1949" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1949" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1949" s="3">
+        <v>49.26</v>
+      </c>
+      <c r="D1949" s="3">
+        <v>49.44</v>
+      </c>
+      <c r="E1949" s="3">
+        <v>49.05</v>
+      </c>
+      <c r="F1949" s="3">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:6">
+      <c r="A1950" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1950" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1950" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="D1950" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E1950" s="3">
+        <v>41.45</v>
+      </c>
+      <c r="F1950" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:6">
+      <c r="A1951" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1951" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1951" s="3">
+        <v>41.74</v>
+      </c>
+      <c r="D1951" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="E1951" s="3">
+        <v>41.36</v>
+      </c>
+      <c r="F1951" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:6">
+      <c r="A1952" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1952" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1952" s="3">
+        <v>55.35</v>
+      </c>
+      <c r="D1952" s="3">
+        <v>55.5</v>
+      </c>
+      <c r="E1952" s="3">
+        <v>54.78</v>
+      </c>
+      <c r="F1952" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:6">
+      <c r="A1953" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B1953" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1953" s="3">
+        <v>57.13</v>
+      </c>
+      <c r="D1953" s="3">
+        <v>57.76</v>
+      </c>
+      <c r="E1953" s="3">
+        <v>57.06</v>
+      </c>
+      <c r="F1953" s="3">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:6">
+      <c r="A1954" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1954" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1954" s="3">
+        <v>58.94</v>
+      </c>
+      <c r="D1954" s="3">
+        <v>58.95</v>
+      </c>
+      <c r="E1954" s="3">
+        <v>58.27</v>
+      </c>
+      <c r="F1954" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:6">
+      <c r="A1955" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1955" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1955" s="3">
+        <v>57.39</v>
+      </c>
+      <c r="D1955" s="3">
+        <v>57.48</v>
+      </c>
+      <c r="E1955" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="F1955" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:6">
+      <c r="A1956" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1956" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1956" s="3">
+        <v>49.52</v>
+      </c>
+      <c r="D1956" s="3">
+        <v>49.6</v>
+      </c>
+      <c r="E1956" s="3">
+        <v>49.38</v>
+      </c>
+      <c r="F1956" s="3">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:6">
+      <c r="A1957" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1957" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1957" s="3">
+        <v>41.44</v>
+      </c>
+      <c r="D1957" s="3">
+        <v>41.98</v>
+      </c>
+      <c r="E1957" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="F1957" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:6">
+      <c r="A1958" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1958" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1958" s="3">
+        <v>41.39</v>
+      </c>
+      <c r="D1958" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="E1958" s="3">
+        <v>41.34</v>
+      </c>
+      <c r="F1958" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:6">
+      <c r="A1959" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1959" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1959" s="3">
+        <v>54.72</v>
+      </c>
+      <c r="D1959" s="3">
+        <v>55.04</v>
+      </c>
+      <c r="E1959" s="3">
+        <v>54.47</v>
+      </c>
+      <c r="F1959" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:6">
+      <c r="A1960" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B1960" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1960" s="3">
+        <v>57.51</v>
+      </c>
+      <c r="D1960" s="3">
+        <v>57.79</v>
+      </c>
+      <c r="E1960" s="3">
+        <v>57.33</v>
+      </c>
+      <c r="F1960" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:6">
+      <c r="A1961" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1961" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1961" s="3">
+        <v>59.09</v>
+      </c>
+      <c r="D1961" s="3">
+        <v>59.15</v>
+      </c>
+      <c r="E1961" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="F1961" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:6">
+      <c r="A1962" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1962" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1962" s="3">
+        <v>57.25</v>
+      </c>
+      <c r="D1962" s="3">
+        <v>57.31</v>
+      </c>
+      <c r="E1962" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F1962" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:6">
+      <c r="A1963" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1963" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1963" s="3">
+        <v>49.66</v>
+      </c>
+      <c r="D1963" s="3">
+        <v>49.82</v>
+      </c>
+      <c r="E1963" s="3">
+        <v>49.48</v>
+      </c>
+      <c r="F1963" s="3">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:6">
+      <c r="A1964" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1964" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1964" s="3">
+        <v>41.96</v>
+      </c>
+      <c r="D1964" s="3">
+        <v>42.14</v>
+      </c>
+      <c r="E1964" s="3">
+        <v>41.6</v>
+      </c>
+      <c r="F1964" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:6">
+      <c r="A1965" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1965" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1965" s="3">
+        <v>41.54</v>
+      </c>
+      <c r="D1965" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="E1965" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="F1965" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:6">
+      <c r="A1966" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1966" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1966" s="3">
+        <v>54.94</v>
+      </c>
+      <c r="D1966" s="3">
+        <v>55.11</v>
+      </c>
+      <c r="E1966" s="3">
+        <v>54.76</v>
+      </c>
+      <c r="F1966" s="3">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:6">
+      <c r="A1967" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B1967" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1967" s="3">
+        <v>57.95</v>
+      </c>
+      <c r="D1967" s="3">
+        <v>58.13</v>
+      </c>
+      <c r="E1967" s="3">
+        <v>57.16</v>
+      </c>
+      <c r="F1967" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:6">
+      <c r="A1968" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1968" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1968" s="3">
+        <v>58.33</v>
+      </c>
+      <c r="D1968" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1968" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="F1968" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:6">
+      <c r="A1969" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1969" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1969" s="3">
+        <v>57.51</v>
+      </c>
+      <c r="D1969" s="3">
+        <v>57.78</v>
+      </c>
+      <c r="E1969" s="3">
+        <v>56.82</v>
+      </c>
+      <c r="F1969" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:6">
+      <c r="A1970" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1970" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1970" s="3">
+        <v>49.84</v>
+      </c>
+      <c r="D1970" s="3">
+        <v>50.06</v>
+      </c>
+      <c r="E1970" s="3">
+        <v>49.52</v>
+      </c>
+      <c r="F1970" s="3">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:6">
+      <c r="A1971" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1971" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1971" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="D1971" s="3">
+        <v>41.77</v>
+      </c>
+      <c r="E1971" s="3">
+        <v>41.29</v>
+      </c>
+      <c r="F1971" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:6">
+      <c r="A1972" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1972" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1972" s="3">
+        <v>41.59</v>
+      </c>
+      <c r="D1972" s="3">
+        <v>41.67</v>
+      </c>
+      <c r="E1972" s="3">
+        <v>41.2</v>
+      </c>
+      <c r="F1972" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:6">
+      <c r="A1973" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1973" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1973" s="3">
+        <v>54.73</v>
+      </c>
+      <c r="D1973" s="3">
+        <v>55.2</v>
+      </c>
+      <c r="E1973" s="3">
+        <v>54.49</v>
+      </c>
+      <c r="F1973" s="3">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:6">
+      <c r="A1974" s="2">
+        <v>45985</v>
+      </c>
+      <c r="B1974" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1974" s="3">
         <v>57.5</v>
+      </c>
+      <c r="D1974" s="3">
+        <v>57.67</v>
+      </c>
+      <c r="E1974" s="3">
+        <v>57.29</v>
+      </c>
+      <c r="F1974" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:6">
+      <c r="A1975" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1975" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1975" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="D1975" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1975" s="3">
+        <v>58.44</v>
+      </c>
+      <c r="F1975" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:6">
+      <c r="A1976" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1976" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1976" s="3">
+        <v>57.31</v>
+      </c>
+      <c r="D1976" s="3">
+        <v>57.58</v>
+      </c>
+      <c r="E1976" s="3">
+        <v>57.16</v>
+      </c>
+      <c r="F1976" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:6">
+      <c r="A1977" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1977" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1977" s="3">
+        <v>49.41</v>
+      </c>
+      <c r="D1977" s="3">
+        <v>49.59</v>
+      </c>
+      <c r="E1977" s="3">
+        <v>49.12</v>
+      </c>
+      <c r="F1977" s="3">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:6">
+      <c r="A1978" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1978" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1978" s="3">
+        <v>41.97</v>
+      </c>
+      <c r="D1978" s="3">
+        <v>42.15</v>
+      </c>
+      <c r="E1978" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="F1978" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:6">
+      <c r="A1979" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1979" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1979" s="3">
+        <v>41.51</v>
+      </c>
+      <c r="D1979" s="3">
+        <v>41.62</v>
+      </c>
+      <c r="E1979" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="F1979" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:6">
+      <c r="A1980" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1980" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1980" s="3">
+        <v>55.33</v>
+      </c>
+      <c r="D1980" s="3">
+        <v>55.54</v>
+      </c>
+      <c r="E1980" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="F1980" s="3">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:6">
+      <c r="A1981" s="2">
+        <v>45986</v>
+      </c>
+      <c r="B1981" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1981" s="3">
+        <v>57.15</v>
+      </c>
+      <c r="D1981" s="3">
+        <v>57.81</v>
+      </c>
+      <c r="E1981" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="F1981" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:6">
+      <c r="A1982" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1982" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1982" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="D1982" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E1982" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="F1982" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:6">
+      <c r="A1983" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1983" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1983" s="3">
+        <v>56.85</v>
+      </c>
+      <c r="D1983" s="3">
+        <v>57.22</v>
+      </c>
+      <c r="E1983" s="3">
+        <v>56.76</v>
+      </c>
+      <c r="F1983" s="3">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:6">
+      <c r="A1984" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1984" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1984" s="3">
+        <v>49.17</v>
+      </c>
+      <c r="D1984" s="3">
+        <v>49.36</v>
+      </c>
+      <c r="E1984" s="3">
+        <v>48.92</v>
+      </c>
+      <c r="F1984" s="3">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:6">
+      <c r="A1985" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1985" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1985" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="D1985" s="3">
+        <v>41.8</v>
+      </c>
+      <c r="E1985" s="3">
+        <v>41.63</v>
+      </c>
+      <c r="F1985" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:6">
+      <c r="A1986" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1986" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1986" s="3">
+        <v>41.68</v>
+      </c>
+      <c r="D1986" s="3">
+        <v>41.74</v>
+      </c>
+      <c r="E1986" s="3">
+        <v>41.34</v>
+      </c>
+      <c r="F1986" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:6">
+      <c r="A1987" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1987" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1987" s="3">
+        <v>54.44</v>
+      </c>
+      <c r="D1987" s="3">
+        <v>54.97</v>
+      </c>
+      <c r="E1987" s="3">
+        <v>54.2</v>
+      </c>
+      <c r="F1987" s="3">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:6">
+      <c r="A1988" s="2">
+        <v>45987</v>
+      </c>
+      <c r="B1988" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1988" s="3">
+        <v>56.95</v>
+      </c>
+      <c r="D1988" s="3">
+        <v>57.78</v>
+      </c>
+      <c r="E1988" s="3">
+        <v>56.9</v>
+      </c>
+      <c r="F1988" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:6">
+      <c r="A1989" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1989" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1989" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D1989" s="3">
+        <v>59.05</v>
+      </c>
+      <c r="E1989" s="3">
+        <v>58.59</v>
+      </c>
+      <c r="F1989" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:6">
+      <c r="A1990" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1990" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1990" s="3">
+        <v>57.12</v>
+      </c>
+      <c r="D1990" s="3">
+        <v>57.19</v>
+      </c>
+      <c r="E1990" s="3">
+        <v>56.75</v>
+      </c>
+      <c r="F1990" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:6">
+      <c r="A1991" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1991" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1991" s="3">
+        <v>49.12</v>
+      </c>
+      <c r="D1991" s="3">
+        <v>49.23</v>
+      </c>
+      <c r="E1991" s="3">
+        <v>49.09</v>
+      </c>
+      <c r="F1991" s="3">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:6">
+      <c r="A1992" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1992" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1992" s="3">
+        <v>41.38</v>
+      </c>
+      <c r="D1992" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="E1992" s="3">
+        <v>41.19</v>
+      </c>
+      <c r="F1992" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:6">
+      <c r="A1993" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1993" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1993" s="3">
+        <v>41.02</v>
+      </c>
+      <c r="D1993" s="3">
+        <v>41.58</v>
+      </c>
+      <c r="E1993" s="3">
+        <v>40.88</v>
+      </c>
+      <c r="F1993" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:6">
+      <c r="A1994" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1994" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1994" s="3">
+        <v>54.82</v>
+      </c>
+      <c r="D1994" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="E1994" s="3">
+        <v>54.76</v>
+      </c>
+      <c r="F1994" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:6">
+      <c r="A1995" s="2">
+        <v>45988</v>
+      </c>
+      <c r="B1995" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1995" s="3">
+        <v>58.01</v>
+      </c>
+      <c r="D1995" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="E1995" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="F1995" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:6">
+      <c r="A1996" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B1996" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1996" s="3">
+        <v>58.72</v>
+      </c>
+      <c r="D1996" s="3">
+        <v>58.89</v>
+      </c>
+      <c r="E1996" s="3">
+        <v>58.68</v>
+      </c>
+      <c r="F1996" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:6">
+      <c r="A1997" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B1997" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1997" s="3">
+        <v>56.94</v>
+      </c>
+      <c r="D1997" s="3">
+        <v>57.22</v>
+      </c>
+      <c r="E1997" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F1997" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:6">
+      <c r="A1998" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B1998" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1998" s="3">
+        <v>48.91</v>
+      </c>
+      <c r="D1998" s="3">
+        <v>48.92</v>
+      </c>
+      <c r="E1998" s="3">
+        <v>48.67</v>
+      </c>
+      <c r="F1998" s="3">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:6">
+      <c r="A1999" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B1999" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1999" s="3">
+        <v>41.55</v>
+      </c>
+      <c r="D1999" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="E1999" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="F1999" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:6">
+      <c r="A2000" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B2000" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2000" s="3">
+        <v>41</v>
+      </c>
+      <c r="D2000" s="3">
+        <v>41.56</v>
+      </c>
+      <c r="E2000" s="3">
+        <v>40.95</v>
+      </c>
+      <c r="F2000" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:6">
+      <c r="A2001" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B2001" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2001" s="3">
+        <v>54.98</v>
+      </c>
+      <c r="D2001" s="3">
+        <v>54.98</v>
+      </c>
+      <c r="E2001" s="3">
+        <v>54.73</v>
+      </c>
+      <c r="F2001" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:6">
+      <c r="A2002" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B2002" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2002" s="3">
+        <v>57.35</v>
+      </c>
+      <c r="D2002" s="3">
+        <v>57.51</v>
+      </c>
+      <c r="E2002" s="3">
+        <v>57.08</v>
+      </c>
+      <c r="F2002" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:6">
+      <c r="A2003" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2003" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2003" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="D2003" s="3">
+        <v>58.88</v>
+      </c>
+      <c r="E2003" s="3">
+        <v>58.67</v>
+      </c>
+      <c r="F2003" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:6">
+      <c r="A2004" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2004" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2004" s="3">
+        <v>56.69</v>
+      </c>
+      <c r="D2004" s="3">
+        <v>57.44</v>
+      </c>
+      <c r="E2004" s="3">
+        <v>56.67</v>
+      </c>
+      <c r="F2004" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:6">
+      <c r="A2005" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2005" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2005" s="3">
+        <v>48.73</v>
+      </c>
+      <c r="D2005" s="3">
+        <v>48.85</v>
+      </c>
+      <c r="E2005" s="3">
+        <v>48.37</v>
+      </c>
+      <c r="F2005" s="3">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:6">
+      <c r="A2006" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2006" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2006" s="3">
+        <v>41.59</v>
+      </c>
+      <c r="D2006" s="3">
+        <v>42</v>
+      </c>
+      <c r="E2006" s="3">
+        <v>41.39</v>
+      </c>
+      <c r="F2006" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:6">
+      <c r="A2007" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2007" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2007" s="3">
+        <v>41.52</v>
+      </c>
+      <c r="D2007" s="3">
+        <v>41.56</v>
+      </c>
+      <c r="E2007" s="3">
+        <v>41.19</v>
+      </c>
+      <c r="F2007" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:6">
+      <c r="A2008" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2008" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2008" s="3">
+        <v>54.85</v>
+      </c>
+      <c r="D2008" s="3">
+        <v>55.04</v>
+      </c>
+      <c r="E2008" s="3">
+        <v>54.53</v>
+      </c>
+      <c r="F2008" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:6">
+      <c r="A2009" s="2">
+        <v>45990</v>
+      </c>
+      <c r="B2009" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2009" s="3">
+        <v>57.42</v>
+      </c>
+      <c r="D2009" s="3">
+        <v>57.92</v>
+      </c>
+      <c r="E2009" s="3">
+        <v>57.14</v>
+      </c>
+      <c r="F2009" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:6">
+      <c r="A2010" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2010" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2010" s="3">
+        <v>59.23</v>
+      </c>
+      <c r="D2010" s="3">
+        <v>59.51</v>
+      </c>
+      <c r="E2010" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="F2010" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:6">
+      <c r="A2011" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2011" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2011" s="3">
+        <v>57.66</v>
+      </c>
+      <c r="D2011" s="3">
+        <v>57.88</v>
+      </c>
+      <c r="E2011" s="3">
+        <v>57.01</v>
+      </c>
+      <c r="F2011" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:6">
+      <c r="A2012" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2012" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2012" s="3">
+        <v>48.61</v>
+      </c>
+      <c r="D2012" s="3">
+        <v>48.71</v>
+      </c>
+      <c r="E2012" s="3">
+        <v>48.32</v>
+      </c>
+      <c r="F2012" s="3">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:6">
+      <c r="A2013" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2013" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2013" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="D2013" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="E2013" s="3">
+        <v>41.43</v>
+      </c>
+      <c r="F2013" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:6">
+      <c r="A2014" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2014" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2014" s="3">
+        <v>41.31</v>
+      </c>
+      <c r="D2014" s="3">
+        <v>41.69</v>
+      </c>
+      <c r="E2014" s="3">
+        <v>41.28</v>
+      </c>
+      <c r="F2014" s="3">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:6">
+      <c r="A2015" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2015" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2015" s="3">
+        <v>54.5</v>
+      </c>
+      <c r="D2015" s="3">
+        <v>55.09</v>
+      </c>
+      <c r="E2015" s="3">
+        <v>54.43</v>
+      </c>
+      <c r="F2015" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:6">
+      <c r="A2016" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B2016" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2016" s="3">
+        <v>57.91</v>
+      </c>
+      <c r="D2016" s="3">
+        <v>57.99</v>
+      </c>
+      <c r="E2016" s="3">
+        <v>57.33</v>
+      </c>
+      <c r="F2016" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:6">
+      <c r="A2017" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2017" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2017" s="3">
+        <v>58.55</v>
+      </c>
+      <c r="D2017" s="3">
+        <v>59.12</v>
+      </c>
+      <c r="E2017" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="F2017" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:6">
+      <c r="A2018" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2018" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2018" s="3">
+        <v>57.61</v>
+      </c>
+      <c r="D2018" s="3">
+        <v>57.89</v>
+      </c>
+      <c r="E2018" s="3">
+        <v>56.75</v>
+      </c>
+      <c r="F2018" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:6">
+      <c r="A2019" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2019" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2019" s="3">
+        <v>48.41</v>
+      </c>
+      <c r="D2019" s="3">
+        <v>48.61</v>
+      </c>
+      <c r="E2019" s="3">
+        <v>48.37</v>
+      </c>
+      <c r="F2019" s="3">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:6">
+      <c r="A2020" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2020" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2020" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="D2020" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="E2020" s="3">
+        <v>41.24</v>
+      </c>
+      <c r="F2020" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:6">
+      <c r="A2021" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2021" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2021" s="3">
+        <v>41.21</v>
+      </c>
+      <c r="D2021" s="3">
+        <v>41.28</v>
+      </c>
+      <c r="E2021" s="3">
+        <v>40.91</v>
+      </c>
+      <c r="F2021" s="3">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:6">
+      <c r="A2022" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2022" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2022" s="3">
+        <v>55.17</v>
+      </c>
+      <c r="D2022" s="3">
+        <v>55.26</v>
+      </c>
+      <c r="E2022" s="3">
+        <v>54.72</v>
+      </c>
+      <c r="F2022" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:6">
+      <c r="A2023" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2023" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2023" s="3">
+        <v>58.06</v>
+      </c>
+      <c r="D2023" s="3">
+        <v>58.44</v>
+      </c>
+      <c r="E2023" s="3">
+        <v>57.88</v>
+      </c>
+      <c r="F2023" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:6">
+      <c r="A2024" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2024" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2024" s="3">
+        <v>58.82</v>
+      </c>
+      <c r="D2024" s="3">
+        <v>58.86</v>
+      </c>
+      <c r="E2024" s="3">
+        <v>58.63</v>
+      </c>
+      <c r="F2024" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:6">
+      <c r="A2025" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2025" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2025" s="3">
+        <v>56.88</v>
+      </c>
+      <c r="D2025" s="3">
+        <v>57.14</v>
+      </c>
+      <c r="E2025" s="3">
+        <v>56.68</v>
+      </c>
+      <c r="F2025" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:6">
+      <c r="A2026" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2026" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2026" s="3">
+        <v>48.28</v>
+      </c>
+      <c r="D2026" s="3">
+        <v>48.47</v>
+      </c>
+      <c r="E2026" s="3">
+        <v>48.13</v>
+      </c>
+      <c r="F2026" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:6">
+      <c r="A2027" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2027" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2027" s="3">
+        <v>41.55</v>
+      </c>
+      <c r="D2027" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="E2027" s="3">
+        <v>41.36</v>
+      </c>
+      <c r="F2027" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:6">
+      <c r="A2028" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2028" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2028" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="D2028" s="3">
+        <v>41.36</v>
+      </c>
+      <c r="E2028" s="3">
+        <v>40.91</v>
+      </c>
+      <c r="F2028" s="3">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:6">
+      <c r="A2029" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2029" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2029" s="3">
+        <v>54.3</v>
+      </c>
+      <c r="D2029" s="3">
+        <v>55.04</v>
+      </c>
+      <c r="E2029" s="3">
+        <v>54.11</v>
+      </c>
+      <c r="F2029" s="3">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:6">
+      <c r="A2030" s="2">
+        <v>45993</v>
+      </c>
+      <c r="B2030" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2030" s="3">
+        <v>57.62</v>
+      </c>
+      <c r="D2030" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="E2030" s="3">
+        <v>57.36</v>
+      </c>
+      <c r="F2030" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:6">
+      <c r="A2031" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2031" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2031" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="D2031" s="3">
+        <v>59.08</v>
+      </c>
+      <c r="E2031" s="3">
+        <v>58.01</v>
+      </c>
+      <c r="F2031" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:6">
+      <c r="A2032" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2032" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2032" s="3">
+        <v>57.03</v>
+      </c>
+      <c r="D2032" s="3">
+        <v>57.15</v>
+      </c>
+      <c r="E2032" s="3">
+        <v>56.89</v>
+      </c>
+      <c r="F2032" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:6">
+      <c r="A2033" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2033" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2033" s="3">
+        <v>47.72</v>
+      </c>
+      <c r="D2033" s="3">
+        <v>48.49</v>
+      </c>
+      <c r="E2033" s="3">
+        <v>47.55</v>
+      </c>
+      <c r="F2033" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:6">
+      <c r="A2034" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2034" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2034" s="3">
+        <v>41.49</v>
+      </c>
+      <c r="D2034" s="3">
+        <v>41.83</v>
+      </c>
+      <c r="E2034" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="F2034" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:6">
+      <c r="A2035" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2035" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2035" s="3">
+        <v>41.09</v>
+      </c>
+      <c r="D2035" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="E2035" s="3">
+        <v>40.89</v>
+      </c>
+      <c r="F2035" s="3">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:6">
+      <c r="A2036" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2036" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2036" s="3">
+        <v>54.7</v>
+      </c>
+      <c r="D2036" s="3">
+        <v>54.84</v>
+      </c>
+      <c r="E2036" s="3">
+        <v>54.61</v>
+      </c>
+      <c r="F2036" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:6">
+      <c r="A2037" s="2">
+        <v>45994</v>
+      </c>
+      <c r="B2037" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2037" s="3">
+        <v>58.22</v>
+      </c>
+      <c r="D2037" s="3">
+        <v>58.23</v>
+      </c>
+      <c r="E2037" s="3">
+        <v>58.06</v>
+      </c>
+      <c r="F2037" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:6">
+      <c r="A2038" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2038" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2038" s="3">
+        <v>58.94</v>
+      </c>
+      <c r="D2038" s="3">
+        <v>58.95</v>
+      </c>
+      <c r="E2038" s="3">
+        <v>58.27</v>
+      </c>
+      <c r="F2038" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:6">
+      <c r="A2039" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2039" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2039" s="3">
+        <v>56.57</v>
+      </c>
+      <c r="D2039" s="3">
+        <v>57.49</v>
+      </c>
+      <c r="E2039" s="3">
+        <v>56.5</v>
+      </c>
+      <c r="F2039" s="3">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:6">
+      <c r="A2040" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2040" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2040" s="3">
+        <v>48.42</v>
+      </c>
+      <c r="D2040" s="3">
+        <v>48.61</v>
+      </c>
+      <c r="E2040" s="3">
+        <v>48.17</v>
+      </c>
+      <c r="F2040" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:6">
+      <c r="A2041" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2041" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2041" s="3">
+        <v>41.47</v>
+      </c>
+      <c r="D2041" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="E2041" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="F2041" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:6">
+      <c r="A2042" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2042" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2042" s="3">
+        <v>41.02</v>
+      </c>
+      <c r="D2042" s="3">
+        <v>41.12</v>
+      </c>
+      <c r="E2042" s="3">
+        <v>40.91</v>
+      </c>
+      <c r="F2042" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:6">
+      <c r="A2043" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2043" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2043" s="3">
+        <v>54.86</v>
+      </c>
+      <c r="D2043" s="3">
+        <v>54.91</v>
+      </c>
+      <c r="E2043" s="3">
+        <v>54.42</v>
+      </c>
+      <c r="F2043" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:6">
+      <c r="A2044" s="2">
+        <v>45995</v>
+      </c>
+      <c r="B2044" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2044" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="D2044" s="3">
+        <v>58.2</v>
+      </c>
+      <c r="E2044" s="3">
+        <v>58.13</v>
+      </c>
+      <c r="F2044" s="3">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:6">
+      <c r="A2045" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2045" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2045" s="3">
+        <v>59.09</v>
+      </c>
+      <c r="D2045" s="3">
+        <v>59.15</v>
+      </c>
+      <c r="E2045" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="F2045" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:6">
+      <c r="A2046" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2046" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2046" s="3">
+        <v>57.03</v>
+      </c>
+      <c r="D2046" s="3">
+        <v>57.12</v>
+      </c>
+      <c r="E2046" s="3">
+        <v>56.78</v>
+      </c>
+      <c r="F2046" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:6">
+      <c r="A2047" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2047" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2047" s="3">
+        <v>48.06</v>
+      </c>
+      <c r="D2047" s="3">
+        <v>48.24</v>
+      </c>
+      <c r="E2047" s="3">
+        <v>47.86</v>
+      </c>
+      <c r="F2047" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:6">
+      <c r="A2048" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2048" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2048" s="3">
+        <v>41.42</v>
+      </c>
+      <c r="D2048" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E2048" s="3">
+        <v>41.25</v>
+      </c>
+      <c r="F2048" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:6">
+      <c r="A2049" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2049" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2049" s="3">
+        <v>40.82</v>
+      </c>
+      <c r="D2049" s="3">
+        <v>41.01</v>
+      </c>
+      <c r="E2049" s="3">
+        <v>40.7</v>
+      </c>
+      <c r="F2049" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:6">
+      <c r="A2050" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2050" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2050" s="3">
+        <v>54.58</v>
+      </c>
+      <c r="D2050" s="3">
+        <v>55.08</v>
+      </c>
+      <c r="E2050" s="3">
+        <v>54.54</v>
+      </c>
+      <c r="F2050" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:6">
+      <c r="A2051" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B2051" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2051" s="3">
+        <v>58.26</v>
+      </c>
+      <c r="D2051" s="3">
+        <v>58.46</v>
+      </c>
+      <c r="E2051" s="3">
+        <v>57.92</v>
+      </c>
+      <c r="F2051" s="3">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:6">
+      <c r="A2052" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2052" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2052" s="3">
+        <v>58.33</v>
+      </c>
+      <c r="D2052" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2052" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="F2052" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:6">
+      <c r="A2053" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2053" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2053" s="3">
+        <v>57.05</v>
+      </c>
+      <c r="D2053" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="E2053" s="3">
+        <v>56.59</v>
+      </c>
+      <c r="F2053" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:6">
+      <c r="A2054" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2054" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2054" s="3">
+        <v>48.32</v>
+      </c>
+      <c r="D2054" s="3">
+        <v>48.4</v>
+      </c>
+      <c r="E2054" s="3">
+        <v>48.18</v>
+      </c>
+      <c r="F2054" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:6">
+      <c r="A2055" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2055" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2055" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="D2055" s="3">
+        <v>41.99</v>
+      </c>
+      <c r="E2055" s="3">
+        <v>41.45</v>
+      </c>
+      <c r="F2055" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:6">
+      <c r="A2056" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2056" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2056" s="3">
+        <v>41</v>
+      </c>
+      <c r="D2056" s="3">
+        <v>41.01</v>
+      </c>
+      <c r="E2056" s="3">
+        <v>40.91</v>
+      </c>
+      <c r="F2056" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:6">
+      <c r="A2057" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2057" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2057" s="3">
+        <v>54.53</v>
+      </c>
+      <c r="D2057" s="3">
+        <v>54.75</v>
+      </c>
+      <c r="E2057" s="3">
+        <v>54.27</v>
+      </c>
+      <c r="F2057" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:6">
+      <c r="A2058" s="2">
+        <v>45999</v>
+      </c>
+      <c r="B2058" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2058" s="3">
+        <v>57.88</v>
+      </c>
+      <c r="D2058" s="3">
+        <v>58.51</v>
+      </c>
+      <c r="E2058" s="3">
+        <v>57.81</v>
+      </c>
+      <c r="F2058" s="3">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:6">
+      <c r="A2059" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2059" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2059" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="D2059" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2059" s="3">
+        <v>58.44</v>
+      </c>
+      <c r="F2059" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:6">
+      <c r="A2060" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2060" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2060" s="3">
+        <v>57.31</v>
+      </c>
+      <c r="D2060" s="3">
+        <v>57.58</v>
+      </c>
+      <c r="E2060" s="3">
+        <v>56.62</v>
+      </c>
+      <c r="F2060" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:6">
+      <c r="A2061" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2061" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2061" s="3">
+        <v>48.02</v>
+      </c>
+      <c r="D2061" s="3">
+        <v>48.32</v>
+      </c>
+      <c r="E2061" s="3">
+        <v>47.84</v>
+      </c>
+      <c r="F2061" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:6">
+      <c r="A2062" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2062" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2062" s="3">
+        <v>41.44</v>
+      </c>
+      <c r="D2062" s="3">
+        <v>41.98</v>
+      </c>
+      <c r="E2062" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="F2062" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:6">
+      <c r="A2063" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2063" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2063" s="3">
+        <v>41.33</v>
+      </c>
+      <c r="D2063" s="3">
+        <v>41.38</v>
+      </c>
+      <c r="E2063" s="3">
+        <v>40.96</v>
+      </c>
+      <c r="F2063" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:6">
+      <c r="A2064" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2064" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2064" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="D2064" s="3">
+        <v>54.71</v>
+      </c>
+      <c r="E2064" s="3">
+        <v>54.33</v>
+      </c>
+      <c r="F2064" s="3">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:6">
+      <c r="A2065" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B2065" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2065" s="3">
+        <v>58.29</v>
+      </c>
+      <c r="D2065" s="3">
+        <v>58.63</v>
+      </c>
+      <c r="E2065" s="3">
+        <v>58.1</v>
+      </c>
+      <c r="F2065" s="3">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:6">
+      <c r="A2066" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2066" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2066" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="D2066" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2066" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="F2066" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:6">
+      <c r="A2067" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2067" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2067" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="D2067" s="3">
+        <v>57.37</v>
+      </c>
+      <c r="E2067" s="3">
+        <v>56.96</v>
+      </c>
+      <c r="F2067" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:6">
+      <c r="A2068" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2068" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2068" s="3">
+        <v>48.33</v>
+      </c>
+      <c r="D2068" s="3">
+        <v>48.55</v>
+      </c>
+      <c r="E2068" s="3">
+        <v>48.03</v>
+      </c>
+      <c r="F2068" s="3">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:6">
+      <c r="A2069" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2069" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2069" s="3">
+        <v>41.96</v>
+      </c>
+      <c r="D2069" s="3">
+        <v>42.14</v>
+      </c>
+      <c r="E2069" s="3">
+        <v>41.6</v>
+      </c>
+      <c r="F2069" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:6">
+      <c r="A2070" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2070" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2070" s="3">
+        <v>40.84</v>
+      </c>
+      <c r="D2070" s="3">
+        <v>41.04</v>
+      </c>
+      <c r="E2070" s="3">
+        <v>40.73</v>
+      </c>
+      <c r="F2070" s="3">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:6">
+      <c r="A2071" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2071" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2071" s="3">
+        <v>54.95</v>
+      </c>
+      <c r="D2071" s="3">
+        <v>55.1</v>
+      </c>
+      <c r="E2071" s="3">
+        <v>54.38</v>
+      </c>
+      <c r="F2071" s="3">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:6">
+      <c r="A2072" s="2">
+        <v>46001</v>
+      </c>
+      <c r="B2072" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2072" s="3">
+        <v>58.71</v>
+      </c>
+      <c r="D2072" s="3">
+        <v>58.9</v>
+      </c>
+      <c r="E2072" s="3">
+        <v>58.05</v>
+      </c>
+      <c r="F2072" s="3">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:6">
+      <c r="A2073" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2073" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2073" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D2073" s="3">
+        <v>59.05</v>
+      </c>
+      <c r="E2073" s="3">
+        <v>58.59</v>
+      </c>
+      <c r="F2073" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:6">
+      <c r="A2074" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2074" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2074" s="3">
+        <v>56.65</v>
+      </c>
+      <c r="D2074" s="3">
+        <v>57.02</v>
+      </c>
+      <c r="E2074" s="3">
+        <v>56.56</v>
+      </c>
+      <c r="F2074" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:6">
+      <c r="A2075" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2075" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2075" s="3">
+        <v>48.01</v>
+      </c>
+      <c r="D2075" s="3">
+        <v>48.18</v>
+      </c>
+      <c r="E2075" s="3">
+        <v>47.73</v>
+      </c>
+      <c r="F2075" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:6">
+      <c r="A2076" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2076" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2076" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="D2076" s="3">
+        <v>41.77</v>
+      </c>
+      <c r="E2076" s="3">
+        <v>41.29</v>
+      </c>
+      <c r="F2076" s="3">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:6">
+      <c r="A2077" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2077" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2077" s="3">
+        <v>40.73</v>
+      </c>
+      <c r="D2077" s="3">
+        <v>40.88</v>
+      </c>
+      <c r="E2077" s="3">
+        <v>40.63</v>
+      </c>
+      <c r="F2077" s="3">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:6">
+      <c r="A2078" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2078" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2078" s="3">
+        <v>54.32</v>
+      </c>
+      <c r="D2078" s="3">
+        <v>54.64</v>
+      </c>
+      <c r="E2078" s="3">
+        <v>54.07</v>
+      </c>
+      <c r="F2078" s="3">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:6">
+      <c r="A2079" s="2">
+        <v>46002</v>
+      </c>
+      <c r="B2079" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2079" s="3">
+        <v>58.4</v>
+      </c>
+      <c r="D2079" s="3">
+        <v>58.56</v>
+      </c>
+      <c r="E2079" s="3">
+        <v>58.32</v>
+      </c>
+      <c r="F2079" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:6">
+      <c r="A2080" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2080" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2080" s="3">
+        <v>58.72</v>
+      </c>
+      <c r="D2080" s="3">
+        <v>58.89</v>
+      </c>
+      <c r="E2080" s="3">
+        <v>58.68</v>
+      </c>
+      <c r="F2080" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:6">
+      <c r="A2081" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2081" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2081" s="3">
+        <v>56.87</v>
+      </c>
+      <c r="D2081" s="3">
+        <v>57.12</v>
+      </c>
+      <c r="E2081" s="3">
+        <v>56.64</v>
+      </c>
+      <c r="F2081" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:6">
+      <c r="A2082" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2082" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2082" s="3">
+        <v>47.84</v>
+      </c>
+      <c r="D2082" s="3">
+        <v>48.03</v>
+      </c>
+      <c r="E2082" s="3">
+        <v>47.62</v>
+      </c>
+      <c r="F2082" s="3">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:6">
+      <c r="A2083" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2083" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2083" s="3">
+        <v>41.63</v>
+      </c>
+      <c r="D2083" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="E2083" s="3">
+        <v>41.6</v>
+      </c>
+      <c r="F2083" s="3">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:6">
+      <c r="A2084" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2084" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2084" s="3">
+        <v>40.63</v>
+      </c>
+      <c r="D2084" s="3">
+        <v>40.7</v>
+      </c>
+      <c r="E2084" s="3">
+        <v>40.41</v>
+      </c>
+      <c r="F2084" s="3">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:6">
+      <c r="A2085" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2085" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2085" s="3">
+        <v>55.04</v>
+      </c>
+      <c r="D2085" s="3">
+        <v>55.21</v>
+      </c>
+      <c r="E2085" s="3">
+        <v>54.46</v>
+      </c>
+      <c r="F2085" s="3">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:6">
+      <c r="A2086" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B2086" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2086" s="3">
+        <v>58.1</v>
+      </c>
+      <c r="D2086" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2086" s="3">
+        <v>57.99</v>
+      </c>
+      <c r="F2086" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:6">
+      <c r="A2087" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2087" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2087" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="D2087" s="3">
+        <v>58.88</v>
+      </c>
+      <c r="E2087" s="3">
+        <v>58.67</v>
+      </c>
+      <c r="F2087" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:6">
+      <c r="A2088" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2088" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2088" s="3">
+        <v>56.83</v>
+      </c>
+      <c r="D2088" s="3">
+        <v>56.91</v>
+      </c>
+      <c r="E2088" s="3">
+        <v>56.57</v>
+      </c>
+      <c r="F2088" s="3">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:6">
+      <c r="A2089" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2089" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2089" s="3">
+        <v>47.48</v>
+      </c>
+      <c r="D2089" s="3">
+        <v>47.58</v>
+      </c>
+      <c r="E2089" s="3">
+        <v>47.39</v>
+      </c>
+      <c r="F2089" s="3">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:6">
+      <c r="A2090" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2090" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2090" s="3">
+        <v>41.52</v>
+      </c>
+      <c r="D2090" s="3">
+        <v>41.61</v>
+      </c>
+      <c r="E2090" s="3">
+        <v>41.43</v>
+      </c>
+      <c r="F2090" s="3">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:6">
+      <c r="A2091" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2091" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2091" s="3">
+        <v>40.53</v>
+      </c>
+      <c r="D2091" s="3">
+        <v>40.63</v>
+      </c>
+      <c r="E2091" s="3">
+        <v>40.47</v>
+      </c>
+      <c r="F2091" s="3">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:6">
+      <c r="A2092" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2092" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2092" s="3">
+        <v>54.44</v>
+      </c>
+      <c r="D2092" s="3">
+        <v>54.9</v>
+      </c>
+      <c r="E2092" s="3">
+        <v>54.19</v>
+      </c>
+      <c r="F2092" s="3">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:6">
+      <c r="A2093" s="2">
+        <v>46006</v>
+      </c>
+      <c r="B2093" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2093" s="3">
+        <v>58.46</v>
+      </c>
+      <c r="D2093" s="3">
+        <v>58.78</v>
+      </c>
+      <c r="E2093" s="3">
+        <v>58.23</v>
+      </c>
+      <c r="F2093" s="3">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:6">
+      <c r="A2094" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2094" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2094" s="5"/>
+      <c r="D2094" s="5"/>
+      <c r="E2094" s="5"/>
+      <c r="F2094" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:6">
+      <c r="A2095" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2095" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2095" s="5"/>
+      <c r="D2095" s="5"/>
+      <c r="E2095" s="5"/>
+      <c r="F2095" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:6">
+      <c r="A2096" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2096" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2096" s="5"/>
+      <c r="D2096" s="5"/>
+      <c r="E2096" s="5"/>
+      <c r="F2096" s="5">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:6">
+      <c r="A2097" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2097" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2097" s="5"/>
+      <c r="D2097" s="5"/>
+      <c r="E2097" s="5"/>
+      <c r="F2097" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:6">
+      <c r="A2098" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2098" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2098" s="5"/>
+      <c r="D2098" s="5"/>
+      <c r="E2098" s="5"/>
+      <c r="F2098" s="5">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:6">
+      <c r="A2099" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2099" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2099" s="5"/>
+      <c r="D2099" s="5"/>
+      <c r="E2099" s="5"/>
+      <c r="F2099" s="5">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:6">
+      <c r="A2100" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B2100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2100" s="5"/>
+      <c r="D2100" s="5"/>
+      <c r="E2100" s="5"/>
+      <c r="F2100" s="5">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:6">
+      <c r="A2101" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2101" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2101" s="5"/>
+      <c r="D2101" s="5"/>
+      <c r="E2101" s="5"/>
+      <c r="F2101" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:6">
+      <c r="A2102" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2102" s="5"/>
+      <c r="D2102" s="5"/>
+      <c r="E2102" s="5"/>
+      <c r="F2102" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:6">
+      <c r="A2103" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2103" s="5"/>
+      <c r="D2103" s="5"/>
+      <c r="E2103" s="5"/>
+      <c r="F2103" s="5">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6">
+      <c r="A2104" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2104" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2104" s="5"/>
+      <c r="D2104" s="5"/>
+      <c r="E2104" s="5"/>
+      <c r="F2104" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6">
+      <c r="A2105" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2105" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2105" s="5"/>
+      <c r="D2105" s="5"/>
+      <c r="E2105" s="5"/>
+      <c r="F2105" s="5">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6">
+      <c r="A2106" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2106" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2106" s="5"/>
+      <c r="D2106" s="5"/>
+      <c r="E2106" s="5"/>
+      <c r="F2106" s="5">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6">
+      <c r="A2107" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B2107" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2107" s="5"/>
+      <c r="D2107" s="5"/>
+      <c r="E2107" s="5"/>
+      <c r="F2107" s="5">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6">
+      <c r="A2108" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2108" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2108" s="5"/>
+      <c r="D2108" s="5"/>
+      <c r="E2108" s="5"/>
+      <c r="F2108" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6">
+      <c r="A2109" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2109" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2109" s="5"/>
+      <c r="D2109" s="5"/>
+      <c r="E2109" s="5"/>
+      <c r="F2109" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6">
+      <c r="A2110" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2110" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2110" s="5"/>
+      <c r="D2110" s="5"/>
+      <c r="E2110" s="5"/>
+      <c r="F2110" s="5">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6">
+      <c r="A2111" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2111" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2111" s="5"/>
+      <c r="D2111" s="5"/>
+      <c r="E2111" s="5"/>
+      <c r="F2111" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6">
+      <c r="A2112" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2112" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2112" s="5"/>
+      <c r="D2112" s="5"/>
+      <c r="E2112" s="5"/>
+      <c r="F2112" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:6">
+      <c r="A2113" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2113" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2113" s="5"/>
+      <c r="D2113" s="5"/>
+      <c r="E2113" s="5"/>
+      <c r="F2113" s="5">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:6">
+      <c r="A2114" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B2114" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2114" s="5"/>
+      <c r="D2114" s="5"/>
+      <c r="E2114" s="5"/>
+      <c r="F2114" s="5">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:6">
+      <c r="A2115" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2115" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2115" s="5"/>
+      <c r="D2115" s="5"/>
+      <c r="E2115" s="5"/>
+      <c r="F2115" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:6">
+      <c r="A2116" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2116" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2116" s="5"/>
+      <c r="D2116" s="5"/>
+      <c r="E2116" s="5"/>
+      <c r="F2116" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:6">
+      <c r="A2117" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2117" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2117" s="5"/>
+      <c r="D2117" s="5"/>
+      <c r="E2117" s="5"/>
+      <c r="F2117" s="5">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:6">
+      <c r="A2118" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2118" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2118" s="5"/>
+      <c r="D2118" s="5"/>
+      <c r="E2118" s="5"/>
+      <c r="F2118" s="5">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:6">
+      <c r="A2119" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2119" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2119" s="5"/>
+      <c r="D2119" s="5"/>
+      <c r="E2119" s="5"/>
+      <c r="F2119" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:6">
+      <c r="A2120" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2120" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2120" s="5"/>
+      <c r="D2120" s="5"/>
+      <c r="E2120" s="5"/>
+      <c r="F2120" s="5">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:6">
+      <c r="A2121" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B2121" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2121" s="5"/>
+      <c r="D2121" s="5"/>
+      <c r="E2121" s="5"/>
+      <c r="F2121" s="5">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:6">
+      <c r="A2122" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2122" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2122" s="5"/>
+      <c r="D2122" s="5"/>
+      <c r="E2122" s="5"/>
+      <c r="F2122" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:6">
+      <c r="A2123" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2123" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2123" s="5"/>
+      <c r="D2123" s="5"/>
+      <c r="E2123" s="5"/>
+      <c r="F2123" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:6">
+      <c r="A2124" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2124" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2124" s="5"/>
+      <c r="D2124" s="5"/>
+      <c r="E2124" s="5"/>
+      <c r="F2124" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:6">
+      <c r="A2125" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2125" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2125" s="5"/>
+      <c r="D2125" s="5"/>
+      <c r="E2125" s="5"/>
+      <c r="F2125" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:6">
+      <c r="A2126" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2126" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2126" s="5"/>
+      <c r="D2126" s="5"/>
+      <c r="E2126" s="5"/>
+      <c r="F2126" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:6">
+      <c r="A2127" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2127" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2127" s="5"/>
+      <c r="D2127" s="5"/>
+      <c r="E2127" s="5"/>
+      <c r="F2127" s="5">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:6">
+      <c r="A2128" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B2128" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2128" s="5"/>
+      <c r="D2128" s="5"/>
+      <c r="E2128" s="5"/>
+      <c r="F2128" s="5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:6">
+      <c r="A2129" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2129" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2129" s="5"/>
+      <c r="D2129" s="5"/>
+      <c r="E2129" s="5"/>
+      <c r="F2129" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:6">
+      <c r="A2130" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2130" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2130" s="5"/>
+      <c r="D2130" s="5"/>
+      <c r="E2130" s="5"/>
+      <c r="F2130" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:6">
+      <c r="A2131" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2131" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2131" s="5"/>
+      <c r="D2131" s="5"/>
+      <c r="E2131" s="5"/>
+      <c r="F2131" s="5">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:6">
+      <c r="A2132" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2132" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2132" s="5"/>
+      <c r="D2132" s="5"/>
+      <c r="E2132" s="5"/>
+      <c r="F2132" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:6">
+      <c r="A2133" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2133" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2133" s="5"/>
+      <c r="D2133" s="5"/>
+      <c r="E2133" s="5"/>
+      <c r="F2133" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:6">
+      <c r="A2134" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2134" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2134" s="5"/>
+      <c r="D2134" s="5"/>
+      <c r="E2134" s="5"/>
+      <c r="F2134" s="5">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:6">
+      <c r="A2135" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B2135" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2135" s="5"/>
+      <c r="D2135" s="5"/>
+      <c r="E2135" s="5"/>
+      <c r="F2135" s="5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:6">
+      <c r="A2136" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2136" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2136" s="5"/>
+      <c r="D2136" s="5"/>
+      <c r="E2136" s="5"/>
+      <c r="F2136" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:6">
+      <c r="A2137" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2137" s="5"/>
+      <c r="D2137" s="5"/>
+      <c r="E2137" s="5"/>
+      <c r="F2137" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:6">
+      <c r="A2138" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2138" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2138" s="5"/>
+      <c r="D2138" s="5"/>
+      <c r="E2138" s="5"/>
+      <c r="F2138" s="5">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:6">
+      <c r="A2139" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2139" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2139" s="5"/>
+      <c r="D2139" s="5"/>
+      <c r="E2139" s="5"/>
+      <c r="F2139" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:6">
+      <c r="A2140" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2140" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2140" s="5"/>
+      <c r="D2140" s="5"/>
+      <c r="E2140" s="5"/>
+      <c r="F2140" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:6">
+      <c r="A2141" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2141" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2141" s="5"/>
+      <c r="D2141" s="5"/>
+      <c r="E2141" s="5"/>
+      <c r="F2141" s="5">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:6">
+      <c r="A2142" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B2142" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2142" s="5"/>
+      <c r="D2142" s="5"/>
+      <c r="E2142" s="5"/>
+      <c r="F2142" s="5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:6">
+      <c r="A2143" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2143" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2143" s="5"/>
+      <c r="D2143" s="5"/>
+      <c r="E2143" s="5"/>
+      <c r="F2143" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:6">
+      <c r="A2144" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2144" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2144" s="5"/>
+      <c r="D2144" s="5"/>
+      <c r="E2144" s="5"/>
+      <c r="F2144" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:6">
+      <c r="A2145" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2145" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2145" s="5"/>
+      <c r="D2145" s="5"/>
+      <c r="E2145" s="5"/>
+      <c r="F2145" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:6">
+      <c r="A2146" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2146" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2146" s="5"/>
+      <c r="D2146" s="5"/>
+      <c r="E2146" s="5"/>
+      <c r="F2146" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:6">
+      <c r="A2147" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2147" s="5"/>
+      <c r="D2147" s="5"/>
+      <c r="E2147" s="5"/>
+      <c r="F2147" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:6">
+      <c r="A2148" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2148" s="5"/>
+      <c r="D2148" s="5"/>
+      <c r="E2148" s="5"/>
+      <c r="F2148" s="5">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:6">
+      <c r="A2149" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B2149" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2149" s="5"/>
+      <c r="D2149" s="5"/>
+      <c r="E2149" s="5"/>
+      <c r="F2149" s="5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:6">
+      <c r="A2150" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2150" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2150" s="5"/>
+      <c r="D2150" s="5"/>
+      <c r="E2150" s="5"/>
+      <c r="F2150" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:6">
+      <c r="A2151" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2151" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2151" s="5"/>
+      <c r="D2151" s="5"/>
+      <c r="E2151" s="5"/>
+      <c r="F2151" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:6">
+      <c r="A2152" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2152" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2152" s="5"/>
+      <c r="D2152" s="5"/>
+      <c r="E2152" s="5"/>
+      <c r="F2152" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:6">
+      <c r="A2153" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2153" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2153" s="5"/>
+      <c r="D2153" s="5"/>
+      <c r="E2153" s="5"/>
+      <c r="F2153" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:6">
+      <c r="A2154" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2154" s="5"/>
+      <c r="D2154" s="5"/>
+      <c r="E2154" s="5"/>
+      <c r="F2154" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:6">
+      <c r="A2155" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2155" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2155" s="5"/>
+      <c r="D2155" s="5"/>
+      <c r="E2155" s="5"/>
+      <c r="F2155" s="5">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:6">
+      <c r="A2156" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B2156" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2156" s="5"/>
+      <c r="D2156" s="5"/>
+      <c r="E2156" s="5"/>
+      <c r="F2156" s="5">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:6">
+      <c r="A2157" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2157" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2157" s="5"/>
+      <c r="D2157" s="5"/>
+      <c r="E2157" s="5"/>
+      <c r="F2157" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:6">
+      <c r="A2158" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2158" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2158" s="5"/>
+      <c r="D2158" s="5"/>
+      <c r="E2158" s="5"/>
+      <c r="F2158" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:6">
+      <c r="A2159" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2159" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2159" s="5"/>
+      <c r="D2159" s="5"/>
+      <c r="E2159" s="5"/>
+      <c r="F2159" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:6">
+      <c r="A2160" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2160" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2160" s="5"/>
+      <c r="D2160" s="5"/>
+      <c r="E2160" s="5"/>
+      <c r="F2160" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:6">
+      <c r="A2161" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2161" s="5"/>
+      <c r="D2161" s="5"/>
+      <c r="E2161" s="5"/>
+      <c r="F2161" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:6">
+      <c r="A2162" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2162" s="5"/>
+      <c r="D2162" s="5"/>
+      <c r="E2162" s="5"/>
+      <c r="F2162" s="5">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:6">
+      <c r="A2163" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B2163" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2163" s="5"/>
+      <c r="D2163" s="5"/>
+      <c r="E2163" s="5"/>
+      <c r="F2163" s="5">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:6">
+      <c r="A2164" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2164" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2164" s="5"/>
+      <c r="D2164" s="4"/>
+      <c r="E2164" s="5"/>
+      <c r="F2164" s="5">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:6">
+      <c r="A2165" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2165" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2165" s="5"/>
+      <c r="D2165" s="4"/>
+      <c r="E2165" s="5"/>
+      <c r="F2165" s="5">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:6">
+      <c r="A2166" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2166" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2166" s="5"/>
+      <c r="D2166" s="4"/>
+      <c r="E2166" s="5"/>
+      <c r="F2166" s="5">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:6">
+      <c r="A2167" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2167" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2167" s="5"/>
+      <c r="D2167" s="4"/>
+      <c r="E2167" s="5"/>
+      <c r="F2167" s="5">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:6">
+      <c r="A2168" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2168" s="5"/>
+      <c r="D2168" s="4"/>
+      <c r="E2168" s="5"/>
+      <c r="F2168" s="5">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:6">
+      <c r="A2169" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2169" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2169" s="5"/>
+      <c r="D2169" s="4"/>
+      <c r="E2169" s="5"/>
+      <c r="F2169" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:6">
+      <c r="A2170" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B2170" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2170" s="5"/>
+      <c r="D2170" s="4"/>
+      <c r="E2170" s="5"/>
+      <c r="F2170" s="5">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:6">
+      <c r="A2171" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2171" s="3"/>
+      <c r="D2171" s="2"/>
+      <c r="E2171" s="3"/>
+      <c r="F2171" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:6">
+      <c r="A2172" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2172" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2172" s="3"/>
+      <c r="D2172" s="2"/>
+      <c r="E2172" s="3"/>
+      <c r="F2172" s="3">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:6">
+      <c r="A2173" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2173" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2173" s="3"/>
+      <c r="D2173" s="2"/>
+      <c r="E2173" s="3"/>
+      <c r="F2173" s="3">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:6">
+      <c r="A2174" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2174" s="3"/>
+      <c r="D2174" s="2"/>
+      <c r="E2174" s="3"/>
+      <c r="F2174" s="3">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:6">
+      <c r="A2175" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2175" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2175" s="3"/>
+      <c r="D2175" s="2"/>
+      <c r="E2175" s="3"/>
+      <c r="F2175" s="3">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:6">
+      <c r="A2176" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2176" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2176" s="3"/>
+      <c r="D2176" s="2"/>
+      <c r="E2176" s="3"/>
+      <c r="F2176" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:6">
+      <c r="A2177" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B2177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2177" s="3"/>
+      <c r="D2177" s="2"/>
+      <c r="E2177" s="3"/>
+      <c r="F2177" s="3">
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>

--- a/价格数据模版.xlsx
+++ b/价格数据模版.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="13">
   <si>
     <t>日期</t>
   </si>
@@ -717,14 +717,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1065,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2177"/>
+  <dimension ref="A1:F2443"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="6" width="25.75" customWidth="1"/>
@@ -42932,1080 +42931,1542 @@
       </c>
     </row>
     <row r="2094" spans="1:6">
-      <c r="A2094" s="4">
+      <c r="A2094" s="2">
         <v>46007</v>
       </c>
-      <c r="B2094" s="5" t="s">
+      <c r="B2094" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2094" s="5"/>
-      <c r="D2094" s="5"/>
-      <c r="E2094" s="5"/>
-      <c r="F2094" s="5">
+      <c r="C2094" s="3">
+        <v>58.55</v>
+      </c>
+      <c r="D2094" s="3">
+        <v>59.12</v>
+      </c>
+      <c r="E2094" s="3">
+        <v>58.34</v>
+      </c>
+      <c r="F2094" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2095" spans="1:6">
-      <c r="A2095" s="4">
+      <c r="A2095" s="2">
         <v>46007</v>
       </c>
-      <c r="B2095" s="5" t="s">
+      <c r="B2095" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2095" s="5"/>
-      <c r="D2095" s="5"/>
-      <c r="E2095" s="5"/>
-      <c r="F2095" s="5">
+      <c r="C2095" s="3">
+        <v>56.58</v>
+      </c>
+      <c r="D2095" s="3">
+        <v>56.84</v>
+      </c>
+      <c r="E2095" s="3">
+        <v>56.38</v>
+      </c>
+      <c r="F2095" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2096" spans="1:6">
-      <c r="A2096" s="4">
+      <c r="A2096" s="2">
         <v>46007</v>
       </c>
-      <c r="B2096" s="5" t="s">
+      <c r="B2096" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2096" s="5"/>
-      <c r="D2096" s="5"/>
-      <c r="E2096" s="5"/>
-      <c r="F2096" s="5">
+      <c r="C2096" s="3">
+        <v>46.93</v>
+      </c>
+      <c r="D2096" s="3">
+        <v>47.69</v>
+      </c>
+      <c r="E2096" s="3">
+        <v>46.77</v>
+      </c>
+      <c r="F2096" s="3">
         <v>47.4</v>
       </c>
     </row>
     <row r="2097" spans="1:6">
-      <c r="A2097" s="4">
+      <c r="A2097" s="2">
         <v>46007</v>
       </c>
-      <c r="B2097" s="5" t="s">
+      <c r="B2097" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2097" s="5"/>
-      <c r="D2097" s="5"/>
-      <c r="E2097" s="5"/>
-      <c r="F2097" s="5">
-        <v>41.5</v>
+      <c r="C2097" s="3">
+        <v>41.68</v>
+      </c>
+      <c r="D2097" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="E2097" s="3">
+        <v>41.62</v>
+      </c>
+      <c r="F2097" s="3">
+        <v>41.7</v>
       </c>
     </row>
     <row r="2098" spans="1:6">
-      <c r="A2098" s="4">
+      <c r="A2098" s="2">
         <v>46007</v>
       </c>
-      <c r="B2098" s="5" t="s">
+      <c r="B2098" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2098" s="5"/>
-      <c r="D2098" s="5"/>
-      <c r="E2098" s="5"/>
-      <c r="F2098" s="5">
+      <c r="C2098" s="3">
+        <v>40.33</v>
+      </c>
+      <c r="D2098" s="3">
+        <v>40.51</v>
+      </c>
+      <c r="E2098" s="3">
+        <v>40.2</v>
+      </c>
+      <c r="F2098" s="3">
         <v>40.5</v>
       </c>
     </row>
     <row r="2099" spans="1:6">
-      <c r="A2099" s="4">
+      <c r="A2099" s="2">
         <v>46007</v>
       </c>
-      <c r="B2099" s="5" t="s">
+      <c r="B2099" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2099" s="5"/>
-      <c r="D2099" s="5"/>
-      <c r="E2099" s="5"/>
-      <c r="F2099" s="5">
+      <c r="C2099" s="3">
+        <v>54.43</v>
+      </c>
+      <c r="D2099" s="3">
+        <v>54.65</v>
+      </c>
+      <c r="E2099" s="3">
+        <v>54.17</v>
+      </c>
+      <c r="F2099" s="3">
         <v>54.6</v>
       </c>
     </row>
     <row r="2100" spans="1:6">
-      <c r="A2100" s="4">
+      <c r="A2100" s="2">
         <v>46007</v>
       </c>
-      <c r="B2100" s="5" t="s">
+      <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2100" s="5"/>
-      <c r="D2100" s="5"/>
-      <c r="E2100" s="5"/>
-      <c r="F2100" s="5">
+      <c r="C2100" s="3">
+        <v>59.36</v>
+      </c>
+      <c r="D2100" s="3">
+        <v>59.73</v>
+      </c>
+      <c r="E2100" s="3">
+        <v>59.17</v>
+      </c>
+      <c r="F2100" s="3">
         <v>59.4</v>
       </c>
     </row>
     <row r="2101" spans="1:6">
-      <c r="A2101" s="4">
+      <c r="A2101" s="2">
         <v>46008</v>
       </c>
-      <c r="B2101" s="5" t="s">
+      <c r="B2101" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2101" s="5"/>
-      <c r="D2101" s="5"/>
-      <c r="E2101" s="5"/>
-      <c r="F2101" s="5">
+      <c r="C2101" s="3">
+        <v>58.82</v>
+      </c>
+      <c r="D2101" s="3">
+        <v>58.86</v>
+      </c>
+      <c r="E2101" s="3">
+        <v>58.63</v>
+      </c>
+      <c r="F2101" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2102" spans="1:6">
-      <c r="A2102" s="4">
+      <c r="A2102" s="2">
         <v>46008</v>
       </c>
-      <c r="B2102" s="5" t="s">
+      <c r="B2102" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2102" s="5"/>
-      <c r="D2102" s="5"/>
-      <c r="E2102" s="5"/>
-      <c r="F2102" s="5">
+      <c r="C2102" s="3">
+        <v>56.73</v>
+      </c>
+      <c r="D2102" s="3">
+        <v>56.85</v>
+      </c>
+      <c r="E2102" s="3">
+        <v>56.59</v>
+      </c>
+      <c r="F2102" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2103" spans="1:6">
-      <c r="A2103" s="4">
+      <c r="A2103" s="2">
         <v>46008</v>
       </c>
-      <c r="B2103" s="5" t="s">
+      <c r="B2103" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2103" s="5"/>
-      <c r="D2103" s="5"/>
-      <c r="E2103" s="5"/>
-      <c r="F2103" s="5">
+      <c r="C2103" s="3">
+        <v>47.62</v>
+      </c>
+      <c r="D2103" s="3">
+        <v>47.8</v>
+      </c>
+      <c r="E2103" s="3">
+        <v>47.37</v>
+      </c>
+      <c r="F2103" s="3">
         <v>47.4</v>
       </c>
     </row>
     <row r="2104" spans="1:6">
-      <c r="A2104" s="4">
+      <c r="A2104" s="2">
         <v>46008</v>
       </c>
-      <c r="B2104" s="5" t="s">
+      <c r="B2104" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2104" s="5"/>
-      <c r="D2104" s="5"/>
-      <c r="E2104" s="5"/>
-      <c r="F2104" s="5">
-        <v>41.5</v>
+      <c r="C2104" s="3">
+        <v>41.79</v>
+      </c>
+      <c r="D2104" s="3">
+        <v>42.09</v>
+      </c>
+      <c r="E2104" s="3">
+        <v>41.62</v>
+      </c>
+      <c r="F2104" s="3">
+        <v>41.8</v>
       </c>
     </row>
     <row r="2105" spans="1:6">
-      <c r="A2105" s="4">
+      <c r="A2105" s="2">
         <v>46008</v>
       </c>
-      <c r="B2105" s="5" t="s">
+      <c r="B2105" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2105" s="5"/>
-      <c r="D2105" s="5"/>
-      <c r="E2105" s="5"/>
-      <c r="F2105" s="5">
+      <c r="C2105" s="3">
         <v>40.5</v>
       </c>
+      <c r="D2105" s="3">
+        <v>40.51</v>
+      </c>
+      <c r="E2105" s="3">
+        <v>40.42</v>
+      </c>
+      <c r="F2105" s="3">
+        <v>40.5</v>
+      </c>
     </row>
     <row r="2106" spans="1:6">
-      <c r="A2106" s="4">
+      <c r="A2106" s="2">
         <v>46008</v>
       </c>
-      <c r="B2106" s="5" t="s">
+      <c r="B2106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2106" s="5"/>
-      <c r="D2106" s="5"/>
-      <c r="E2106" s="5"/>
-      <c r="F2106" s="5">
+      <c r="C2106" s="3">
+        <v>54.54</v>
+      </c>
+      <c r="D2106" s="3">
+        <v>54.61</v>
+      </c>
+      <c r="E2106" s="3">
+        <v>54.23</v>
+      </c>
+      <c r="F2106" s="3">
         <v>54.5</v>
       </c>
     </row>
     <row r="2107" spans="1:6">
-      <c r="A2107" s="4">
+      <c r="A2107" s="2">
         <v>46008</v>
       </c>
-      <c r="B2107" s="5" t="s">
+      <c r="B2107" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2107" s="5"/>
-      <c r="D2107" s="5"/>
-      <c r="E2107" s="5"/>
-      <c r="F2107" s="5">
+      <c r="C2107" s="3">
+        <v>59.81</v>
+      </c>
+      <c r="D2107" s="3">
+        <v>60.01</v>
+      </c>
+      <c r="E2107" s="3">
+        <v>59.15</v>
+      </c>
+      <c r="F2107" s="3">
         <v>59.4</v>
       </c>
     </row>
     <row r="2108" spans="1:6">
-      <c r="A2108" s="4">
+      <c r="A2108" s="2">
         <v>46009</v>
       </c>
-      <c r="B2108" s="5" t="s">
+      <c r="B2108" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2108" s="5"/>
-      <c r="D2108" s="5"/>
-      <c r="E2108" s="5"/>
-      <c r="F2108" s="5">
+      <c r="C2108" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="D2108" s="3">
+        <v>59.08</v>
+      </c>
+      <c r="E2108" s="3">
+        <v>58.01</v>
+      </c>
+      <c r="F2108" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2109" spans="1:6">
-      <c r="A2109" s="4">
+      <c r="A2109" s="2">
         <v>46009</v>
       </c>
-      <c r="B2109" s="5" t="s">
+      <c r="B2109" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2109" s="5"/>
-      <c r="D2109" s="5"/>
-      <c r="E2109" s="5"/>
-      <c r="F2109" s="5">
+      <c r="C2109" s="3">
+        <v>56.27</v>
+      </c>
+      <c r="D2109" s="3">
+        <v>57.19</v>
+      </c>
+      <c r="E2109" s="3">
+        <v>56.2</v>
+      </c>
+      <c r="F2109" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2110" spans="1:6">
-      <c r="A2110" s="4">
+      <c r="A2110" s="2">
         <v>46009</v>
       </c>
-      <c r="B2110" s="5" t="s">
+      <c r="B2110" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2110" s="5"/>
-      <c r="D2110" s="5"/>
-      <c r="E2110" s="5"/>
-      <c r="F2110" s="5">
+      <c r="C2110" s="3">
+        <v>47.27</v>
+      </c>
+      <c r="D2110" s="3">
+        <v>47.44</v>
+      </c>
+      <c r="E2110" s="3">
+        <v>47.06</v>
+      </c>
+      <c r="F2110" s="3">
         <v>47.4</v>
       </c>
     </row>
     <row r="2111" spans="1:6">
-      <c r="A2111" s="4">
+      <c r="A2111" s="2">
         <v>46009</v>
       </c>
-      <c r="B2111" s="5" t="s">
+      <c r="B2111" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2111" s="5"/>
-      <c r="D2111" s="5"/>
-      <c r="E2111" s="5"/>
-      <c r="F2111" s="5">
-        <v>41.5</v>
+      <c r="C2111" s="3">
+        <v>41.87</v>
+      </c>
+      <c r="D2111" s="3">
+        <v>42.17</v>
+      </c>
+      <c r="E2111" s="3">
+        <v>41.71</v>
+      </c>
+      <c r="F2111" s="3">
+        <v>41.9</v>
       </c>
     </row>
     <row r="2112" spans="1:6">
-      <c r="A2112" s="4">
+      <c r="A2112" s="2">
         <v>46009</v>
       </c>
-      <c r="B2112" s="5" t="s">
+      <c r="B2112" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2112" s="5"/>
-      <c r="D2112" s="5"/>
-      <c r="E2112" s="5"/>
-      <c r="F2112" s="5">
+      <c r="C2112" s="3">
+        <v>40.44</v>
+      </c>
+      <c r="D2112" s="3">
+        <v>40.48</v>
+      </c>
+      <c r="E2112" s="3">
+        <v>40.36</v>
+      </c>
+      <c r="F2112" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2113" spans="1:6">
-      <c r="A2113" s="4">
+      <c r="A2113" s="2">
         <v>46009</v>
       </c>
-      <c r="B2113" s="5" t="s">
+      <c r="B2113" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2113" s="5"/>
-      <c r="D2113" s="5"/>
-      <c r="E2113" s="5"/>
-      <c r="F2113" s="5">
+      <c r="C2113" s="3">
+        <v>54.85</v>
+      </c>
+      <c r="D2113" s="3">
+        <v>55</v>
+      </c>
+      <c r="E2113" s="3">
+        <v>54.28</v>
+      </c>
+      <c r="F2113" s="3">
         <v>54.5</v>
       </c>
     </row>
     <row r="2114" spans="1:6">
-      <c r="A2114" s="4">
+      <c r="A2114" s="2">
         <v>46009</v>
       </c>
-      <c r="B2114" s="5" t="s">
+      <c r="B2114" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2114" s="5"/>
-      <c r="D2114" s="5"/>
-      <c r="E2114" s="5"/>
-      <c r="F2114" s="5">
+      <c r="C2114" s="3">
+        <v>59.59</v>
+      </c>
+      <c r="D2114" s="3">
+        <v>59.76</v>
+      </c>
+      <c r="E2114" s="3">
+        <v>59.51</v>
+      </c>
+      <c r="F2114" s="3">
         <v>59.6</v>
       </c>
     </row>
     <row r="2115" spans="1:6">
-      <c r="A2115" s="4">
+      <c r="A2115" s="2">
         <v>46010</v>
       </c>
-      <c r="B2115" s="5" t="s">
+      <c r="B2115" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2115" s="5"/>
-      <c r="D2115" s="5"/>
-      <c r="E2115" s="5"/>
-      <c r="F2115" s="5">
+      <c r="C2115" s="3">
+        <v>58.94</v>
+      </c>
+      <c r="D2115" s="3">
+        <v>58.95</v>
+      </c>
+      <c r="E2115" s="3">
+        <v>58.27</v>
+      </c>
+      <c r="F2115" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2116" spans="1:6">
-      <c r="A2116" s="4">
+      <c r="A2116" s="2">
         <v>46010</v>
       </c>
-      <c r="B2116" s="5" t="s">
+      <c r="B2116" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2116" s="5"/>
-      <c r="D2116" s="5"/>
-      <c r="E2116" s="5"/>
-      <c r="F2116" s="5">
+      <c r="C2116" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="D2116" s="3">
+        <v>57.07</v>
+      </c>
+      <c r="E2116" s="3">
+        <v>56.58</v>
+      </c>
+      <c r="F2116" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2117" spans="1:6">
-      <c r="A2117" s="4">
+      <c r="A2117" s="2">
         <v>46010</v>
       </c>
-      <c r="B2117" s="5" t="s">
+      <c r="B2117" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2117" s="5"/>
-      <c r="D2117" s="5"/>
-      <c r="E2117" s="5"/>
-      <c r="F2117" s="5">
+      <c r="C2117" s="3">
+        <v>47.52</v>
+      </c>
+      <c r="D2117" s="3">
+        <v>47.6</v>
+      </c>
+      <c r="E2117" s="3">
+        <v>47.38</v>
+      </c>
+      <c r="F2117" s="3">
         <v>47.4</v>
       </c>
     </row>
     <row r="2118" spans="1:6">
-      <c r="A2118" s="4">
+      <c r="A2118" s="2">
         <v>46010</v>
       </c>
-      <c r="B2118" s="5" t="s">
+      <c r="B2118" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2118" s="5"/>
-      <c r="D2118" s="5"/>
-      <c r="E2118" s="5"/>
-      <c r="F2118" s="5">
-        <v>41.5</v>
+      <c r="C2118" s="3">
+        <v>41.64</v>
+      </c>
+      <c r="D2118" s="3">
+        <v>42.18</v>
+      </c>
+      <c r="E2118" s="3">
+        <v>41.53</v>
+      </c>
+      <c r="F2118" s="3">
+        <v>41.9</v>
       </c>
     </row>
     <row r="2119" spans="1:6">
-      <c r="A2119" s="4">
+      <c r="A2119" s="2">
         <v>46010</v>
       </c>
-      <c r="B2119" s="5" t="s">
+      <c r="B2119" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2119" s="5"/>
-      <c r="D2119" s="5"/>
-      <c r="E2119" s="5"/>
-      <c r="F2119" s="5">
+      <c r="C2119" s="3">
+        <v>40.39</v>
+      </c>
+      <c r="D2119" s="3">
+        <v>40.7</v>
+      </c>
+      <c r="E2119" s="3">
+        <v>40.34</v>
+      </c>
+      <c r="F2119" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2120" spans="1:6">
-      <c r="A2120" s="4">
+      <c r="A2120" s="2">
         <v>46010</v>
       </c>
-      <c r="B2120" s="5" t="s">
+      <c r="B2120" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2120" s="5"/>
-      <c r="D2120" s="5"/>
-      <c r="E2120" s="5"/>
-      <c r="F2120" s="5">
+      <c r="C2120" s="3">
+        <v>54.41</v>
+      </c>
+      <c r="D2120" s="3">
+        <v>54.43</v>
+      </c>
+      <c r="E2120" s="3">
+        <v>54.03</v>
+      </c>
+      <c r="F2120" s="3">
         <v>54.4</v>
       </c>
     </row>
     <row r="2121" spans="1:6">
-      <c r="A2121" s="4">
+      <c r="A2121" s="2">
         <v>46010</v>
       </c>
-      <c r="B2121" s="5" t="s">
+      <c r="B2121" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2121" s="5"/>
-      <c r="D2121" s="5"/>
-      <c r="E2121" s="5"/>
-      <c r="F2121" s="5">
+      <c r="C2121" s="3">
+        <v>59.29</v>
+      </c>
+      <c r="D2121" s="3">
+        <v>60.03</v>
+      </c>
+      <c r="E2121" s="3">
+        <v>59.18</v>
+      </c>
+      <c r="F2121" s="3">
         <v>59.6</v>
       </c>
     </row>
     <row r="2122" spans="1:6">
-      <c r="A2122" s="4">
+      <c r="A2122" s="2">
         <v>46013</v>
       </c>
-      <c r="B2122" s="5" t="s">
+      <c r="B2122" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2122" s="5"/>
-      <c r="D2122" s="5"/>
-      <c r="E2122" s="5"/>
-      <c r="F2122" s="5">
+      <c r="C2122" s="3">
+        <v>59.09</v>
+      </c>
+      <c r="D2122" s="3">
+        <v>59.15</v>
+      </c>
+      <c r="E2122" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="F2122" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2123" spans="1:6">
-      <c r="A2123" s="4">
+      <c r="A2123" s="2">
         <v>46013</v>
       </c>
-      <c r="B2123" s="5" t="s">
+      <c r="B2123" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2123" s="5"/>
-      <c r="D2123" s="5"/>
-      <c r="E2123" s="5"/>
-      <c r="F2123" s="5">
+      <c r="C2123" s="3">
+        <v>56.85</v>
+      </c>
+      <c r="D2123" s="3">
+        <v>56.91</v>
+      </c>
+      <c r="E2123" s="3">
+        <v>56.39</v>
+      </c>
+      <c r="F2123" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2124" spans="1:6">
-      <c r="A2124" s="4">
+      <c r="A2124" s="2">
         <v>46013</v>
       </c>
-      <c r="B2124" s="5" t="s">
+      <c r="B2124" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2124" s="5"/>
-      <c r="D2124" s="5"/>
-      <c r="E2124" s="5"/>
-      <c r="F2124" s="5">
+      <c r="C2124" s="3">
+        <v>47.92</v>
+      </c>
+      <c r="D2124" s="3">
+        <v>48.12</v>
+      </c>
+      <c r="E2124" s="3">
+        <v>47.75</v>
+      </c>
+      <c r="F2124" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="2125" spans="1:6">
-      <c r="A2125" s="4">
+      <c r="A2125" s="2">
         <v>46013</v>
       </c>
-      <c r="B2125" s="5" t="s">
+      <c r="B2125" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2125" s="5"/>
-      <c r="D2125" s="5"/>
-      <c r="E2125" s="5"/>
-      <c r="F2125" s="5">
-        <v>41.6</v>
+      <c r="C2125" s="3">
+        <v>41.83</v>
+      </c>
+      <c r="D2125" s="3">
+        <v>42.02</v>
+      </c>
+      <c r="E2125" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="F2125" s="3">
+        <v>41.8</v>
       </c>
     </row>
     <row r="2126" spans="1:6">
-      <c r="A2126" s="4">
+      <c r="A2126" s="2">
         <v>46013</v>
       </c>
-      <c r="B2126" s="5" t="s">
+      <c r="B2126" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2126" s="5"/>
-      <c r="D2126" s="5"/>
-      <c r="E2126" s="5"/>
-      <c r="F2126" s="5">
+      <c r="C2126" s="3">
+        <v>40.54</v>
+      </c>
+      <c r="D2126" s="3">
+        <v>40.69</v>
+      </c>
+      <c r="E2126" s="3">
+        <v>40.33</v>
+      </c>
+      <c r="F2126" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2127" spans="1:6">
-      <c r="A2127" s="4">
+      <c r="A2127" s="2">
         <v>46013</v>
       </c>
-      <c r="B2127" s="5" t="s">
+      <c r="B2127" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2127" s="5"/>
-      <c r="D2127" s="5"/>
-      <c r="E2127" s="5"/>
-      <c r="F2127" s="5">
+      <c r="C2127" s="3">
+        <v>54.84</v>
+      </c>
+      <c r="D2127" s="3">
+        <v>55.01</v>
+      </c>
+      <c r="E2127" s="3">
+        <v>54.26</v>
+      </c>
+      <c r="F2127" s="3">
         <v>54.4</v>
       </c>
     </row>
     <row r="2128" spans="1:6">
-      <c r="A2128" s="4">
+      <c r="A2128" s="2">
         <v>46013</v>
       </c>
-      <c r="B2128" s="5" t="s">
+      <c r="B2128" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2128" s="5"/>
-      <c r="D2128" s="5"/>
-      <c r="E2128" s="5"/>
-      <c r="F2128" s="5">
+      <c r="C2128" s="3">
+        <v>59.92</v>
+      </c>
+      <c r="D2128" s="3">
+        <v>60.38</v>
+      </c>
+      <c r="E2128" s="3">
+        <v>59.68</v>
+      </c>
+      <c r="F2128" s="3">
         <v>60.1</v>
       </c>
     </row>
     <row r="2129" spans="1:6">
-      <c r="A2129" s="4">
+      <c r="A2129" s="2">
         <v>46014</v>
       </c>
-      <c r="B2129" s="5" t="s">
+      <c r="B2129" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2129" s="5"/>
-      <c r="D2129" s="5"/>
-      <c r="E2129" s="5"/>
-      <c r="F2129" s="5">
+      <c r="C2129" s="3">
+        <v>58.33</v>
+      </c>
+      <c r="D2129" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2129" s="3">
+        <v>58.18</v>
+      </c>
+      <c r="F2129" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2130" spans="1:6">
-      <c r="A2130" s="4">
+      <c r="A2130" s="2">
         <v>46014</v>
       </c>
-      <c r="B2130" s="5" t="s">
+      <c r="B2130" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2130" s="5"/>
-      <c r="D2130" s="5"/>
-      <c r="E2130" s="5"/>
-      <c r="F2130" s="5">
+      <c r="C2130" s="3">
+        <v>57.11</v>
+      </c>
+      <c r="D2130" s="3">
+        <v>57.38</v>
+      </c>
+      <c r="E2130" s="3">
+        <v>56.42</v>
+      </c>
+      <c r="F2130" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2131" spans="1:6">
-      <c r="A2131" s="4">
+      <c r="A2131" s="2">
         <v>46014</v>
       </c>
-      <c r="B2131" s="5" t="s">
+      <c r="B2131" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2131" s="5"/>
-      <c r="D2131" s="5"/>
-      <c r="E2131" s="5"/>
-      <c r="F2131" s="5">
+      <c r="C2131" s="3">
+        <v>47.93</v>
+      </c>
+      <c r="D2131" s="3">
+        <v>48.14</v>
+      </c>
+      <c r="E2131" s="3">
+        <v>47.73</v>
+      </c>
+      <c r="F2131" s="3">
         <v>47.9</v>
       </c>
     </row>
     <row r="2132" spans="1:6">
-      <c r="A2132" s="4">
+      <c r="A2132" s="2">
         <v>46014</v>
       </c>
-      <c r="B2132" s="5" t="s">
+      <c r="B2132" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2132" s="5"/>
-      <c r="D2132" s="5"/>
-      <c r="E2132" s="5"/>
-      <c r="F2132" s="5">
-        <v>41.6</v>
+      <c r="C2132" s="3">
+        <v>41.47</v>
+      </c>
+      <c r="D2132" s="3">
+        <v>41.87</v>
+      </c>
+      <c r="E2132" s="3">
+        <v>41.39</v>
+      </c>
+      <c r="F2132" s="3">
+        <v>41.8</v>
       </c>
     </row>
     <row r="2133" spans="1:6">
-      <c r="A2133" s="4">
+      <c r="A2133" s="2">
         <v>46014</v>
       </c>
-      <c r="B2133" s="5" t="s">
+      <c r="B2133" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2133" s="5"/>
-      <c r="D2133" s="5"/>
-      <c r="E2133" s="5"/>
-      <c r="F2133" s="5">
+      <c r="C2133" s="3">
+        <v>40.58</v>
+      </c>
+      <c r="D2133" s="3">
+        <v>40.66</v>
+      </c>
+      <c r="E2133" s="3">
+        <v>40.21</v>
+      </c>
+      <c r="F2133" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2134" spans="1:6">
-      <c r="A2134" s="4">
+      <c r="A2134" s="2">
         <v>46014</v>
       </c>
-      <c r="B2134" s="5" t="s">
+      <c r="B2134" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2134" s="5"/>
-      <c r="D2134" s="5"/>
-      <c r="E2134" s="5"/>
-      <c r="F2134" s="5">
+      <c r="C2134" s="3">
+        <v>54.23</v>
+      </c>
+      <c r="D2134" s="3">
+        <v>54.42</v>
+      </c>
+      <c r="E2134" s="3">
+        <v>53.84</v>
+      </c>
+      <c r="F2134" s="3">
         <v>54.2</v>
       </c>
     </row>
     <row r="2135" spans="1:6">
-      <c r="A2135" s="4">
+      <c r="A2135" s="2">
         <v>46014</v>
       </c>
-      <c r="B2135" s="5" t="s">
+      <c r="B2135" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2135" s="5"/>
-      <c r="D2135" s="5"/>
-      <c r="E2135" s="5"/>
-      <c r="F2135" s="5">
+      <c r="C2135" s="3">
         <v>60.1</v>
       </c>
+      <c r="D2135" s="3">
+        <v>60.28</v>
+      </c>
+      <c r="E2135" s="3">
+        <v>59.88</v>
+      </c>
+      <c r="F2135" s="3">
+        <v>60.1</v>
+      </c>
     </row>
     <row r="2136" spans="1:6">
-      <c r="A2136" s="4">
+      <c r="A2136" s="2">
         <v>46015</v>
       </c>
-      <c r="B2136" s="5" t="s">
+      <c r="B2136" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2136" s="5"/>
-      <c r="D2136" s="5"/>
-      <c r="E2136" s="5"/>
-      <c r="F2136" s="5">
+      <c r="C2136" s="3">
+        <v>58.62</v>
+      </c>
+      <c r="D2136" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2136" s="3">
+        <v>58.44</v>
+      </c>
+      <c r="F2136" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2137" spans="1:6">
-      <c r="A2137" s="4">
+      <c r="A2137" s="2">
         <v>46015</v>
       </c>
-      <c r="B2137" s="5" t="s">
+      <c r="B2137" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2137" s="5"/>
-      <c r="D2137" s="5"/>
-      <c r="E2137" s="5"/>
-      <c r="F2137" s="5">
+      <c r="C2137" s="3">
+        <v>56.91</v>
+      </c>
+      <c r="D2137" s="3">
+        <v>57.17</v>
+      </c>
+      <c r="E2137" s="3">
+        <v>56.76</v>
+      </c>
+      <c r="F2137" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2138" spans="1:6">
-      <c r="A2138" s="4">
+      <c r="A2138" s="2">
         <v>46015</v>
       </c>
-      <c r="B2138" s="5" t="s">
+      <c r="B2138" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2138" s="5"/>
-      <c r="D2138" s="5"/>
-      <c r="E2138" s="5"/>
-      <c r="F2138" s="5">
+      <c r="C2138" s="3">
         <v>47.8</v>
       </c>
+      <c r="D2138" s="3">
+        <v>47.98</v>
+      </c>
+      <c r="E2138" s="3">
+        <v>47.53</v>
+      </c>
+      <c r="F2138" s="3">
+        <v>47.8</v>
+      </c>
     </row>
     <row r="2139" spans="1:6">
-      <c r="A2139" s="4">
+      <c r="A2139" s="2">
         <v>46015</v>
       </c>
-      <c r="B2139" s="5" t="s">
+      <c r="B2139" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2139" s="5"/>
-      <c r="D2139" s="5"/>
-      <c r="E2139" s="5"/>
-      <c r="F2139" s="5">
-        <v>41.6</v>
+      <c r="C2139" s="3">
+        <v>42.07</v>
+      </c>
+      <c r="D2139" s="3">
+        <v>42.25</v>
+      </c>
+      <c r="E2139" s="3">
+        <v>41.8</v>
+      </c>
+      <c r="F2139" s="3">
+        <v>41.8</v>
       </c>
     </row>
     <row r="2140" spans="1:6">
-      <c r="A2140" s="4">
+      <c r="A2140" s="2">
         <v>46015</v>
       </c>
-      <c r="B2140" s="5" t="s">
+      <c r="B2140" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2140" s="5"/>
-      <c r="D2140" s="5"/>
-      <c r="E2140" s="5"/>
-      <c r="F2140" s="5">
+      <c r="C2140" s="3">
+        <v>40.51</v>
+      </c>
+      <c r="D2140" s="3">
+        <v>40.62</v>
+      </c>
+      <c r="E2140" s="3">
+        <v>40.37</v>
+      </c>
+      <c r="F2140" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2141" spans="1:6">
-      <c r="A2141" s="4">
+      <c r="A2141" s="2">
         <v>46015</v>
       </c>
-      <c r="B2141" s="5" t="s">
+      <c r="B2141" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2141" s="5"/>
-      <c r="D2141" s="5"/>
-      <c r="E2141" s="5"/>
-      <c r="F2141" s="5">
+      <c r="C2141" s="3">
+        <v>54.62</v>
+      </c>
+      <c r="D2141" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="E2141" s="3">
+        <v>53.94</v>
+      </c>
+      <c r="F2141" s="3">
         <v>54.2</v>
       </c>
     </row>
     <row r="2142" spans="1:6">
-      <c r="A2142" s="4">
+      <c r="A2142" s="2">
         <v>46015</v>
       </c>
-      <c r="B2142" s="5" t="s">
+      <c r="B2142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2142" s="5"/>
-      <c r="D2142" s="5"/>
-      <c r="E2142" s="5"/>
-      <c r="F2142" s="5">
+      <c r="C2142" s="3">
+        <v>59.73</v>
+      </c>
+      <c r="D2142" s="3">
+        <v>60.43</v>
+      </c>
+      <c r="E2142" s="3">
+        <v>59.65</v>
+      </c>
+      <c r="F2142" s="3">
         <v>60.1</v>
       </c>
     </row>
     <row r="2143" spans="1:6">
-      <c r="A2143" s="4">
+      <c r="A2143" s="2">
         <v>46016</v>
       </c>
-      <c r="B2143" s="5" t="s">
+      <c r="B2143" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2143" s="5"/>
-      <c r="D2143" s="5"/>
-      <c r="E2143" s="5"/>
-      <c r="F2143" s="5">
+      <c r="C2143" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="D2143" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="E2143" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="F2143" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2144" spans="1:6">
-      <c r="A2144" s="4">
+      <c r="A2144" s="2">
         <v>46016</v>
       </c>
-      <c r="B2144" s="5" t="s">
+      <c r="B2144" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2144" s="5"/>
-      <c r="D2144" s="5"/>
-      <c r="E2144" s="5"/>
-      <c r="F2144" s="5">
+      <c r="C2144" s="3">
+        <v>56.45</v>
+      </c>
+      <c r="D2144" s="3">
+        <v>56.82</v>
+      </c>
+      <c r="E2144" s="3">
+        <v>56.36</v>
+      </c>
+      <c r="F2144" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2145" spans="1:6">
-      <c r="A2145" s="4">
+      <c r="A2145" s="2">
         <v>46016</v>
       </c>
-      <c r="B2145" s="5" t="s">
+      <c r="B2145" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2145" s="5"/>
-      <c r="D2145" s="5"/>
-      <c r="E2145" s="5"/>
-      <c r="F2145" s="5">
+      <c r="C2145" s="3">
+        <v>47.95</v>
+      </c>
+      <c r="D2145" s="3">
+        <v>48.28</v>
+      </c>
+      <c r="E2145" s="3">
+        <v>47.84</v>
+      </c>
+      <c r="F2145" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="2146" spans="1:6">
-      <c r="A2146" s="4">
+      <c r="A2146" s="2">
         <v>46016</v>
       </c>
-      <c r="B2146" s="5" t="s">
+      <c r="B2146" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2146" s="5"/>
-      <c r="D2146" s="5"/>
-      <c r="E2146" s="5"/>
-      <c r="F2146" s="5">
-        <v>41.6</v>
+      <c r="C2146" s="3">
+        <v>41.72</v>
+      </c>
+      <c r="D2146" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="E2146" s="3">
+        <v>41.63</v>
+      </c>
+      <c r="F2146" s="3">
+        <v>41.7</v>
       </c>
     </row>
     <row r="2147" spans="1:6">
-      <c r="A2147" s="4">
+      <c r="A2147" s="2">
         <v>46016</v>
       </c>
-      <c r="B2147" s="5" t="s">
+      <c r="B2147" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2147" s="5"/>
-      <c r="D2147" s="5"/>
-      <c r="E2147" s="5"/>
-      <c r="F2147" s="5">
+      <c r="C2147" s="3">
+        <v>40.67</v>
+      </c>
+      <c r="D2147" s="3">
+        <v>40.74</v>
+      </c>
+      <c r="E2147" s="3">
+        <v>40.34</v>
+      </c>
+      <c r="F2147" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2148" spans="1:6">
-      <c r="A2148" s="4">
+      <c r="A2148" s="2">
         <v>46016</v>
       </c>
-      <c r="B2148" s="5" t="s">
+      <c r="B2148" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2148" s="5"/>
-      <c r="D2148" s="5"/>
-      <c r="E2148" s="5"/>
-      <c r="F2148" s="5">
+      <c r="C2148" s="3">
+        <v>53.75</v>
+      </c>
+      <c r="D2148" s="3">
+        <v>54.27</v>
+      </c>
+      <c r="E2148" s="3">
+        <v>53.51</v>
+      </c>
+      <c r="F2148" s="3">
         <v>54.2</v>
       </c>
     </row>
     <row r="2149" spans="1:6">
-      <c r="A2149" s="4">
+      <c r="A2149" s="2">
         <v>46016</v>
       </c>
-      <c r="B2149" s="5" t="s">
+      <c r="B2149" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2149" s="5"/>
-      <c r="D2149" s="5"/>
-      <c r="E2149" s="5"/>
-      <c r="F2149" s="5">
+      <c r="C2149" s="3">
+        <v>59.53</v>
+      </c>
+      <c r="D2149" s="3">
+        <v>60.39</v>
+      </c>
+      <c r="E2149" s="3">
+        <v>59.48</v>
+      </c>
+      <c r="F2149" s="3">
         <v>60.1</v>
       </c>
     </row>
     <row r="2150" spans="1:6">
-      <c r="A2150" s="4">
+      <c r="A2150" s="2">
         <v>46017</v>
       </c>
-      <c r="B2150" s="5" t="s">
+      <c r="B2150" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2150" s="5"/>
-      <c r="D2150" s="5"/>
-      <c r="E2150" s="5"/>
-      <c r="F2150" s="5">
+      <c r="C2150" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D2150" s="3">
+        <v>59.05</v>
+      </c>
+      <c r="E2150" s="3">
+        <v>58.59</v>
+      </c>
+      <c r="F2150" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2151" spans="1:6">
-      <c r="A2151" s="4">
+      <c r="A2151" s="2">
         <v>46017</v>
       </c>
-      <c r="B2151" s="5" t="s">
+      <c r="B2151" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2151" s="5"/>
-      <c r="D2151" s="5"/>
-      <c r="E2151" s="5"/>
-      <c r="F2151" s="5">
+      <c r="C2151" s="3">
+        <v>56.67</v>
+      </c>
+      <c r="D2151" s="3">
+        <v>56.92</v>
+      </c>
+      <c r="E2151" s="3">
+        <v>56.44</v>
+      </c>
+      <c r="F2151" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2152" spans="1:6">
-      <c r="A2152" s="4">
+      <c r="A2152" s="2">
         <v>46017</v>
       </c>
-      <c r="B2152" s="5" t="s">
+      <c r="B2152" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2152" s="5"/>
-      <c r="D2152" s="5"/>
-      <c r="E2152" s="5"/>
-      <c r="F2152" s="5">
+      <c r="C2152" s="3">
+        <v>48.02</v>
+      </c>
+      <c r="D2152" s="3">
+        <v>48.12</v>
+      </c>
+      <c r="E2152" s="3">
+        <v>47.99</v>
+      </c>
+      <c r="F2152" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="2153" spans="1:6">
-      <c r="A2153" s="4">
+      <c r="A2153" s="2">
         <v>46017</v>
       </c>
-      <c r="B2153" s="5" t="s">
+      <c r="B2153" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2153" s="5"/>
-      <c r="D2153" s="5"/>
-      <c r="E2153" s="5"/>
-      <c r="F2153" s="5">
-        <v>41.6</v>
+      <c r="C2153" s="3">
+        <v>41.38</v>
+      </c>
+      <c r="D2153" s="3">
+        <v>41.81</v>
+      </c>
+      <c r="E2153" s="3">
+        <v>41.19</v>
+      </c>
+      <c r="F2153" s="3">
+        <v>41.7</v>
       </c>
     </row>
     <row r="2154" spans="1:6">
-      <c r="A2154" s="4">
+      <c r="A2154" s="2">
         <v>46017</v>
       </c>
-      <c r="B2154" s="5" t="s">
+      <c r="B2154" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2154" s="5"/>
-      <c r="D2154" s="5"/>
-      <c r="E2154" s="5"/>
-      <c r="F2154" s="5">
+      <c r="C2154" s="3">
+        <v>40.03</v>
+      </c>
+      <c r="D2154" s="3">
+        <v>40.58</v>
+      </c>
+      <c r="E2154" s="3">
+        <v>39.89</v>
+      </c>
+      <c r="F2154" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2155" spans="1:6">
-      <c r="A2155" s="4">
+      <c r="A2155" s="2">
         <v>46017</v>
       </c>
-      <c r="B2155" s="5" t="s">
+      <c r="B2155" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2155" s="5"/>
-      <c r="D2155" s="5"/>
-      <c r="E2155" s="5"/>
-      <c r="F2155" s="5">
+      <c r="C2155" s="3">
+        <v>54.12</v>
+      </c>
+      <c r="D2155" s="3">
+        <v>54.13</v>
+      </c>
+      <c r="E2155" s="3">
+        <v>54.06</v>
+      </c>
+      <c r="F2155" s="3">
         <v>54.1</v>
       </c>
     </row>
     <row r="2156" spans="1:6">
-      <c r="A2156" s="4">
+      <c r="A2156" s="2">
         <v>46017</v>
       </c>
-      <c r="B2156" s="5" t="s">
+      <c r="B2156" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2156" s="5"/>
-      <c r="D2156" s="5"/>
-      <c r="E2156" s="5"/>
-      <c r="F2156" s="5">
+      <c r="C2156" s="3">
+        <v>60.63</v>
+      </c>
+      <c r="D2156" s="3">
+        <v>60.92</v>
+      </c>
+      <c r="E2156" s="3">
+        <v>59.69</v>
+      </c>
+      <c r="F2156" s="3">
         <v>60.1</v>
       </c>
     </row>
     <row r="2157" spans="1:6">
-      <c r="A2157" s="4">
+      <c r="A2157" s="2">
         <v>46020</v>
       </c>
-      <c r="B2157" s="5" t="s">
+      <c r="B2157" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2157" s="5"/>
-      <c r="D2157" s="5"/>
-      <c r="E2157" s="5"/>
-      <c r="F2157" s="5">
+      <c r="C2157" s="3">
+        <v>58.72</v>
+      </c>
+      <c r="D2157" s="3">
+        <v>58.89</v>
+      </c>
+      <c r="E2157" s="3">
+        <v>58.68</v>
+      </c>
+      <c r="F2157" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2158" spans="1:6">
-      <c r="A2158" s="4">
+      <c r="A2158" s="2">
         <v>46020</v>
       </c>
-      <c r="B2158" s="5" t="s">
+      <c r="B2158" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2158" s="5"/>
-      <c r="D2158" s="5"/>
-      <c r="E2158" s="5"/>
-      <c r="F2158" s="5">
+      <c r="C2158" s="3">
+        <v>56.64</v>
+      </c>
+      <c r="D2158" s="3">
+        <v>56.92</v>
+      </c>
+      <c r="E2158" s="3">
+        <v>56.48</v>
+      </c>
+      <c r="F2158" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2159" spans="1:6">
-      <c r="A2159" s="4">
+      <c r="A2159" s="2">
         <v>46020</v>
       </c>
-      <c r="B2159" s="5" t="s">
+      <c r="B2159" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2159" s="5"/>
-      <c r="D2159" s="5"/>
-      <c r="E2159" s="5"/>
-      <c r="F2159" s="5">
+      <c r="C2159" s="3">
+        <v>47.62</v>
+      </c>
+      <c r="D2159" s="3">
+        <v>48.01</v>
+      </c>
+      <c r="E2159" s="3">
+        <v>47.47</v>
+      </c>
+      <c r="F2159" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="2160" spans="1:6">
-      <c r="A2160" s="4">
+      <c r="A2160" s="2">
         <v>46020</v>
       </c>
-      <c r="B2160" s="5" t="s">
+      <c r="B2160" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2160" s="5"/>
-      <c r="D2160" s="5"/>
-      <c r="E2160" s="5"/>
-      <c r="F2160" s="5">
-        <v>41.6</v>
+      <c r="C2160" s="3">
+        <v>41.55</v>
+      </c>
+      <c r="D2160" s="3">
+        <v>41.86</v>
+      </c>
+      <c r="E2160" s="3">
+        <v>41.41</v>
+      </c>
+      <c r="F2160" s="3">
+        <v>41.7</v>
       </c>
     </row>
     <row r="2161" spans="1:6">
-      <c r="A2161" s="4">
+      <c r="A2161" s="2">
         <v>46020</v>
       </c>
-      <c r="B2161" s="5" t="s">
+      <c r="B2161" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2161" s="5"/>
-      <c r="D2161" s="5"/>
-      <c r="E2161" s="5"/>
-      <c r="F2161" s="5">
+      <c r="C2161" s="3">
+        <v>40.01</v>
+      </c>
+      <c r="D2161" s="3">
+        <v>40.56</v>
+      </c>
+      <c r="E2161" s="3">
+        <v>39.96</v>
+      </c>
+      <c r="F2161" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2162" spans="1:6">
-      <c r="A2162" s="4">
+      <c r="A2162" s="2">
         <v>46020</v>
       </c>
-      <c r="B2162" s="5" t="s">
+      <c r="B2162" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2162" s="5"/>
-      <c r="D2162" s="5"/>
-      <c r="E2162" s="5"/>
-      <c r="F2162" s="5">
+      <c r="C2162" s="3">
+        <v>54.28</v>
+      </c>
+      <c r="D2162" s="3">
+        <v>54.28</v>
+      </c>
+      <c r="E2162" s="3">
+        <v>54.03</v>
+      </c>
+      <c r="F2162" s="3">
         <v>54.1</v>
       </c>
     </row>
     <row r="2163" spans="1:6">
-      <c r="A2163" s="4">
+      <c r="A2163" s="2">
         <v>46020</v>
       </c>
-      <c r="B2163" s="5" t="s">
+      <c r="B2163" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2163" s="5"/>
-      <c r="D2163" s="5"/>
-      <c r="E2163" s="5"/>
-      <c r="F2163" s="5">
+      <c r="C2163" s="3">
+        <v>60.53</v>
+      </c>
+      <c r="D2163" s="3">
+        <v>60.61</v>
+      </c>
+      <c r="E2163" s="3">
+        <v>60.24</v>
+      </c>
+      <c r="F2163" s="3">
         <v>60.6</v>
       </c>
     </row>
     <row r="2164" spans="1:6">
-      <c r="A2164" s="4">
+      <c r="A2164" s="2">
         <v>46021</v>
       </c>
-      <c r="B2164" s="5" t="s">
+      <c r="B2164" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2164" s="5"/>
-      <c r="D2164" s="4"/>
-      <c r="E2164" s="5"/>
-      <c r="F2164" s="5">
+      <c r="C2164" s="3">
+        <v>58.83</v>
+      </c>
+      <c r="D2164" s="3">
+        <v>58.88</v>
+      </c>
+      <c r="E2164" s="3">
+        <v>58.67</v>
+      </c>
+      <c r="F2164" s="3">
         <v>58.7</v>
       </c>
     </row>
     <row r="2165" spans="1:6">
-      <c r="A2165" s="4">
+      <c r="A2165" s="2">
         <v>46021</v>
       </c>
-      <c r="B2165" s="5" t="s">
+      <c r="B2165" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2165" s="5"/>
-      <c r="D2165" s="4"/>
-      <c r="E2165" s="5"/>
-      <c r="F2165" s="5">
+      <c r="C2165" s="3">
+        <v>56.39</v>
+      </c>
+      <c r="D2165" s="3">
+        <v>57.14</v>
+      </c>
+      <c r="E2165" s="3">
+        <v>56.37</v>
+      </c>
+      <c r="F2165" s="3">
         <v>56.8</v>
       </c>
     </row>
     <row r="2166" spans="1:6">
-      <c r="A2166" s="4">
+      <c r="A2166" s="2">
         <v>46021</v>
       </c>
-      <c r="B2166" s="5" t="s">
+      <c r="B2166" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2166" s="5"/>
-      <c r="D2166" s="4"/>
-      <c r="E2166" s="5"/>
-      <c r="F2166" s="5">
+      <c r="C2166" s="3">
+        <v>48.26</v>
+      </c>
+      <c r="D2166" s="3">
+        <v>48.48</v>
+      </c>
+      <c r="E2166" s="3">
+        <v>48.04</v>
+      </c>
+      <c r="F2166" s="3">
         <v>48.3</v>
       </c>
     </row>
     <row r="2167" spans="1:6">
-      <c r="A2167" s="4">
+      <c r="A2167" s="2">
         <v>46021</v>
       </c>
-      <c r="B2167" s="5" t="s">
+      <c r="B2167" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2167" s="5"/>
-      <c r="D2167" s="4"/>
-      <c r="E2167" s="5"/>
-      <c r="F2167" s="5">
-        <v>41.6</v>
+      <c r="C2167" s="3">
+        <v>41.59</v>
+      </c>
+      <c r="D2167" s="3">
+        <v>42</v>
+      </c>
+      <c r="E2167" s="3">
+        <v>41.39</v>
+      </c>
+      <c r="F2167" s="3">
+        <v>41.7</v>
       </c>
     </row>
     <row r="2168" spans="1:6">
-      <c r="A2168" s="4">
+      <c r="A2168" s="2">
         <v>46021</v>
       </c>
-      <c r="B2168" s="5" t="s">
+      <c r="B2168" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2168" s="5"/>
-      <c r="D2168" s="4"/>
-      <c r="E2168" s="5"/>
-      <c r="F2168" s="5">
+      <c r="C2168" s="3">
+        <v>40.52</v>
+      </c>
+      <c r="D2168" s="3">
+        <v>40.55</v>
+      </c>
+      <c r="E2168" s="3">
+        <v>40.19</v>
+      </c>
+      <c r="F2168" s="3">
         <v>40.4</v>
       </c>
     </row>
     <row r="2169" spans="1:6">
-      <c r="A2169" s="4">
+      <c r="A2169" s="2">
         <v>46021</v>
       </c>
-      <c r="B2169" s="5" t="s">
+      <c r="B2169" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2169" s="5"/>
-      <c r="D2169" s="4"/>
-      <c r="E2169" s="5"/>
-      <c r="F2169" s="5">
+      <c r="C2169" s="3">
+        <v>54.02</v>
+      </c>
+      <c r="D2169" s="3">
+        <v>54.21</v>
+      </c>
+      <c r="E2169" s="3">
+        <v>53.74</v>
+      </c>
+      <c r="F2169" s="3">
         <v>54</v>
       </c>
     </row>
     <row r="2170" spans="1:6">
-      <c r="A2170" s="4">
+      <c r="A2170" s="2">
         <v>46021</v>
       </c>
-      <c r="B2170" s="5" t="s">
+      <c r="B2170" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2170" s="5"/>
-      <c r="D2170" s="4"/>
-      <c r="E2170" s="5"/>
-      <c r="F2170" s="5">
+      <c r="C2170" s="3">
+        <v>60.51</v>
+      </c>
+      <c r="D2170" s="3">
+        <v>61.04</v>
+      </c>
+      <c r="E2170" s="3">
+        <v>60.22</v>
+      </c>
+      <c r="F2170" s="3">
         <v>60.6</v>
       </c>
     </row>
@@ -44016,11 +44477,17 @@
       <c r="B2171" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2171" s="3"/>
-      <c r="D2171" s="2"/>
-      <c r="E2171" s="3"/>
+      <c r="C2171" s="3">
+        <v>59.01</v>
+      </c>
+      <c r="D2171" s="3">
+        <v>59.63</v>
+      </c>
+      <c r="E2171" s="3">
+        <v>58.77</v>
+      </c>
       <c r="F2171" s="3">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="2172" spans="1:6">
@@ -44030,11 +44497,17 @@
       <c r="B2172" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2172" s="3"/>
-      <c r="D2172" s="2"/>
-      <c r="E2172" s="3"/>
+      <c r="C2172" s="3">
+        <v>57.4</v>
+      </c>
+      <c r="D2172" s="3">
+        <v>58.13</v>
+      </c>
+      <c r="E2172" s="3">
+        <v>57.34</v>
+      </c>
       <c r="F2172" s="3">
-        <v>56.8</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="2173" spans="1:6">
@@ -44044,11 +44517,17 @@
       <c r="B2173" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2173" s="3"/>
-      <c r="D2173" s="2"/>
-      <c r="E2173" s="3"/>
+      <c r="C2173" s="3">
+        <v>50.87</v>
+      </c>
+      <c r="D2173" s="3">
+        <v>51.16</v>
+      </c>
+      <c r="E2173" s="3">
+        <v>50.68</v>
+      </c>
       <c r="F2173" s="3">
-        <v>48.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2174" spans="1:6">
@@ -44058,11 +44537,17 @@
       <c r="B2174" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2174" s="3"/>
-      <c r="D2174" s="2"/>
-      <c r="E2174" s="3"/>
+      <c r="C2174" s="3">
+        <v>42.33</v>
+      </c>
+      <c r="D2174" s="3">
+        <v>42.56</v>
+      </c>
+      <c r="E2174" s="3">
+        <v>42.26</v>
+      </c>
       <c r="F2174" s="3">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="2175" spans="1:6">
@@ -44072,11 +44557,17 @@
       <c r="B2175" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2175" s="3"/>
-      <c r="D2175" s="2"/>
-      <c r="E2175" s="3"/>
+      <c r="C2175" s="3">
+        <v>41.64</v>
+      </c>
+      <c r="D2175" s="3">
+        <v>42.09</v>
+      </c>
+      <c r="E2175" s="3">
+        <v>41.61</v>
+      </c>
       <c r="F2175" s="3">
-        <v>40.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="2176" spans="1:6">
@@ -44086,11 +44577,17 @@
       <c r="B2176" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2176" s="3"/>
-      <c r="D2176" s="2"/>
-      <c r="E2176" s="3"/>
+      <c r="C2176" s="3">
+        <v>54.91</v>
+      </c>
+      <c r="D2176" s="3">
+        <v>55.29</v>
+      </c>
+      <c r="E2176" s="3">
+        <v>54.84</v>
+      </c>
       <c r="F2176" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2177" spans="1:6">
@@ -44100,11 +44597,4665 @@
       <c r="B2177" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2177" s="3"/>
-      <c r="D2177" s="2"/>
-      <c r="E2177" s="3"/>
+      <c r="C2177" s="3">
+        <v>63.45</v>
+      </c>
+      <c r="D2177" s="3">
+        <v>64.14</v>
+      </c>
+      <c r="E2177" s="3">
+        <v>63.33</v>
+      </c>
       <c r="F2177" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:6">
+      <c r="A2178" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2178" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2178" s="3">
+        <v>59.71</v>
+      </c>
+      <c r="D2178" s="3">
+        <v>60.23</v>
+      </c>
+      <c r="E2178" s="3">
+        <v>59.49</v>
+      </c>
+      <c r="F2178" s="3">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:6">
+      <c r="A2179" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2179" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2179" s="3">
+        <v>57.95</v>
+      </c>
+      <c r="D2179" s="3">
+        <v>58.07</v>
+      </c>
+      <c r="E2179" s="3">
+        <v>57.93</v>
+      </c>
+      <c r="F2179" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:6">
+      <c r="A2180" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2180" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2180" s="3">
+        <v>51.34</v>
+      </c>
+      <c r="D2180" s="3">
+        <v>51.5</v>
+      </c>
+      <c r="E2180" s="3">
+        <v>51.12</v>
+      </c>
+      <c r="F2180" s="3">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:6">
+      <c r="A2181" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2181" s="3">
+        <v>42.97</v>
+      </c>
+      <c r="D2181" s="3">
+        <v>43.23</v>
+      </c>
+      <c r="E2181" s="3">
+        <v>42.81</v>
+      </c>
+      <c r="F2181" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:6">
+      <c r="A2182" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2182" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2182" s="3">
+        <v>42.65</v>
+      </c>
+      <c r="D2182" s="3">
+        <v>43.29</v>
+      </c>
+      <c r="E2182" s="3">
+        <v>42.58</v>
+      </c>
+      <c r="F2182" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:6">
+      <c r="A2183" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2183" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2183" s="3">
+        <v>55.13</v>
+      </c>
+      <c r="D2183" s="3">
+        <v>55.3</v>
+      </c>
+      <c r="E2183" s="3">
+        <v>55.09</v>
+      </c>
+      <c r="F2183" s="3">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:6">
+      <c r="A2184" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B2184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2184" s="3">
+        <v>64.86</v>
+      </c>
+      <c r="D2184" s="3">
+        <v>65.06</v>
+      </c>
+      <c r="E2184" s="3">
+        <v>64.56</v>
+      </c>
+      <c r="F2184" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:6">
+      <c r="A2185" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2185" s="3">
+        <v>59.92</v>
+      </c>
+      <c r="D2185" s="3">
+        <v>59.96</v>
+      </c>
+      <c r="E2185" s="3">
+        <v>59.73</v>
+      </c>
+      <c r="F2185" s="3">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:6">
+      <c r="A2186" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2186" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2186" s="3">
+        <v>58.52</v>
+      </c>
+      <c r="D2186" s="3">
+        <v>58.8</v>
+      </c>
+      <c r="E2186" s="3">
+        <v>57.65</v>
+      </c>
+      <c r="F2186" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:6">
+      <c r="A2187" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2187" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2187" s="3">
+        <v>51.49</v>
+      </c>
+      <c r="D2187" s="3">
+        <v>51.61</v>
+      </c>
+      <c r="E2187" s="3">
+        <v>51.35</v>
+      </c>
+      <c r="F2187" s="3">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:6">
+      <c r="A2188" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2188" s="3">
+        <v>43.39</v>
+      </c>
+      <c r="D2188" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="E2188" s="3">
+        <v>43.28</v>
+      </c>
+      <c r="F2188" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:6">
+      <c r="A2189" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2189" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2189" s="3">
+        <v>43.48</v>
+      </c>
+      <c r="D2189" s="3">
+        <v>43.57</v>
+      </c>
+      <c r="E2189" s="3">
+        <v>43.38</v>
+      </c>
+      <c r="F2189" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:6">
+      <c r="A2190" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2190" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2190" s="3">
+        <v>55.36</v>
+      </c>
+      <c r="D2190" s="3">
+        <v>55.81</v>
+      </c>
+      <c r="E2190" s="3">
+        <v>55.29</v>
+      </c>
+      <c r="F2190" s="3">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:6">
+      <c r="A2191" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B2191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2191" s="3">
+        <v>65.49</v>
+      </c>
+      <c r="D2191" s="3">
+        <v>65.58</v>
+      </c>
+      <c r="E2191" s="3">
+        <v>64.68</v>
+      </c>
+      <c r="F2191" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:6">
+      <c r="A2192" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2192" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2192" s="3">
+        <v>60.48</v>
+      </c>
+      <c r="D2192" s="3">
+        <v>60.89</v>
+      </c>
+      <c r="E2192" s="3">
+        <v>60.3</v>
+      </c>
+      <c r="F2192" s="3">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:6">
+      <c r="A2193" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2193" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2193" s="3">
+        <v>57.77</v>
+      </c>
+      <c r="D2193" s="3">
+        <v>58.04</v>
+      </c>
+      <c r="E2193" s="3">
+        <v>57.58</v>
+      </c>
+      <c r="F2193" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:6">
+      <c r="A2194" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2194" s="3">
+        <v>51.03</v>
+      </c>
+      <c r="D2194" s="3">
+        <v>51.23</v>
+      </c>
+      <c r="E2194" s="3">
+        <v>50.97</v>
+      </c>
+      <c r="F2194" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:6">
+      <c r="A2195" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2195" s="3">
+        <v>43.52</v>
+      </c>
+      <c r="D2195" s="3">
+        <v>43.61</v>
+      </c>
+      <c r="E2195" s="3">
+        <v>43.49</v>
+      </c>
+      <c r="F2195" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:6">
+      <c r="A2196" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2196" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2196" s="3">
+        <v>43.78</v>
+      </c>
+      <c r="D2196" s="3">
+        <v>43.97</v>
+      </c>
+      <c r="E2196" s="3">
+        <v>43.5</v>
+      </c>
+      <c r="F2196" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:6">
+      <c r="A2197" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2197" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2197" s="3">
+        <v>55.59</v>
+      </c>
+      <c r="D2197" s="3">
+        <v>55.8</v>
+      </c>
+      <c r="E2197" s="3">
+        <v>55.3</v>
+      </c>
+      <c r="F2197" s="3">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:6">
+      <c r="A2198" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B2198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2198" s="3">
+        <v>65.67</v>
+      </c>
+      <c r="D2198" s="3">
+        <v>66.27</v>
+      </c>
+      <c r="E2198" s="3">
+        <v>65.49</v>
+      </c>
+      <c r="F2198" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:6">
+      <c r="A2199" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2199" s="3">
+        <v>60.75</v>
+      </c>
+      <c r="D2199" s="3">
+        <v>60.76</v>
+      </c>
+      <c r="E2199" s="3">
+        <v>60.06</v>
+      </c>
+      <c r="F2199" s="3">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:6">
+      <c r="A2200" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2200" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2200" s="3">
+        <v>58.16</v>
+      </c>
+      <c r="D2200" s="3">
+        <v>58.25</v>
+      </c>
+      <c r="E2200" s="3">
+        <v>58.02</v>
+      </c>
+      <c r="F2200" s="3">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:6">
+      <c r="A2201" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2201" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2201" s="3">
+        <v>51.6</v>
+      </c>
+      <c r="D2201" s="3">
+        <v>52.3</v>
+      </c>
+      <c r="E2201" s="3">
+        <v>51.55</v>
+      </c>
+      <c r="F2201" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:6">
+      <c r="A2202" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2202" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2202" s="3">
+        <v>43.16</v>
+      </c>
+      <c r="D2202" s="3">
+        <v>43.51</v>
+      </c>
+      <c r="E2202" s="3">
+        <v>43.02</v>
+      </c>
+      <c r="F2202" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:6">
+      <c r="A2203" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2203" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2203" s="3">
+        <v>43.51</v>
+      </c>
+      <c r="D2203" s="3">
+        <v>43.6</v>
+      </c>
+      <c r="E2203" s="3">
+        <v>43.43</v>
+      </c>
+      <c r="F2203" s="3">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:6">
+      <c r="A2204" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2204" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2204" s="3">
+        <v>55.54</v>
+      </c>
+      <c r="D2204" s="3">
+        <v>55.75</v>
+      </c>
+      <c r="E2204" s="3">
+        <v>55.37</v>
+      </c>
+      <c r="F2204" s="3">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:6">
+      <c r="A2205" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B2205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2205" s="3">
+        <v>65.66</v>
+      </c>
+      <c r="D2205" s="3">
+        <v>66.05</v>
+      </c>
+      <c r="E2205" s="3">
+        <v>65.36</v>
+      </c>
+      <c r="F2205" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:6">
+      <c r="A2206" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2206" s="3">
+        <v>60.83</v>
+      </c>
+      <c r="D2206" s="3">
+        <v>61.1</v>
+      </c>
+      <c r="E2206" s="3">
+        <v>60.78</v>
+      </c>
+      <c r="F2206" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:6">
+      <c r="A2207" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2207" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2207" s="3">
+        <v>58.4</v>
+      </c>
+      <c r="D2207" s="3">
+        <v>58.8</v>
+      </c>
+      <c r="E2207" s="3">
+        <v>58.32</v>
+      </c>
+      <c r="F2207" s="3">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:6">
+      <c r="A2208" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2208" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2208" s="3">
+        <v>51.49</v>
+      </c>
+      <c r="D2208" s="3">
+        <v>52.32</v>
+      </c>
+      <c r="E2208" s="3">
+        <v>51.3</v>
+      </c>
+      <c r="F2208" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:6">
+      <c r="A2209" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2209" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2209" s="3">
+        <v>43.94</v>
+      </c>
+      <c r="D2209" s="3">
+        <v>44.17</v>
+      </c>
+      <c r="E2209" s="3">
+        <v>43.74</v>
+      </c>
+      <c r="F2209" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:6">
+      <c r="A2210" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2210" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2210" s="3">
+        <v>43.98</v>
+      </c>
+      <c r="D2210" s="3">
+        <v>44.11</v>
+      </c>
+      <c r="E2210" s="3">
+        <v>43.77</v>
+      </c>
+      <c r="F2210" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:6">
+      <c r="A2211" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2211" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2211" s="3">
+        <v>55.75</v>
+      </c>
+      <c r="D2211" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="E2211" s="3">
+        <v>55.56</v>
+      </c>
+      <c r="F2211" s="3">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:6">
+      <c r="A2212" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B2212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2212" s="3">
+        <v>66.63</v>
+      </c>
+      <c r="D2212" s="3">
+        <v>67.32</v>
+      </c>
+      <c r="E2212" s="3">
+        <v>66.52</v>
+      </c>
+      <c r="F2212" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:6">
+      <c r="A2213" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2213" s="3">
+        <v>60.61</v>
+      </c>
+      <c r="D2213" s="3">
+        <v>61.14</v>
+      </c>
+      <c r="E2213" s="3">
+        <v>60.45</v>
+      </c>
+      <c r="F2213" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:6">
+      <c r="A2214" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2214" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2214" s="3">
+        <v>58.55</v>
+      </c>
+      <c r="D2214" s="3">
+        <v>58.74</v>
+      </c>
+      <c r="E2214" s="3">
+        <v>58.39</v>
+      </c>
+      <c r="F2214" s="3">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:6">
+      <c r="A2215" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2215" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2215" s="3">
+        <v>52.24</v>
+      </c>
+      <c r="D2215" s="3">
+        <v>52.44</v>
+      </c>
+      <c r="E2215" s="3">
+        <v>51.97</v>
+      </c>
+      <c r="F2215" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:6">
+      <c r="A2216" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2216" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2216" s="3">
+        <v>43.78</v>
+      </c>
+      <c r="D2216" s="3">
+        <v>44.14</v>
+      </c>
+      <c r="E2216" s="3">
+        <v>43.61</v>
+      </c>
+      <c r="F2216" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:6">
+      <c r="A2217" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2217" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2217" s="3">
+        <v>43.84</v>
+      </c>
+      <c r="D2217" s="3">
+        <v>44.17</v>
+      </c>
+      <c r="E2217" s="3">
+        <v>43.69</v>
+      </c>
+      <c r="F2217" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:6">
+      <c r="A2218" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2218" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2218" s="3">
+        <v>56</v>
+      </c>
+      <c r="D2218" s="3">
+        <v>56.34</v>
+      </c>
+      <c r="E2218" s="3">
+        <v>55.95</v>
+      </c>
+      <c r="F2218" s="3">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:6">
+      <c r="A2219" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B2219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2219" s="3">
+        <v>66.8</v>
+      </c>
+      <c r="D2219" s="3">
+        <v>67.36</v>
+      </c>
+      <c r="E2219" s="3">
+        <v>66.5</v>
+      </c>
+      <c r="F2219" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:6">
+      <c r="A2220" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2220" s="3">
+        <v>61.41</v>
+      </c>
+      <c r="D2220" s="3">
+        <v>61.63</v>
+      </c>
+      <c r="E2220" s="3">
+        <v>61.23</v>
+      </c>
+      <c r="F2220" s="3">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:6">
+      <c r="A2221" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2221" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2221" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D2221" s="3">
+        <v>58.71</v>
+      </c>
+      <c r="E2221" s="3">
+        <v>58.17</v>
+      </c>
+      <c r="F2221" s="3">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:6">
+      <c r="A2222" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2222" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2222" s="3">
+        <v>52.85</v>
+      </c>
+      <c r="D2222" s="3">
+        <v>53.05</v>
+      </c>
+      <c r="E2222" s="3">
+        <v>52.63</v>
+      </c>
+      <c r="F2222" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:6">
+      <c r="A2223" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2223" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2223" s="3">
+        <v>43.76</v>
+      </c>
+      <c r="D2223" s="3">
+        <v>44.03</v>
+      </c>
+      <c r="E2223" s="3">
+        <v>43.7</v>
+      </c>
+      <c r="F2223" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:6">
+      <c r="A2224" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2224" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2224" s="3">
+        <v>44.43</v>
+      </c>
+      <c r="D2224" s="3">
+        <v>44.82</v>
+      </c>
+      <c r="E2224" s="3">
+        <v>44.21</v>
+      </c>
+      <c r="F2224" s="3">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:6">
+      <c r="A2225" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2225" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2225" s="3">
+        <v>55.68</v>
+      </c>
+      <c r="D2225" s="3">
+        <v>56.45</v>
+      </c>
+      <c r="E2225" s="3">
+        <v>55.5</v>
+      </c>
+      <c r="F2225" s="3">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:6">
+      <c r="A2226" s="2">
+        <v>46034</v>
+      </c>
+      <c r="B2226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2226" s="3">
+        <v>67.64</v>
+      </c>
+      <c r="D2226" s="3">
+        <v>68.4</v>
+      </c>
+      <c r="E2226" s="3">
+        <v>67.42</v>
+      </c>
+      <c r="F2226" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:6">
+      <c r="A2227" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2227" s="3">
+        <v>61.06</v>
+      </c>
+      <c r="D2227" s="3">
+        <v>61.63</v>
+      </c>
+      <c r="E2227" s="3">
+        <v>60.94</v>
+      </c>
+      <c r="F2227" s="3">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:6">
+      <c r="A2228" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2228" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2228" s="3">
+        <v>58.92</v>
+      </c>
+      <c r="D2228" s="3">
+        <v>59.2</v>
+      </c>
+      <c r="E2228" s="3">
+        <v>58.21</v>
+      </c>
+      <c r="F2228" s="3">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:6">
+      <c r="A2229" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2229" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2229" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="D2229" s="3">
+        <v>53.53</v>
+      </c>
+      <c r="E2229" s="3">
+        <v>53.28</v>
+      </c>
+      <c r="F2229" s="3">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:6">
+      <c r="A2230" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2230" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2230" s="3">
+        <v>44.47</v>
+      </c>
+      <c r="D2230" s="3">
+        <v>44.81</v>
+      </c>
+      <c r="E2230" s="3">
+        <v>44.29</v>
+      </c>
+      <c r="F2230" s="3">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:6">
+      <c r="A2231" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2231" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2231" s="3">
+        <v>44.28</v>
+      </c>
+      <c r="D2231" s="3">
+        <v>44.67</v>
+      </c>
+      <c r="E2231" s="3">
+        <v>44.21</v>
+      </c>
+      <c r="F2231" s="3">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:6">
+      <c r="A2232" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2232" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2232" s="3">
+        <v>56.5</v>
+      </c>
+      <c r="D2232" s="3">
+        <v>56.72</v>
+      </c>
+      <c r="E2232" s="3">
+        <v>56.43</v>
+      </c>
+      <c r="F2232" s="3">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:6">
+      <c r="A2233" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B2233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2233" s="3">
+        <v>68.97</v>
+      </c>
+      <c r="D2233" s="3">
+        <v>69.08</v>
+      </c>
+      <c r="E2233" s="3">
+        <v>68.66</v>
+      </c>
+      <c r="F2233" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:6">
+      <c r="A2234" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2234" s="3">
+        <v>61.91</v>
+      </c>
+      <c r="D2234" s="3">
+        <v>62.37</v>
+      </c>
+      <c r="E2234" s="3">
+        <v>61.85</v>
+      </c>
+      <c r="F2234" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:6">
+      <c r="A2235" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2235" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2235" s="3">
+        <v>58.71</v>
+      </c>
+      <c r="D2235" s="3">
+        <v>58.99</v>
+      </c>
+      <c r="E2235" s="3">
+        <v>58.56</v>
+      </c>
+      <c r="F2235" s="3">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:6">
+      <c r="A2236" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2236" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2236" s="3">
+        <v>53.58</v>
+      </c>
+      <c r="D2236" s="3">
+        <v>53.73</v>
+      </c>
+      <c r="E2236" s="3">
+        <v>53.38</v>
+      </c>
+      <c r="F2236" s="3">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:6">
+      <c r="A2237" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2237" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2237" s="3">
+        <v>44.87</v>
+      </c>
+      <c r="D2237" s="3">
+        <v>45.29</v>
+      </c>
+      <c r="E2237" s="3">
+        <v>44.69</v>
+      </c>
+      <c r="F2237" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:6">
+      <c r="A2238" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2238" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2238" s="3">
+        <v>44.31</v>
+      </c>
+      <c r="D2238" s="3">
+        <v>44.51</v>
+      </c>
+      <c r="E2238" s="3">
+        <v>44.17</v>
+      </c>
+      <c r="F2238" s="3">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:6">
+      <c r="A2239" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2239" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2239" s="3">
+        <v>56.57</v>
+      </c>
+      <c r="D2239" s="3">
+        <v>56.67</v>
+      </c>
+      <c r="E2239" s="3">
+        <v>56.38</v>
+      </c>
+      <c r="F2239" s="3">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:6">
+      <c r="A2240" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B2240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2240" s="3">
+        <v>69.75</v>
+      </c>
+      <c r="D2240" s="3">
+        <v>70</v>
+      </c>
+      <c r="E2240" s="3">
+        <v>69.72</v>
+      </c>
+      <c r="F2240" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:6">
+      <c r="A2241" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2241" s="3">
+        <v>62.4</v>
+      </c>
+      <c r="D2241" s="3">
+        <v>62.78</v>
+      </c>
+      <c r="E2241" s="3">
+        <v>62.38</v>
+      </c>
+      <c r="F2241" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:6">
+      <c r="A2242" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2242" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2242" s="3">
+        <v>58.69</v>
+      </c>
+      <c r="D2242" s="3">
+        <v>58.72</v>
+      </c>
+      <c r="E2242" s="3">
+        <v>58.6</v>
+      </c>
+      <c r="F2242" s="3">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:6">
+      <c r="A2243" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2243" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2243" s="3">
+        <v>54.27</v>
+      </c>
+      <c r="D2243" s="3">
+        <v>54.86</v>
+      </c>
+      <c r="E2243" s="3">
+        <v>54.14</v>
+      </c>
+      <c r="F2243" s="3">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:6">
+      <c r="A2244" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2244" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2244" s="3">
+        <v>45.46</v>
+      </c>
+      <c r="D2244" s="3">
+        <v>45.8</v>
+      </c>
+      <c r="E2244" s="3">
+        <v>45.34</v>
+      </c>
+      <c r="F2244" s="3">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:6">
+      <c r="A2245" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2245" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2245" s="3">
+        <v>44.9</v>
+      </c>
+      <c r="D2245" s="3">
+        <v>45.02</v>
+      </c>
+      <c r="E2245" s="3">
+        <v>44.84</v>
+      </c>
+      <c r="F2245" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:6">
+      <c r="A2246" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2246" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2246" s="3">
+        <v>56.94</v>
+      </c>
+      <c r="D2246" s="3">
+        <v>57.4</v>
+      </c>
+      <c r="E2246" s="3">
+        <v>56.9</v>
+      </c>
+      <c r="F2246" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:6">
+      <c r="A2247" s="2">
+        <v>46037</v>
+      </c>
+      <c r="B2247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2247" s="3">
+        <v>70.73</v>
+      </c>
+      <c r="D2247" s="3">
+        <v>71</v>
+      </c>
+      <c r="E2247" s="3">
+        <v>70.67</v>
+      </c>
+      <c r="F2247" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:6">
+      <c r="A2248" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2248" s="3">
+        <v>62.34</v>
+      </c>
+      <c r="D2248" s="3">
+        <v>62.95</v>
+      </c>
+      <c r="E2248" s="3">
+        <v>62.12</v>
+      </c>
+      <c r="F2248" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:6">
+      <c r="A2249" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2249" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2249" s="3">
+        <v>61.01</v>
+      </c>
+      <c r="D2249" s="3">
+        <v>61.24</v>
+      </c>
+      <c r="E2249" s="3">
         <v>60.8</v>
+      </c>
+      <c r="F2249" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:6">
+      <c r="A2250" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2250" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2250" s="3">
+        <v>54.7</v>
+      </c>
+      <c r="D2250" s="3">
+        <v>55.03</v>
+      </c>
+      <c r="E2250" s="3">
+        <v>54.51</v>
+      </c>
+      <c r="F2250" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:6">
+      <c r="A2251" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2251" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2251" s="3">
+        <v>45.25</v>
+      </c>
+      <c r="D2251" s="3">
+        <v>45.53</v>
+      </c>
+      <c r="E2251" s="3">
+        <v>45.19</v>
+      </c>
+      <c r="F2251" s="3">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:6">
+      <c r="A2252" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2252" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2252" s="3">
+        <v>44.81</v>
+      </c>
+      <c r="D2252" s="3">
+        <v>45.01</v>
+      </c>
+      <c r="E2252" s="3">
+        <v>44.67</v>
+      </c>
+      <c r="F2252" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:6">
+      <c r="A2253" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2253" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2253" s="3">
+        <v>56.82</v>
+      </c>
+      <c r="D2253" s="3">
+        <v>57.05</v>
+      </c>
+      <c r="E2253" s="3">
+        <v>56.56</v>
+      </c>
+      <c r="F2253" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:6">
+      <c r="A2254" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B2254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2254" s="3">
+        <v>70.75</v>
+      </c>
+      <c r="D2254" s="3">
+        <v>71.4</v>
+      </c>
+      <c r="E2254" s="3">
+        <v>70.52</v>
+      </c>
+      <c r="F2254" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:6">
+      <c r="A2255" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2255" s="3">
+        <v>62.62</v>
+      </c>
+      <c r="D2255" s="3">
+        <v>62.67</v>
+      </c>
+      <c r="E2255" s="3">
+        <v>62.43</v>
+      </c>
+      <c r="F2255" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:6">
+      <c r="A2256" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2256" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2256" s="3">
+        <v>61.13</v>
+      </c>
+      <c r="D2256" s="3">
+        <v>61.26</v>
+      </c>
+      <c r="E2256" s="3">
+        <v>60.98</v>
+      </c>
+      <c r="F2256" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:6">
+      <c r="A2257" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2257" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2257" s="3">
+        <v>54.95</v>
+      </c>
+      <c r="D2257" s="3">
+        <v>55.16</v>
+      </c>
+      <c r="E2257" s="3">
+        <v>54.67</v>
+      </c>
+      <c r="F2257" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:6">
+      <c r="A2258" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2258" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2258" s="3">
+        <v>45.97</v>
+      </c>
+      <c r="D2258" s="3">
+        <v>46.32</v>
+      </c>
+      <c r="E2258" s="3">
+        <v>45.78</v>
+      </c>
+      <c r="F2258" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:6">
+      <c r="A2259" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2259" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2259" s="3">
+        <v>45.24</v>
+      </c>
+      <c r="D2259" s="3">
+        <v>45.32</v>
+      </c>
+      <c r="E2259" s="3">
+        <v>45.18</v>
+      </c>
+      <c r="F2259" s="3">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:6">
+      <c r="A2260" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2260" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2260" s="3">
+        <v>57.43</v>
+      </c>
+      <c r="D2260" s="3">
+        <v>57.5</v>
+      </c>
+      <c r="E2260" s="3">
+        <v>56.72</v>
+      </c>
+      <c r="F2260" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:6">
+      <c r="A2261" s="2">
+        <v>46041</v>
+      </c>
+      <c r="B2261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2261" s="3">
+        <v>70.93</v>
+      </c>
+      <c r="D2261" s="3">
+        <v>71.17</v>
+      </c>
+      <c r="E2261" s="3">
+        <v>70.6</v>
+      </c>
+      <c r="F2261" s="3">
+        <v>70.9</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:6">
+      <c r="A2262" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2262" s="3">
+        <v>61.95</v>
+      </c>
+      <c r="D2262" s="3">
+        <v>62.91</v>
+      </c>
+      <c r="E2262" s="3">
+        <v>61.76</v>
+      </c>
+      <c r="F2262" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:6">
+      <c r="A2263" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2263" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2263" s="3">
+        <v>60.63</v>
+      </c>
+      <c r="D2263" s="3">
+        <v>61.62</v>
+      </c>
+      <c r="E2263" s="3">
+        <v>60.55</v>
+      </c>
+      <c r="F2263" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:6">
+      <c r="A2264" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2264" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2264" s="3">
+        <v>54.55</v>
+      </c>
+      <c r="D2264" s="3">
+        <v>54.75</v>
+      </c>
+      <c r="E2264" s="3">
+        <v>54.31</v>
+      </c>
+      <c r="F2264" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:6">
+      <c r="A2265" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2265" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2265" s="3">
+        <v>46.37</v>
+      </c>
+      <c r="D2265" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="E2265" s="3">
+        <v>46.19</v>
+      </c>
+      <c r="F2265" s="3">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:6">
+      <c r="A2266" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2266" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2266" s="3">
+        <v>45.43</v>
+      </c>
+      <c r="D2266" s="3">
+        <v>45.58</v>
+      </c>
+      <c r="E2266" s="3">
+        <v>45.39</v>
+      </c>
+      <c r="F2266" s="3">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:6">
+      <c r="A2267" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2267" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2267" s="3">
+        <v>57.36</v>
+      </c>
+      <c r="D2267" s="3">
+        <v>57.52</v>
+      </c>
+      <c r="E2267" s="3">
+        <v>56.77</v>
+      </c>
+      <c r="F2267" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:6">
+      <c r="A2268" s="2">
+        <v>46042</v>
+      </c>
+      <c r="B2268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2268" s="3">
+        <v>70.8</v>
+      </c>
+      <c r="D2268" s="3">
+        <v>70.93</v>
+      </c>
+      <c r="E2268" s="3">
+        <v>70.66</v>
+      </c>
+      <c r="F2268" s="3">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:6">
+      <c r="A2269" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2269" s="3">
+        <v>62.76</v>
+      </c>
+      <c r="D2269" s="3">
+        <v>62.77</v>
+      </c>
+      <c r="E2269" s="3">
+        <v>62.05</v>
+      </c>
+      <c r="F2269" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:6">
+      <c r="A2270" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2270" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2270" s="3">
+        <v>61.4</v>
+      </c>
+      <c r="D2270" s="3">
+        <v>61.49</v>
+      </c>
+      <c r="E2270" s="3">
+        <v>60.96</v>
+      </c>
+      <c r="F2270" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:6">
+      <c r="A2271" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2271" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2271" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="D2271" s="3">
+        <v>54.93</v>
+      </c>
+      <c r="E2271" s="3">
+        <v>54.67</v>
+      </c>
+      <c r="F2271" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:6">
+      <c r="A2272" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2272" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2272" s="3">
+        <v>46.21</v>
+      </c>
+      <c r="D2272" s="3">
+        <v>46.81</v>
+      </c>
+      <c r="E2272" s="3">
+        <v>46.08</v>
+      </c>
+      <c r="F2272" s="3">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:6">
+      <c r="A2273" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2273" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2273" s="3">
+        <v>45.66</v>
+      </c>
+      <c r="D2273" s="3">
+        <v>46.04</v>
+      </c>
+      <c r="E2273" s="3">
+        <v>45.61</v>
+      </c>
+      <c r="F2273" s="3">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:6">
+      <c r="A2274" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2274" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2274" s="3">
+        <v>56.71</v>
+      </c>
+      <c r="D2274" s="3">
+        <v>57.04</v>
+      </c>
+      <c r="E2274" s="3">
+        <v>56.45</v>
+      </c>
+      <c r="F2274" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:6">
+      <c r="A2275" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B2275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2275" s="3">
+        <v>70.71</v>
+      </c>
+      <c r="D2275" s="3">
+        <v>71.05</v>
+      </c>
+      <c r="E2275" s="3">
+        <v>70.49</v>
+      </c>
+      <c r="F2275" s="3">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:6">
+      <c r="A2276" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2276" s="3">
+        <v>62.63</v>
+      </c>
+      <c r="D2276" s="3">
+        <v>62.8</v>
+      </c>
+      <c r="E2276" s="3">
+        <v>62.58</v>
+      </c>
+      <c r="F2276" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:6">
+      <c r="A2277" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2277" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2277" s="3">
+        <v>61.26</v>
+      </c>
+      <c r="D2277" s="3">
+        <v>61.31</v>
+      </c>
+      <c r="E2277" s="3">
+        <v>60.75</v>
+      </c>
+      <c r="F2277" s="3">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:6">
+      <c r="A2278" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2278" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2278" s="3">
+        <v>54.49</v>
+      </c>
+      <c r="D2278" s="3">
+        <v>54.83</v>
+      </c>
+      <c r="E2278" s="3">
+        <v>54.29</v>
+      </c>
+      <c r="F2278" s="3">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:6">
+      <c r="A2279" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2279" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2279" s="3">
+        <v>46.79</v>
+      </c>
+      <c r="D2279" s="3">
+        <v>47</v>
+      </c>
+      <c r="E2279" s="3">
+        <v>46.39</v>
+      </c>
+      <c r="F2279" s="3">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:6">
+      <c r="A2280" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2280" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2280" s="3">
+        <v>45.85</v>
+      </c>
+      <c r="D2280" s="3">
+        <v>46.16</v>
+      </c>
+      <c r="E2280" s="3">
+        <v>45.79</v>
+      </c>
+      <c r="F2280" s="3">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:6">
+      <c r="A2281" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2281" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2281" s="3">
+        <v>57.19</v>
+      </c>
+      <c r="D2281" s="3">
+        <v>57.57</v>
+      </c>
+      <c r="E2281" s="3">
+        <v>57.09</v>
+      </c>
+      <c r="F2281" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:6">
+      <c r="A2282" s="2">
+        <v>46044</v>
+      </c>
+      <c r="B2282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2282" s="3">
+        <v>71.25</v>
+      </c>
+      <c r="D2282" s="3">
+        <v>71.48</v>
+      </c>
+      <c r="E2282" s="3">
+        <v>70.28</v>
+      </c>
+      <c r="F2282" s="3">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:6">
+      <c r="A2283" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2283" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2283" s="3">
+        <v>62.3</v>
+      </c>
+      <c r="D2283" s="3">
+        <v>62.84</v>
+      </c>
+      <c r="E2283" s="3">
+        <v>62.14</v>
+      </c>
+      <c r="F2283" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:6">
+      <c r="A2284" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2284" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2284" s="3">
+        <v>60.85</v>
+      </c>
+      <c r="D2284" s="3">
+        <v>61.14</v>
+      </c>
+      <c r="E2284" s="3">
+        <v>60.29</v>
+      </c>
+      <c r="F2284" s="3">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:6">
+      <c r="A2285" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2285" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2285" s="3">
+        <v>54.55</v>
+      </c>
+      <c r="D2285" s="3">
+        <v>54.79</v>
+      </c>
+      <c r="E2285" s="3">
+        <v>54.31</v>
+      </c>
+      <c r="F2285" s="3">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:6">
+      <c r="A2286" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2286" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2286" s="3">
+        <v>46.98</v>
+      </c>
+      <c r="D2286" s="3">
+        <v>47.08</v>
+      </c>
+      <c r="E2286" s="3">
+        <v>46.88</v>
+      </c>
+      <c r="F2286" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:6">
+      <c r="A2287" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2287" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2287" s="3">
+        <v>45.97</v>
+      </c>
+      <c r="D2287" s="3">
+        <v>46.13</v>
+      </c>
+      <c r="E2287" s="3">
+        <v>45.83</v>
+      </c>
+      <c r="F2287" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:6">
+      <c r="A2288" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2288" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2288" s="3">
+        <v>57.13</v>
+      </c>
+      <c r="D2288" s="3">
+        <v>57.61</v>
+      </c>
+      <c r="E2288" s="3">
+        <v>56.87</v>
+      </c>
+      <c r="F2288" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:6">
+      <c r="A2289" s="2">
+        <v>46045</v>
+      </c>
+      <c r="B2289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2289" s="3">
+        <v>70.62</v>
+      </c>
+      <c r="D2289" s="3">
+        <v>70.82</v>
+      </c>
+      <c r="E2289" s="3">
+        <v>70.34</v>
+      </c>
+      <c r="F2289" s="3">
+        <v>70.6</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:6">
+      <c r="A2290" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2290" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2290" s="3">
+        <v>62.61</v>
+      </c>
+      <c r="D2290" s="3">
+        <v>62.84</v>
+      </c>
+      <c r="E2290" s="3">
+        <v>62.42</v>
+      </c>
+      <c r="F2290" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:6">
+      <c r="A2291" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2291" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2291" s="3">
+        <v>60.82</v>
+      </c>
+      <c r="D2291" s="3">
+        <v>61.1</v>
+      </c>
+      <c r="E2291" s="3">
+        <v>60.66</v>
+      </c>
+      <c r="F2291" s="3">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:6">
+      <c r="A2292" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2292" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2292" s="3">
+        <v>54.09</v>
+      </c>
+      <c r="D2292" s="3">
+        <v>54.79</v>
+      </c>
+      <c r="E2292" s="3">
+        <v>53.88</v>
+      </c>
+      <c r="F2292" s="3">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:6">
+      <c r="A2293" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2293" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2293" s="3">
+        <v>47.33</v>
+      </c>
+      <c r="D2293" s="3">
+        <v>47.81</v>
+      </c>
+      <c r="E2293" s="3">
+        <v>47.33</v>
+      </c>
+      <c r="F2293" s="3">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:6">
+      <c r="A2294" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2294" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2294" s="3">
+        <v>46.12</v>
+      </c>
+      <c r="D2294" s="3">
+        <v>46.25</v>
+      </c>
+      <c r="E2294" s="3">
+        <v>45.97</v>
+      </c>
+      <c r="F2294" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:6">
+      <c r="A2295" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2295" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2295" s="3">
+        <v>57.74</v>
+      </c>
+      <c r="D2295" s="3">
+        <v>57.97</v>
+      </c>
+      <c r="E2295" s="3">
+        <v>57.02</v>
+      </c>
+      <c r="F2295" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:6">
+      <c r="A2296" s="2">
+        <v>46048</v>
+      </c>
+      <c r="B2296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2296" s="3">
+        <v>70.17</v>
+      </c>
+      <c r="D2296" s="3">
+        <v>70.98</v>
+      </c>
+      <c r="E2296" s="3">
+        <v>70.07</v>
+      </c>
+      <c r="F2296" s="3">
+        <v>70.6</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:6">
+      <c r="A2297" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2297" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2297" s="3">
+        <v>62.25</v>
+      </c>
+      <c r="D2297" s="3">
+        <v>62.84</v>
+      </c>
+      <c r="E2297" s="3">
+        <v>62.13</v>
+      </c>
+      <c r="F2297" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:6">
+      <c r="A2298" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2298" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2298" s="3">
+        <v>60.79</v>
+      </c>
+      <c r="D2298" s="3">
+        <v>60.82</v>
+      </c>
+      <c r="E2298" s="3">
+        <v>60.69</v>
+      </c>
+      <c r="F2298" s="3">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:6">
+      <c r="A2299" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2299" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2299" s="3">
+        <v>54.19</v>
+      </c>
+      <c r="D2299" s="3">
+        <v>54.4</v>
+      </c>
+      <c r="E2299" s="3">
+        <v>53.9</v>
+      </c>
+      <c r="F2299" s="3">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:6">
+      <c r="A2300" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2300" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2300" s="3">
+        <v>47.9</v>
+      </c>
+      <c r="D2300" s="3">
+        <v>48.15</v>
+      </c>
+      <c r="E2300" s="3">
+        <v>47.84</v>
+      </c>
+      <c r="F2300" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:6">
+      <c r="A2301" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2301" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2301" s="3">
+        <v>46.31</v>
+      </c>
+      <c r="D2301" s="3">
+        <v>46.38</v>
+      </c>
+      <c r="E2301" s="3">
+        <v>45.94</v>
+      </c>
+      <c r="F2301" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:6">
+      <c r="A2302" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2302" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2302" s="3">
+        <v>56.82</v>
+      </c>
+      <c r="D2302" s="3">
+        <v>57.37</v>
+      </c>
+      <c r="E2302" s="3">
+        <v>56.57</v>
+      </c>
+      <c r="F2302" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:6">
+      <c r="A2303" s="2">
+        <v>46049</v>
+      </c>
+      <c r="B2303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2303" s="3">
+        <v>70.5</v>
+      </c>
+      <c r="D2303" s="3">
+        <v>70.73</v>
+      </c>
+      <c r="E2303" s="3">
+        <v>70.41</v>
+      </c>
+      <c r="F2303" s="3">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:6">
+      <c r="A2304" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2304" s="3">
+        <v>62.64</v>
+      </c>
+      <c r="D2304" s="3">
+        <v>63.07</v>
+      </c>
+      <c r="E2304" s="3">
+        <v>62.58</v>
+      </c>
+      <c r="F2304" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:6">
+      <c r="A2305" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2305" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2305" s="3">
+        <v>60.66</v>
+      </c>
+      <c r="D2305" s="3">
+        <v>60.92</v>
+      </c>
+      <c r="E2305" s="3">
+        <v>60.41</v>
+      </c>
+      <c r="F2305" s="3">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:6">
+      <c r="A2306" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2306" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2306" s="3">
+        <v>54.18</v>
+      </c>
+      <c r="D2306" s="3">
+        <v>54.37</v>
+      </c>
+      <c r="E2306" s="3">
+        <v>54.17</v>
+      </c>
+      <c r="F2306" s="3">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:6">
+      <c r="A2307" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2307" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2307" s="3">
+        <v>48.48</v>
+      </c>
+      <c r="D2307" s="3">
+        <v>48.62</v>
+      </c>
+      <c r="E2307" s="3">
+        <v>48.25</v>
+      </c>
+      <c r="F2307" s="3">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:6">
+      <c r="A2308" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2308" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2308" s="3">
+        <v>45.58</v>
+      </c>
+      <c r="D2308" s="3">
+        <v>46.2</v>
+      </c>
+      <c r="E2308" s="3">
+        <v>45.42</v>
+      </c>
+      <c r="F2308" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:6">
+      <c r="A2309" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2309" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2309" s="3">
+        <v>57.42</v>
+      </c>
+      <c r="D2309" s="3">
+        <v>57.42</v>
+      </c>
+      <c r="E2309" s="3">
+        <v>57.26</v>
+      </c>
+      <c r="F2309" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:6">
+      <c r="A2310" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B2310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2310" s="3">
+        <v>71.12</v>
+      </c>
+      <c r="D2310" s="3">
+        <v>71.46</v>
+      </c>
+      <c r="E2310" s="3">
+        <v>70.02</v>
+      </c>
+      <c r="F2310" s="3">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:6">
+      <c r="A2311" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2311" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2311" s="3">
+        <v>62.72</v>
+      </c>
+      <c r="D2311" s="3">
+        <v>62.9</v>
+      </c>
+      <c r="E2311" s="3">
+        <v>62.68</v>
+      </c>
+      <c r="F2311" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:6">
+      <c r="A2312" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2312" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2312" s="3">
+        <v>60.63</v>
+      </c>
+      <c r="D2312" s="3">
+        <v>60.93</v>
+      </c>
+      <c r="E2312" s="3">
+        <v>60.46</v>
+      </c>
+      <c r="F2312" s="3">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:6">
+      <c r="A2313" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2313" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2313" s="3">
+        <v>53.77</v>
+      </c>
+      <c r="D2313" s="3">
+        <v>54.21</v>
+      </c>
+      <c r="E2313" s="3">
+        <v>53.6</v>
+      </c>
+      <c r="F2313" s="3">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:6">
+      <c r="A2314" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2314" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2314" s="3">
+        <v>48.33</v>
+      </c>
+      <c r="D2314" s="3">
+        <v>48.69</v>
+      </c>
+      <c r="E2314" s="3">
+        <v>48.16</v>
+      </c>
+      <c r="F2314" s="3">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:6">
+      <c r="A2315" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2315" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2315" s="3">
+        <v>45.56</v>
+      </c>
+      <c r="D2315" s="3">
+        <v>46.18</v>
+      </c>
+      <c r="E2315" s="3">
+        <v>45.5</v>
+      </c>
+      <c r="F2315" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:6">
+      <c r="A2316" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2316" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2316" s="3">
+        <v>57.49</v>
+      </c>
+      <c r="D2316" s="3">
+        <v>57.49</v>
+      </c>
+      <c r="E2316" s="3">
+        <v>57.23</v>
+      </c>
+      <c r="F2316" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:6">
+      <c r="A2317" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B2317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2317" s="3">
+        <v>70.32</v>
+      </c>
+      <c r="D2317" s="3">
+        <v>70.51</v>
+      </c>
+      <c r="E2317" s="3">
+        <v>69.99</v>
+      </c>
+      <c r="F2317" s="3">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:6">
+      <c r="A2318" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2318" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2318" s="3">
+        <v>62.83</v>
+      </c>
+      <c r="D2318" s="3">
+        <v>62.89</v>
+      </c>
+      <c r="E2318" s="3">
+        <v>62.67</v>
+      </c>
+      <c r="F2318" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:6">
+      <c r="A2319" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2319" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2319" s="3">
+        <v>60.36</v>
+      </c>
+      <c r="D2319" s="3">
+        <v>61.17</v>
+      </c>
+      <c r="E2319" s="3">
+        <v>60.34</v>
+      </c>
+      <c r="F2319" s="3">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:6">
+      <c r="A2320" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2320" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2320" s="3">
+        <v>54</v>
+      </c>
+      <c r="D2320" s="3">
+        <v>54.41</v>
+      </c>
+      <c r="E2320" s="3">
+        <v>53.75</v>
+      </c>
+      <c r="F2320" s="3">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:6">
+      <c r="A2321" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2321" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2321" s="3">
+        <v>48.37</v>
+      </c>
+      <c r="D2321" s="3">
+        <v>48.85</v>
+      </c>
+      <c r="E2321" s="3">
+        <v>48.13</v>
+      </c>
+      <c r="F2321" s="3">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:6">
+      <c r="A2322" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2322" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2322" s="3">
+        <v>46.13</v>
+      </c>
+      <c r="D2322" s="3">
+        <v>46.17</v>
+      </c>
+      <c r="E2322" s="3">
+        <v>45.76</v>
+      </c>
+      <c r="F2322" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:6">
+      <c r="A2323" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2323" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2323" s="3">
+        <v>57.36</v>
+      </c>
+      <c r="D2323" s="3">
+        <v>57.55</v>
+      </c>
+      <c r="E2323" s="3">
+        <v>57.02</v>
+      </c>
+      <c r="F2323" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:6">
+      <c r="A2324" s="2">
+        <v>46052</v>
+      </c>
+      <c r="B2324" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2324" s="3">
+        <v>70.4</v>
+      </c>
+      <c r="D2324" s="3">
+        <v>71.01</v>
+      </c>
+      <c r="E2324" s="3">
+        <v>70.06</v>
+      </c>
+      <c r="F2324" s="3">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:6">
+      <c r="A2325" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2325" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2325" s="3">
+        <v>63.26</v>
+      </c>
+      <c r="D2325" s="3">
+        <v>63.57</v>
+      </c>
+      <c r="E2325" s="3">
+        <v>62.32</v>
+      </c>
+      <c r="F2325" s="3">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:6">
+      <c r="A2326" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2326" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2326" s="3">
+        <v>61.39</v>
+      </c>
+      <c r="D2326" s="3">
+        <v>61.63</v>
+      </c>
+      <c r="E2326" s="3">
+        <v>60.71</v>
+      </c>
+      <c r="F2326" s="3">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:6">
+      <c r="A2327" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2327" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2327" s="3">
+        <v>53.93</v>
+      </c>
+      <c r="D2327" s="3">
+        <v>54.37</v>
+      </c>
+      <c r="E2327" s="3">
+        <v>53.72</v>
+      </c>
+      <c r="F2327" s="3">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:6">
+      <c r="A2328" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2328" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2328" s="3">
+        <v>48.26</v>
+      </c>
+      <c r="D2328" s="3">
+        <v>48.68</v>
+      </c>
+      <c r="E2328" s="3">
+        <v>48.19</v>
+      </c>
+      <c r="F2328" s="3">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:6">
+      <c r="A2329" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2329" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2329" s="3">
+        <v>45.9</v>
+      </c>
+      <c r="D2329" s="3">
+        <v>46.32</v>
+      </c>
+      <c r="E2329" s="3">
+        <v>45.86</v>
+      </c>
+      <c r="F2329" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:6">
+      <c r="A2330" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2330" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2330" s="3">
+        <v>56.98</v>
+      </c>
+      <c r="D2330" s="3">
+        <v>57.61</v>
+      </c>
+      <c r="E2330" s="3">
+        <v>56.92</v>
+      </c>
+      <c r="F2330" s="3">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:6">
+      <c r="A2331" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B2331" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2331" s="3">
+        <v>71</v>
+      </c>
+      <c r="D2331" s="3">
+        <v>71.1</v>
+      </c>
+      <c r="E2331" s="3">
+        <v>70.3</v>
+      </c>
+      <c r="F2331" s="3">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:6">
+      <c r="A2332" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2332" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2332" s="3"/>
+      <c r="D2332" s="3"/>
+      <c r="E2332" s="3"/>
+      <c r="F2332" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:6">
+      <c r="A2333" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2333" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2333" s="3"/>
+      <c r="D2333" s="3"/>
+      <c r="E2333" s="3"/>
+      <c r="F2333" s="4">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:6">
+      <c r="A2334" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2334" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2334" s="3"/>
+      <c r="D2334" s="3"/>
+      <c r="E2334" s="3"/>
+      <c r="F2334" s="4">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:6">
+      <c r="A2335" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2335" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2335" s="3"/>
+      <c r="D2335" s="3"/>
+      <c r="E2335" s="3"/>
+      <c r="F2335" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:6">
+      <c r="A2336" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2336" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2336" s="3"/>
+      <c r="D2336" s="3"/>
+      <c r="E2336" s="3"/>
+      <c r="F2336" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:6">
+      <c r="A2337" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2337" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2337" s="3"/>
+      <c r="D2337" s="3"/>
+      <c r="E2337" s="3"/>
+      <c r="F2337" s="4">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:6">
+      <c r="A2338" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B2338" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2338" s="3"/>
+      <c r="D2338" s="3"/>
+      <c r="E2338" s="3"/>
+      <c r="F2338" s="4">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:6">
+      <c r="A2339" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2339" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2339" s="3"/>
+      <c r="D2339" s="3"/>
+      <c r="E2339" s="3"/>
+      <c r="F2339" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:6">
+      <c r="A2340" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2340" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2340" s="3"/>
+      <c r="D2340" s="3"/>
+      <c r="E2340" s="3"/>
+      <c r="F2340" s="4">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:6">
+      <c r="A2341" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2341" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2341" s="3"/>
+      <c r="D2341" s="3"/>
+      <c r="E2341" s="3"/>
+      <c r="F2341" s="4">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:6">
+      <c r="A2342" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2342" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2342" s="3"/>
+      <c r="D2342" s="3"/>
+      <c r="E2342" s="3"/>
+      <c r="F2342" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:6">
+      <c r="A2343" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2343" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2343" s="3"/>
+      <c r="D2343" s="3"/>
+      <c r="E2343" s="3"/>
+      <c r="F2343" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:6">
+      <c r="A2344" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2344" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2344" s="3"/>
+      <c r="D2344" s="3"/>
+      <c r="E2344" s="3"/>
+      <c r="F2344" s="4">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:6">
+      <c r="A2345" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B2345" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2345" s="3"/>
+      <c r="D2345" s="3"/>
+      <c r="E2345" s="3"/>
+      <c r="F2345" s="4">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:6">
+      <c r="A2346" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2346" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2346" s="3"/>
+      <c r="D2346" s="3"/>
+      <c r="E2346" s="3"/>
+      <c r="F2346" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:6">
+      <c r="A2347" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2347" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2347" s="3"/>
+      <c r="D2347" s="3"/>
+      <c r="E2347" s="3"/>
+      <c r="F2347" s="4">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:6">
+      <c r="A2348" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2348" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2348" s="3"/>
+      <c r="D2348" s="3"/>
+      <c r="E2348" s="3"/>
+      <c r="F2348" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:6">
+      <c r="A2349" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2349" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2349" s="3"/>
+      <c r="D2349" s="3"/>
+      <c r="E2349" s="3"/>
+      <c r="F2349" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:6">
+      <c r="A2350" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2350" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2350" s="3"/>
+      <c r="D2350" s="3"/>
+      <c r="E2350" s="3"/>
+      <c r="F2350" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:6">
+      <c r="A2351" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2351" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2351" s="3"/>
+      <c r="D2351" s="3"/>
+      <c r="E2351" s="3"/>
+      <c r="F2351" s="4">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:6">
+      <c r="A2352" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B2352" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2352" s="3"/>
+      <c r="D2352" s="3"/>
+      <c r="E2352" s="3"/>
+      <c r="F2352" s="4">
+        <v>70.6</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:6">
+      <c r="A2353" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2353" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2353" s="3"/>
+      <c r="D2353" s="3"/>
+      <c r="E2353" s="3"/>
+      <c r="F2353" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:6">
+      <c r="A2354" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2354" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2354" s="3"/>
+      <c r="D2354" s="3"/>
+      <c r="E2354" s="3"/>
+      <c r="F2354" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:6">
+      <c r="A2355" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2355" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2355" s="3"/>
+      <c r="D2355" s="3"/>
+      <c r="E2355" s="3"/>
+      <c r="F2355" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:6">
+      <c r="A2356" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2356" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2356" s="3"/>
+      <c r="D2356" s="3"/>
+      <c r="E2356" s="3"/>
+      <c r="F2356" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:6">
+      <c r="A2357" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2357" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2357" s="3"/>
+      <c r="D2357" s="3"/>
+      <c r="E2357" s="3"/>
+      <c r="F2357" s="4">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:6">
+      <c r="A2358" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2358" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2358" s="3"/>
+      <c r="D2358" s="3"/>
+      <c r="E2358" s="3"/>
+      <c r="F2358" s="4">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:6">
+      <c r="A2359" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B2359" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2359" s="3"/>
+      <c r="D2359" s="3"/>
+      <c r="E2359" s="3"/>
+      <c r="F2359" s="4">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:6">
+      <c r="A2360" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2360" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2360" s="3"/>
+      <c r="D2360" s="3"/>
+      <c r="E2360" s="3"/>
+      <c r="F2360" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:6">
+      <c r="A2361" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2361" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2361" s="3"/>
+      <c r="D2361" s="3"/>
+      <c r="E2361" s="3"/>
+      <c r="F2361" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:6">
+      <c r="A2362" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2362" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2362" s="3"/>
+      <c r="D2362" s="3"/>
+      <c r="E2362" s="3"/>
+      <c r="F2362" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:6">
+      <c r="A2363" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2363" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2363" s="3"/>
+      <c r="D2363" s="3"/>
+      <c r="E2363" s="3"/>
+      <c r="F2363" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:6">
+      <c r="A2364" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2364" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2364" s="3"/>
+      <c r="D2364" s="3"/>
+      <c r="E2364" s="3"/>
+      <c r="F2364" s="4">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:6">
+      <c r="A2365" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2365" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2365" s="3"/>
+      <c r="D2365" s="3"/>
+      <c r="E2365" s="3"/>
+      <c r="F2365" s="4">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:6">
+      <c r="A2366" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B2366" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2366" s="3"/>
+      <c r="D2366" s="3"/>
+      <c r="E2366" s="3"/>
+      <c r="F2366" s="4">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:6">
+      <c r="A2367" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2367" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2367" s="3"/>
+      <c r="D2367" s="3"/>
+      <c r="E2367" s="3"/>
+      <c r="F2367" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:6">
+      <c r="A2368" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2368" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2368" s="3"/>
+      <c r="D2368" s="3"/>
+      <c r="E2368" s="3"/>
+      <c r="F2368" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:6">
+      <c r="A2369" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2369" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2369" s="3"/>
+      <c r="D2369" s="3"/>
+      <c r="E2369" s="3"/>
+      <c r="F2369" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:6">
+      <c r="A2370" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2370" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2370" s="3"/>
+      <c r="D2370" s="3"/>
+      <c r="E2370" s="3"/>
+      <c r="F2370" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:6">
+      <c r="A2371" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2371" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2371" s="3"/>
+      <c r="D2371" s="3"/>
+      <c r="E2371" s="3"/>
+      <c r="F2371" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:6">
+      <c r="A2372" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2372" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2372" s="3"/>
+      <c r="D2372" s="3"/>
+      <c r="E2372" s="3"/>
+      <c r="F2372" s="4">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:6">
+      <c r="A2373" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B2373" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2373" s="3"/>
+      <c r="D2373" s="3"/>
+      <c r="E2373" s="3"/>
+      <c r="F2373" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:6">
+      <c r="A2374" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2374" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2374" s="3"/>
+      <c r="D2374" s="3"/>
+      <c r="E2374" s="3"/>
+      <c r="F2374" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:6">
+      <c r="A2375" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2375" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2375" s="3"/>
+      <c r="D2375" s="3"/>
+      <c r="E2375" s="3"/>
+      <c r="F2375" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:6">
+      <c r="A2376" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2376" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2376" s="3"/>
+      <c r="D2376" s="3"/>
+      <c r="E2376" s="3"/>
+      <c r="F2376" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:6">
+      <c r="A2377" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2377" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2377" s="3"/>
+      <c r="D2377" s="3"/>
+      <c r="E2377" s="3"/>
+      <c r="F2377" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:6">
+      <c r="A2378" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2378" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2378" s="3"/>
+      <c r="D2378" s="3"/>
+      <c r="E2378" s="3"/>
+      <c r="F2378" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:6">
+      <c r="A2379" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2379" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2379" s="3"/>
+      <c r="D2379" s="3"/>
+      <c r="E2379" s="3"/>
+      <c r="F2379" s="4">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:6">
+      <c r="A2380" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B2380" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2380" s="3"/>
+      <c r="D2380" s="3"/>
+      <c r="E2380" s="3"/>
+      <c r="F2380" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:6">
+      <c r="A2381" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2381" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2381" s="3"/>
+      <c r="D2381" s="3"/>
+      <c r="E2381" s="3"/>
+      <c r="F2381" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:6">
+      <c r="A2382" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2382" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2382" s="3"/>
+      <c r="D2382" s="3"/>
+      <c r="E2382" s="3"/>
+      <c r="F2382" s="4">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:6">
+      <c r="A2383" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2383" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2383" s="3"/>
+      <c r="D2383" s="3"/>
+      <c r="E2383" s="3"/>
+      <c r="F2383" s="4">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:6">
+      <c r="A2384" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2384" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2384" s="3"/>
+      <c r="D2384" s="3"/>
+      <c r="E2384" s="3"/>
+      <c r="F2384" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:6">
+      <c r="A2385" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2385" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2385" s="3"/>
+      <c r="D2385" s="3"/>
+      <c r="E2385" s="3"/>
+      <c r="F2385" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:6">
+      <c r="A2386" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2386" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2386" s="3"/>
+      <c r="D2386" s="3"/>
+      <c r="E2386" s="3"/>
+      <c r="F2386" s="4">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:6">
+      <c r="A2387" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B2387" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2387" s="3"/>
+      <c r="D2387" s="3"/>
+      <c r="E2387" s="3"/>
+      <c r="F2387" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:6">
+      <c r="A2388" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2388" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2388" s="3"/>
+      <c r="D2388" s="3"/>
+      <c r="E2388" s="3"/>
+      <c r="F2388" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:6">
+      <c r="A2389" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2389" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2389" s="3"/>
+      <c r="D2389" s="3"/>
+      <c r="E2389" s="3"/>
+      <c r="F2389" s="4">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:6">
+      <c r="A2390" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2390" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2390" s="3"/>
+      <c r="D2390" s="3"/>
+      <c r="E2390" s="3"/>
+      <c r="F2390" s="4">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:6">
+      <c r="A2391" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2391" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2391" s="3"/>
+      <c r="D2391" s="3"/>
+      <c r="E2391" s="3"/>
+      <c r="F2391" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:6">
+      <c r="A2392" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2392" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2392" s="3"/>
+      <c r="D2392" s="3"/>
+      <c r="E2392" s="3"/>
+      <c r="F2392" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:6">
+      <c r="A2393" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2393" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2393" s="3"/>
+      <c r="D2393" s="3"/>
+      <c r="E2393" s="3"/>
+      <c r="F2393" s="4">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:6">
+      <c r="A2394" s="2">
+        <v>46065</v>
+      </c>
+      <c r="B2394" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2394" s="3"/>
+      <c r="D2394" s="3"/>
+      <c r="E2394" s="3"/>
+      <c r="F2394" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:6">
+      <c r="A2395" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2395" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2395" s="3"/>
+      <c r="D2395" s="3"/>
+      <c r="E2395" s="3"/>
+      <c r="F2395" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:6">
+      <c r="A2396" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2396" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2396" s="3"/>
+      <c r="D2396" s="3"/>
+      <c r="E2396" s="3"/>
+      <c r="F2396" s="4">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:6">
+      <c r="A2397" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2397" s="3"/>
+      <c r="D2397" s="3"/>
+      <c r="E2397" s="3"/>
+      <c r="F2397" s="4">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:6">
+      <c r="A2398" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2398" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2398" s="3"/>
+      <c r="D2398" s="3"/>
+      <c r="E2398" s="3"/>
+      <c r="F2398" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:6">
+      <c r="A2399" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2399" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2399" s="3"/>
+      <c r="D2399" s="3"/>
+      <c r="E2399" s="3"/>
+      <c r="F2399" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:6">
+      <c r="A2400" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2400" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2400" s="3"/>
+      <c r="D2400" s="3"/>
+      <c r="E2400" s="3"/>
+      <c r="F2400" s="4">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:6">
+      <c r="A2401" s="2">
+        <v>46066</v>
+      </c>
+      <c r="B2401" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2401" s="3"/>
+      <c r="D2401" s="3"/>
+      <c r="E2401" s="3"/>
+      <c r="F2401" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:6">
+      <c r="A2402" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2402" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2402" s="3"/>
+      <c r="D2402" s="3"/>
+      <c r="E2402" s="3"/>
+      <c r="F2402" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:6">
+      <c r="A2403" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2403" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2403" s="3"/>
+      <c r="D2403" s="3"/>
+      <c r="E2403" s="3"/>
+      <c r="F2403" s="4">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:6">
+      <c r="A2404" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2404" s="3"/>
+      <c r="D2404" s="3"/>
+      <c r="E2404" s="3"/>
+      <c r="F2404" s="4">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:6">
+      <c r="A2405" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2405" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2405" s="3"/>
+      <c r="D2405" s="3"/>
+      <c r="E2405" s="3"/>
+      <c r="F2405" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:6">
+      <c r="A2406" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2406" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2406" s="3"/>
+      <c r="D2406" s="3"/>
+      <c r="E2406" s="3"/>
+      <c r="F2406" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:6">
+      <c r="A2407" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2407" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2407" s="3"/>
+      <c r="D2407" s="3"/>
+      <c r="E2407" s="3"/>
+      <c r="F2407" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:6">
+      <c r="A2408" s="2">
+        <v>46069</v>
+      </c>
+      <c r="B2408" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2408" s="3"/>
+      <c r="D2408" s="3"/>
+      <c r="E2408" s="3"/>
+      <c r="F2408" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:6">
+      <c r="A2409" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2409" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2409" s="3"/>
+      <c r="D2409" s="3"/>
+      <c r="E2409" s="3"/>
+      <c r="F2409" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:6">
+      <c r="A2410" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2410" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2410" s="3"/>
+      <c r="D2410" s="3"/>
+      <c r="E2410" s="3"/>
+      <c r="F2410" s="4">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:6">
+      <c r="A2411" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2411" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2411" s="3"/>
+      <c r="D2411" s="3"/>
+      <c r="E2411" s="3"/>
+      <c r="F2411" s="4">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:6">
+      <c r="A2412" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2412" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2412" s="3"/>
+      <c r="D2412" s="3"/>
+      <c r="E2412" s="3"/>
+      <c r="F2412" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:6">
+      <c r="A2413" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2413" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2413" s="3"/>
+      <c r="D2413" s="3"/>
+      <c r="E2413" s="3"/>
+      <c r="F2413" s="4">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:6">
+      <c r="A2414" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2414" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2414" s="3"/>
+      <c r="D2414" s="3"/>
+      <c r="E2414" s="3"/>
+      <c r="F2414" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:6">
+      <c r="A2415" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B2415" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2415" s="3"/>
+      <c r="D2415" s="3"/>
+      <c r="E2415" s="3"/>
+      <c r="F2415" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:6">
+      <c r="A2416" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2416" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2416" s="3"/>
+      <c r="D2416" s="3"/>
+      <c r="E2416" s="3"/>
+      <c r="F2416" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:6">
+      <c r="A2417" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2417" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2417" s="3"/>
+      <c r="D2417" s="3"/>
+      <c r="E2417" s="3"/>
+      <c r="F2417" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:6">
+      <c r="A2418" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2418" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2418" s="3"/>
+      <c r="D2418" s="3"/>
+      <c r="E2418" s="3"/>
+      <c r="F2418" s="4">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:6">
+      <c r="A2419" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2419" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2419" s="3"/>
+      <c r="D2419" s="3"/>
+      <c r="E2419" s="3"/>
+      <c r="F2419" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:6">
+      <c r="A2420" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2420" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2420" s="3"/>
+      <c r="D2420" s="3"/>
+      <c r="E2420" s="3"/>
+      <c r="F2420" s="4">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:6">
+      <c r="A2421" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2421" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2421" s="3"/>
+      <c r="D2421" s="3"/>
+      <c r="E2421" s="3"/>
+      <c r="F2421" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:6">
+      <c r="A2422" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B2422" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2422" s="3"/>
+      <c r="D2422" s="3"/>
+      <c r="E2422" s="3"/>
+      <c r="F2422" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:6">
+      <c r="A2423" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2423" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2423" s="3"/>
+      <c r="D2423" s="3"/>
+      <c r="E2423" s="3"/>
+      <c r="F2423" s="4">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:6">
+      <c r="A2424" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2424" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2424" s="3"/>
+      <c r="D2424" s="3"/>
+      <c r="E2424" s="3"/>
+      <c r="F2424" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:6">
+      <c r="A2425" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2425" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2425" s="3"/>
+      <c r="D2425" s="3"/>
+      <c r="E2425" s="3"/>
+      <c r="F2425" s="4">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:6">
+      <c r="A2426" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2426" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2426" s="3"/>
+      <c r="D2426" s="3"/>
+      <c r="E2426" s="3"/>
+      <c r="F2426" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:6">
+      <c r="A2427" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2427" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2427" s="3"/>
+      <c r="D2427" s="3"/>
+      <c r="E2427" s="3"/>
+      <c r="F2427" s="4">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:6">
+      <c r="A2428" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2428" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2428" s="3"/>
+      <c r="D2428" s="3"/>
+      <c r="E2428" s="3"/>
+      <c r="F2428" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:6">
+      <c r="A2429" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B2429" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2429" s="3"/>
+      <c r="D2429" s="3"/>
+      <c r="E2429" s="3"/>
+      <c r="F2429" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:6">
+      <c r="A2430" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2430" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2430" s="3"/>
+      <c r="D2430" s="2"/>
+      <c r="E2430" s="3"/>
+      <c r="F2430" s="4">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:6">
+      <c r="A2431" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2431" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2431" s="3"/>
+      <c r="D2431" s="2"/>
+      <c r="E2431" s="3"/>
+      <c r="F2431" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:6">
+      <c r="A2432" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2432" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2432" s="3"/>
+      <c r="D2432" s="2"/>
+      <c r="E2432" s="3"/>
+      <c r="F2432" s="4">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:6">
+      <c r="A2433" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2433" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2433" s="3"/>
+      <c r="D2433" s="2"/>
+      <c r="E2433" s="3"/>
+      <c r="F2433" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:6">
+      <c r="A2434" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2434" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2434" s="3"/>
+      <c r="D2434" s="2"/>
+      <c r="E2434" s="3"/>
+      <c r="F2434" s="4">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:6">
+      <c r="A2435" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2435" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2435" s="3"/>
+      <c r="D2435" s="2"/>
+      <c r="E2435" s="3"/>
+      <c r="F2435" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:6">
+      <c r="A2436" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B2436" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2436" s="3"/>
+      <c r="D2436" s="2"/>
+      <c r="E2436" s="3"/>
+      <c r="F2436" s="4">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:6">
+      <c r="A2437" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2437" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2437" s="3"/>
+      <c r="D2437" s="2"/>
+      <c r="E2437" s="3"/>
+      <c r="F2437" s="3">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:6">
+      <c r="A2438" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2438" s="3"/>
+      <c r="D2438" s="2"/>
+      <c r="E2438" s="3"/>
+      <c r="F2438" s="3">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:6">
+      <c r="A2439" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2439" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2439" s="3"/>
+      <c r="D2439" s="2"/>
+      <c r="E2439" s="3"/>
+      <c r="F2439" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:6">
+      <c r="A2440" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2440" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2440" s="3"/>
+      <c r="D2440" s="2"/>
+      <c r="E2440" s="3"/>
+      <c r="F2440" s="4">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:6">
+      <c r="A2441" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2441" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2441" s="3"/>
+      <c r="D2441" s="2"/>
+      <c r="E2441" s="3"/>
+      <c r="F2441" s="3">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:6">
+      <c r="A2442" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2442" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2442" s="3"/>
+      <c r="D2442" s="2"/>
+      <c r="E2442" s="3"/>
+      <c r="F2442" s="3">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:6">
+      <c r="A2443" s="2">
+        <v>46081</v>
+      </c>
+      <c r="B2443" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2443" s="3"/>
+      <c r="D2443" s="2"/>
+      <c r="E2443" s="3"/>
+      <c r="F2443" s="3">
+        <v>70.8</v>
       </c>
     </row>
   </sheetData>
